--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1946,42 +1946,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755829</v>
+        <v>125755816</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1990,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523458</v>
+        <v>523620</v>
       </c>
       <c r="R15" t="n">
-        <v>6846108</v>
+        <v>6846303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,45 +2048,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755850</v>
+        <v>125755829</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523417</v>
+        <v>523458</v>
       </c>
       <c r="R16" t="n">
-        <v>6846164</v>
+        <v>6846108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2154,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755892</v>
+        <v>125755850</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2184,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523495</v>
+        <v>523417</v>
       </c>
       <c r="R17" t="n">
-        <v>6846328</v>
+        <v>6846164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,50 +2251,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755816</v>
+        <v>125755892</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523620</v>
+        <v>523495</v>
       </c>
       <c r="R18" t="n">
-        <v>6846303</v>
+        <v>6846328</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2935,32 +2935,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755842</v>
+        <v>125755909</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>91804</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523656</v>
+        <v>523407</v>
       </c>
       <c r="R25" t="n">
-        <v>6846239</v>
+        <v>6846172</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755802</v>
+        <v>125755842</v>
       </c>
       <c r="B26" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523478</v>
+        <v>523656</v>
       </c>
       <c r="R26" t="n">
-        <v>6846087</v>
+        <v>6846239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,59 +3129,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125742433</v>
+        <v>125755802</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>79585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523403</v>
+        <v>523478</v>
       </c>
       <c r="R27" t="n">
-        <v>6846072</v>
+        <v>6846087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,44 +3214,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755909</v>
+        <v>125755864</v>
       </c>
       <c r="B28" t="n">
-        <v>91804</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523407</v>
+        <v>523381</v>
       </c>
       <c r="R28" t="n">
-        <v>6846172</v>
+        <v>6846064</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,45 +3323,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755864</v>
+        <v>125742433</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523381</v>
+        <v>523403</v>
       </c>
       <c r="R29" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,12 +3422,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -6164,57 +6164,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755828</v>
+        <v>125740221</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523512</v>
+        <v>523538</v>
       </c>
       <c r="R58" t="n">
-        <v>6846071</v>
+        <v>6846149</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6258,19 +6249,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125740221</v>
+        <v>125755875</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6301,17 +6292,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523538</v>
+        <v>523436</v>
       </c>
       <c r="R59" t="n">
-        <v>6846149</v>
+        <v>6846102</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6355,57 +6346,66 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755806</v>
+        <v>125755828</v>
       </c>
       <c r="B60" t="n">
-        <v>78999</v>
+        <v>98324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523381</v>
+        <v>523512</v>
       </c>
       <c r="R60" t="n">
-        <v>6846064</v>
+        <v>6846071</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755875</v>
+        <v>125755806</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>78999</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523436</v>
+        <v>523381</v>
       </c>
       <c r="R61" t="n">
-        <v>6846102</v>
+        <v>6846064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125740764</v>
+        <v>125755846</v>
       </c>
       <c r="B62" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523443</v>
+        <v>523604</v>
       </c>
       <c r="R62" t="n">
-        <v>6846070</v>
+        <v>6846240</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,22 +6646,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755846</v>
+        <v>125755796</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523604</v>
+        <v>523627</v>
       </c>
       <c r="R63" t="n">
-        <v>6846240</v>
+        <v>6846239</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,10 +6755,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755796</v>
+        <v>125755863</v>
       </c>
       <c r="B64" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6766,21 +6766,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523627</v>
+        <v>523376</v>
       </c>
       <c r="R64" t="n">
-        <v>6846239</v>
+        <v>6846074</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755863</v>
+        <v>125755854</v>
       </c>
       <c r="B65" t="n">
         <v>78967</v>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523376</v>
+        <v>523410</v>
       </c>
       <c r="R65" t="n">
-        <v>6846074</v>
+        <v>6846112</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755854</v>
+        <v>125755880</v>
       </c>
       <c r="B66" t="n">
         <v>78967</v>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523410</v>
+        <v>523488</v>
       </c>
       <c r="R66" t="n">
-        <v>6846112</v>
+        <v>6846089</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755880</v>
+        <v>125740764</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523488</v>
+        <v>523443</v>
       </c>
       <c r="R67" t="n">
-        <v>6846089</v>
+        <v>6846070</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125740307</v>
+        <v>125740330</v>
       </c>
       <c r="B2" t="n">
         <v>78967</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125741230</v>
+        <v>125755851</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523475</v>
+        <v>523422</v>
       </c>
       <c r="R3" t="n">
-        <v>6846068</v>
+        <v>6846155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,60 +857,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125742098</v>
+        <v>125755807</v>
       </c>
       <c r="B4" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523403</v>
+        <v>523379</v>
       </c>
       <c r="R4" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +959,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1063,45 +1068,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755851</v>
+        <v>125755815</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523422</v>
+        <v>523605</v>
       </c>
       <c r="R6" t="n">
-        <v>6846155</v>
+        <v>6846199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,50 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755815</v>
+        <v>125741230</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523605</v>
+        <v>523475</v>
       </c>
       <c r="R7" t="n">
-        <v>6846199</v>
+        <v>6846068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,65 +1255,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755807</v>
+        <v>125742098</v>
       </c>
       <c r="B8" t="n">
-        <v>56843</v>
+        <v>79585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523379</v>
+        <v>523403</v>
       </c>
       <c r="R8" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R9" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755818</v>
+        <v>125740292</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>98248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523628</v>
+        <v>523521</v>
       </c>
       <c r="R10" t="n">
-        <v>6846224</v>
+        <v>6846131</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,22 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125741174</v>
+        <v>125755896</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523475</v>
+        <v>523465</v>
       </c>
       <c r="R11" t="n">
-        <v>6846068</v>
+        <v>6846335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755799</v>
+        <v>125742564</v>
       </c>
       <c r="B12" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523708</v>
+        <v>523612</v>
       </c>
       <c r="R12" t="n">
-        <v>6846300</v>
+        <v>6846245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,22 +1740,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755896</v>
+        <v>125755799</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523465</v>
+        <v>523708</v>
       </c>
       <c r="R13" t="n">
-        <v>6846335</v>
+        <v>6846300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,48 +1849,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125740292</v>
+        <v>125755818</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>78726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523521</v>
+        <v>523628</v>
       </c>
       <c r="R14" t="n">
-        <v>6846131</v>
+        <v>6846224</v>
       </c>
       <c r="S14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1934,50 +1934,54 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755816</v>
+        <v>125755829</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1986,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523620</v>
+        <v>523458</v>
       </c>
       <c r="R15" t="n">
-        <v>6846303</v>
+        <v>6846108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,54 +2052,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755829</v>
+        <v>125755850</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523458</v>
+        <v>523417</v>
       </c>
       <c r="R16" t="n">
-        <v>6846108</v>
+        <v>6846164</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2147,14 +2142,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755850</v>
+        <v>125755892</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523417</v>
+        <v>523495</v>
       </c>
       <c r="R17" t="n">
-        <v>6846164</v>
+        <v>6846328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2244,52 +2239,57 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755892</v>
+        <v>125755816</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523495</v>
+        <v>523620</v>
       </c>
       <c r="R18" t="n">
-        <v>6846328</v>
+        <v>6846303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,37 +2359,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R19" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2433,19 +2438,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125742673</v>
+        <v>125740874</v>
       </c>
       <c r="B20" t="n">
         <v>78967</v>
@@ -2476,17 +2481,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523590</v>
+        <v>523432</v>
       </c>
       <c r="R20" t="n">
-        <v>6846277</v>
+        <v>6846118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2530,22 +2535,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755812</v>
+        <v>125742673</v>
       </c>
       <c r="B21" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,39 +2558,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523437</v>
+        <v>523590</v>
       </c>
       <c r="R21" t="n">
-        <v>6846102</v>
+        <v>6846277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,19 +2632,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755874</v>
+        <v>125755839</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523446</v>
+        <v>523537</v>
       </c>
       <c r="R22" t="n">
-        <v>6846093</v>
+        <v>6846261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755836</v>
+        <v>125755874</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523502</v>
+        <v>523446</v>
       </c>
       <c r="R23" t="n">
-        <v>6846299</v>
+        <v>6846093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755839</v>
+        <v>125755836</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523537</v>
+        <v>523502</v>
       </c>
       <c r="R24" t="n">
-        <v>6846261</v>
+        <v>6846299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,45 +2935,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755909</v>
+        <v>125742433</v>
       </c>
       <c r="B25" t="n">
-        <v>91804</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1179</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523407</v>
+        <v>523403</v>
       </c>
       <c r="R25" t="n">
-        <v>6846172</v>
+        <v>6846072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,22 +3034,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755842</v>
+        <v>125741338</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,21 +3057,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3067,10 +3081,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523656</v>
+        <v>523403</v>
       </c>
       <c r="R26" t="n">
-        <v>6846239</v>
+        <v>6846072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,22 +3131,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755802</v>
+        <v>125755864</v>
       </c>
       <c r="B27" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3140,21 +3154,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3164,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523478</v>
+        <v>523381</v>
       </c>
       <c r="R27" t="n">
-        <v>6846087</v>
+        <v>6846064</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3219,17 +3233,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3251,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R28" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,59 +3337,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125742433</v>
+        <v>125755842</v>
       </c>
       <c r="B29" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523403</v>
+        <v>523656</v>
       </c>
       <c r="R29" t="n">
-        <v>6846072</v>
+        <v>6846239</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,44 +3422,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125741338</v>
+        <v>125755909</v>
       </c>
       <c r="B30" t="n">
-        <v>78726</v>
+        <v>91811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>1179</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523403</v>
+        <v>523407</v>
       </c>
       <c r="R30" t="n">
-        <v>6846072</v>
+        <v>6846172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3519,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740278</v>
+        <v>125755840</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523522</v>
+        <v>523595</v>
       </c>
       <c r="R31" t="n">
-        <v>6846208</v>
+        <v>6846194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,19 +3616,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125742754</v>
+        <v>125755877</v>
       </c>
       <c r="B32" t="n">
         <v>78967</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523569</v>
+        <v>523461</v>
       </c>
       <c r="R32" t="n">
-        <v>6846303</v>
+        <v>6846105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,22 +3713,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B33" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R33" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755877</v>
+        <v>125740942</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523461</v>
+        <v>523475</v>
       </c>
       <c r="R34" t="n">
-        <v>6846105</v>
+        <v>6846068</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,19 +3907,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755853</v>
+        <v>125742754</v>
       </c>
       <c r="B35" t="n">
         <v>78967</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523425</v>
+        <v>523569</v>
       </c>
       <c r="R35" t="n">
-        <v>6846130</v>
+        <v>6846303</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,19 +4004,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755840</v>
+        <v>125755853</v>
       </c>
       <c r="B36" t="n">
         <v>78967</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523595</v>
+        <v>523425</v>
       </c>
       <c r="R36" t="n">
-        <v>6846194</v>
+        <v>6846130</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755857</v>
+        <v>125755890</v>
       </c>
       <c r="B38" t="n">
         <v>78967</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523398</v>
+        <v>523496</v>
       </c>
       <c r="R38" t="n">
-        <v>6846095</v>
+        <v>6846308</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4300,14 +4300,14 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755890</v>
+        <v>125755857</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523496</v>
+        <v>523398</v>
       </c>
       <c r="R39" t="n">
-        <v>6846308</v>
+        <v>6846095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125740970</v>
+        <v>125755881</v>
       </c>
       <c r="B40" t="n">
         <v>78967</v>
@@ -4435,14 +4435,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523383</v>
+        <v>523499</v>
       </c>
       <c r="R40" t="n">
-        <v>6846110</v>
+        <v>6846107</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,37 +4512,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R41" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4572,6 +4572,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4586,22 +4591,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755901</v>
+        <v>125755814</v>
       </c>
       <c r="B42" t="n">
-        <v>78634</v>
+        <v>92707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523588</v>
+        <v>523456</v>
       </c>
       <c r="R42" t="n">
-        <v>6846217</v>
+        <v>6846109</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,10 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755814</v>
+        <v>125740970</v>
       </c>
       <c r="B43" t="n">
-        <v>92700</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,34 +4711,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523456</v>
+        <v>523383</v>
       </c>
       <c r="R43" t="n">
-        <v>6846109</v>
+        <v>6846110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4785,19 +4785,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B44" t="n">
         <v>78967</v>
@@ -4828,17 +4828,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R44" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4882,44 +4882,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755813</v>
+        <v>125755873</v>
       </c>
       <c r="B45" t="n">
-        <v>97202</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523458</v>
+        <v>523443</v>
       </c>
       <c r="R45" t="n">
-        <v>6846106</v>
+        <v>6846083</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
         <v>125755833</v>
       </c>
       <c r="B46" t="n">
-        <v>91380</v>
+        <v>91387</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755873</v>
+        <v>125755848</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523443</v>
+        <v>523515</v>
       </c>
       <c r="R47" t="n">
-        <v>6846083</v>
+        <v>6846181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5178,17 +5178,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755848</v>
+        <v>125740933</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,37 +5196,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523515</v>
+        <v>523405</v>
       </c>
       <c r="R48" t="n">
-        <v>6846181</v>
+        <v>6846104</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5270,12 +5270,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5372,61 +5372,52 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755831</v>
+        <v>125755813</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>97209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523491</v>
+        <v>523458</v>
       </c>
       <c r="R50" t="n">
-        <v>6846097</v>
+        <v>6846106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,48 +5476,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125740933</v>
+        <v>125755831</v>
       </c>
       <c r="B51" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523405</v>
+        <v>523491</v>
       </c>
       <c r="R51" t="n">
-        <v>6846104</v>
+        <v>6846097</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,12 +5570,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6351,61 +6351,52 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B60" t="n">
-        <v>98324</v>
+        <v>78999</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R60" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6464,45 +6455,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755806</v>
+        <v>125755828</v>
       </c>
       <c r="B61" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523381</v>
+        <v>523512</v>
       </c>
       <c r="R61" t="n">
-        <v>6846064</v>
+        <v>6846071</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755796</v>
+        <v>125755863</v>
       </c>
       <c r="B63" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523627</v>
+        <v>523376</v>
       </c>
       <c r="R63" t="n">
-        <v>6846239</v>
+        <v>6846074</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755863</v>
+        <v>125740764</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6766,37 +6766,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523376</v>
+        <v>523443</v>
       </c>
       <c r="R64" t="n">
-        <v>6846074</v>
+        <v>6846070</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6840,19 +6840,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755854</v>
+        <v>125755880</v>
       </c>
       <c r="B65" t="n">
         <v>78967</v>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523410</v>
+        <v>523488</v>
       </c>
       <c r="R65" t="n">
-        <v>6846112</v>
+        <v>6846089</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755880</v>
+        <v>125755854</v>
       </c>
       <c r="B66" t="n">
         <v>78967</v>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523488</v>
+        <v>523410</v>
       </c>
       <c r="R66" t="n">
-        <v>6846089</v>
+        <v>6846112</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7039,17 +7039,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125740764</v>
+        <v>125755796</v>
       </c>
       <c r="B67" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523443</v>
+        <v>523627</v>
       </c>
       <c r="R67" t="n">
-        <v>6846070</v>
+        <v>6846239</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,22 +7131,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125740179</v>
+        <v>125755805</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523507</v>
+        <v>523478</v>
       </c>
       <c r="R68" t="n">
-        <v>6846247</v>
+        <v>6846168</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7228,22 +7228,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755882</v>
+        <v>125755804</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523515</v>
+        <v>523485</v>
       </c>
       <c r="R69" t="n">
-        <v>6846106</v>
+        <v>6846156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755804</v>
+        <v>125755882</v>
       </c>
       <c r="B70" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7348,21 +7348,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523485</v>
+        <v>523515</v>
       </c>
       <c r="R70" t="n">
-        <v>6846156</v>
+        <v>6846106</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7427,17 +7427,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755805</v>
+        <v>125740179</v>
       </c>
       <c r="B71" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523478</v>
+        <v>523507</v>
       </c>
       <c r="R71" t="n">
-        <v>6846168</v>
+        <v>6846247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7519,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B72" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R72" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755843</v>
+        <v>125755817</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7736,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523662</v>
+        <v>523587</v>
       </c>
       <c r="R74" t="n">
-        <v>6846272</v>
+        <v>6846194</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755891</v>
+        <v>125755843</v>
       </c>
       <c r="B75" t="n">
         <v>78967</v>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523501</v>
+        <v>523662</v>
       </c>
       <c r="R75" t="n">
-        <v>6846327</v>
+        <v>6846272</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8016,32 +8016,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755897</v>
+        <v>125755855</v>
       </c>
       <c r="B77" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523669</v>
+        <v>523410</v>
       </c>
       <c r="R77" t="n">
-        <v>6846274</v>
+        <v>6846095</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8203,14 +8203,14 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755852</v>
+        <v>125755883</v>
       </c>
       <c r="B79" t="n">
         <v>78967</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523420</v>
+        <v>523485</v>
       </c>
       <c r="R79" t="n">
-        <v>6846145</v>
+        <v>6846121</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8300,14 +8300,14 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755883</v>
+        <v>125755847</v>
       </c>
       <c r="B80" t="n">
         <v>78967</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523485</v>
+        <v>523553</v>
       </c>
       <c r="R80" t="n">
-        <v>6846121</v>
+        <v>6846192</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755847</v>
+        <v>125755852</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523553</v>
+        <v>523420</v>
       </c>
       <c r="R81" t="n">
-        <v>6846192</v>
+        <v>6846145</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8494,39 +8494,39 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755841</v>
+        <v>125755897</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523605</v>
+        <v>523669</v>
       </c>
       <c r="R82" t="n">
-        <v>6846199</v>
+        <v>6846274</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8591,14 +8591,14 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755855</v>
+        <v>125755841</v>
       </c>
       <c r="B83" t="n">
         <v>78967</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523410</v>
+        <v>523605</v>
       </c>
       <c r="R83" t="n">
-        <v>6846095</v>
+        <v>6846199</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,14 +8785,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755837</v>
+        <v>125755888</v>
       </c>
       <c r="B85" t="n">
         <v>78967</v>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523530</v>
+        <v>523478</v>
       </c>
       <c r="R85" t="n">
-        <v>6846281</v>
+        <v>6846168</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -8986,32 +8986,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755898</v>
+        <v>125755837</v>
       </c>
       <c r="B87" t="n">
-        <v>92502</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523635</v>
+        <v>523530</v>
       </c>
       <c r="R87" t="n">
-        <v>6846293</v>
+        <v>6846281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9083,32 +9083,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755888</v>
+        <v>125755898</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523478</v>
+        <v>523635</v>
       </c>
       <c r="R88" t="n">
-        <v>6846168</v>
+        <v>6846293</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9367,17 +9367,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755905</v>
+        <v>125755819</v>
       </c>
       <c r="B91" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R91" t="n">
-        <v>6846102</v>
+        <v>6846238</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,7 +9471,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755904</v>
+        <v>125755905</v>
       </c>
       <c r="B92" t="n">
         <v>78634</v>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523504</v>
+        <v>523497</v>
       </c>
       <c r="R92" t="n">
-        <v>6846179</v>
+        <v>6846102</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9561,17 +9561,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755885</v>
+        <v>125755904</v>
       </c>
       <c r="B93" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523473</v>
+        <v>523504</v>
       </c>
       <c r="R93" t="n">
-        <v>6846151</v>
+        <v>6846179</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9658,17 +9658,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755825</v>
+        <v>125755885</v>
       </c>
       <c r="B94" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R94" t="n">
-        <v>6846224</v>
+        <v>6846151</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9755,17 +9755,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755819</v>
+        <v>125755825</v>
       </c>
       <c r="B95" t="n">
-        <v>78726</v>
+        <v>78725</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
         <v>523628</v>
       </c>
       <c r="R95" t="n">
-        <v>6846238</v>
+        <v>6846224</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9859,7 +9859,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755849</v>
+        <v>125755845</v>
       </c>
       <c r="B96" t="n">
         <v>78967</v>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523414</v>
+        <v>523663</v>
       </c>
       <c r="R96" t="n">
-        <v>6846169</v>
+        <v>6846295</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9949,14 +9949,14 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755884</v>
+        <v>125755844</v>
       </c>
       <c r="B97" t="n">
         <v>78967</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523471</v>
+        <v>523705</v>
       </c>
       <c r="R97" t="n">
-        <v>6846134</v>
+        <v>6846300</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10046,14 +10046,14 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755834</v>
+        <v>125755884</v>
       </c>
       <c r="B98" t="n">
         <v>78967</v>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523489</v>
+        <v>523471</v>
       </c>
       <c r="R98" t="n">
-        <v>6846326</v>
+        <v>6846134</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10143,14 +10143,14 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755844</v>
+        <v>125755834</v>
       </c>
       <c r="B99" t="n">
         <v>78967</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523705</v>
+        <v>523489</v>
       </c>
       <c r="R99" t="n">
-        <v>6846300</v>
+        <v>6846326</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10247,7 +10247,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755845</v>
+        <v>125755861</v>
       </c>
       <c r="B100" t="n">
         <v>78967</v>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523663</v>
+        <v>523389</v>
       </c>
       <c r="R100" t="n">
-        <v>6846295</v>
+        <v>6846092</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10434,14 +10434,14 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755861</v>
+        <v>125755849</v>
       </c>
       <c r="B102" t="n">
         <v>78967</v>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523389</v>
+        <v>523414</v>
       </c>
       <c r="R102" t="n">
-        <v>6846092</v>
+        <v>6846169</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10531,17 +10531,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755820</v>
+        <v>125755887</v>
       </c>
       <c r="B103" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10549,21 +10549,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523410</v>
+        <v>523473</v>
       </c>
       <c r="R103" t="n">
-        <v>6846112</v>
+        <v>6846157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10628,17 +10628,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755887</v>
+        <v>125755903</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523473</v>
+        <v>523586</v>
       </c>
       <c r="R104" t="n">
-        <v>6846157</v>
+        <v>6846193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10725,17 +10725,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,37 +10743,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R105" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10817,22 +10817,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755903</v>
+        <v>125742574</v>
       </c>
       <c r="B106" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,37 +10840,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523586</v>
+        <v>523592</v>
       </c>
       <c r="R106" t="n">
-        <v>6846193</v>
+        <v>6846248</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125740330</v>
+        <v>125742098</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523527</v>
+        <v>523403</v>
       </c>
       <c r="R2" t="n">
-        <v>6846185</v>
+        <v>6846072</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755851</v>
+        <v>125740330</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523422</v>
+        <v>523527</v>
       </c>
       <c r="R3" t="n">
-        <v>6846155</v>
+        <v>6846185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755807</v>
+        <v>125741230</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523379</v>
+        <v>523475</v>
       </c>
       <c r="R4" t="n">
-        <v>6846064</v>
+        <v>6846068</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755824</v>
+        <v>125755851</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523501</v>
+        <v>523422</v>
       </c>
       <c r="R5" t="n">
-        <v>6846078</v>
+        <v>6846155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755815</v>
+        <v>125755807</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,27 +1074,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1108,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523605</v>
+        <v>523379</v>
       </c>
       <c r="R6" t="n">
-        <v>6846199</v>
+        <v>6846064</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,45 +1165,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125741230</v>
+        <v>125755815</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523475</v>
+        <v>523605</v>
       </c>
       <c r="R7" t="n">
-        <v>6846068</v>
+        <v>6846199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125742098</v>
+        <v>125755824</v>
       </c>
       <c r="B8" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523403</v>
+        <v>523501</v>
       </c>
       <c r="R8" t="n">
-        <v>6846072</v>
+        <v>6846078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,60 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125741174</v>
+        <v>125740292</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>98248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523475</v>
+        <v>523521</v>
       </c>
       <c r="R9" t="n">
-        <v>6846068</v>
+        <v>6846131</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,60 +1449,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125740292</v>
+        <v>125755799</v>
       </c>
       <c r="B10" t="n">
-        <v>98248</v>
+        <v>79585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523521</v>
+        <v>523708</v>
       </c>
       <c r="R10" t="n">
-        <v>6846131</v>
+        <v>6846300</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,22 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755896</v>
+        <v>125755818</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523465</v>
+        <v>523628</v>
       </c>
       <c r="R11" t="n">
-        <v>6846335</v>
+        <v>6846224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755799</v>
+        <v>125741174</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523708</v>
+        <v>523475</v>
       </c>
       <c r="R13" t="n">
-        <v>6846300</v>
+        <v>6846068</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,22 +1837,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R14" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,61 +1939,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755829</v>
+        <v>125755892</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523458</v>
+        <v>523495</v>
       </c>
       <c r="R15" t="n">
-        <v>6846108</v>
+        <v>6846328</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,52 +2036,61 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755850</v>
+        <v>125755829</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523417</v>
+        <v>523458</v>
       </c>
       <c r="R16" t="n">
-        <v>6846164</v>
+        <v>6846108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,52 +2142,57 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755892</v>
+        <v>125755816</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523495</v>
+        <v>523620</v>
       </c>
       <c r="R17" t="n">
-        <v>6846328</v>
+        <v>6846303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,57 +2244,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755816</v>
+        <v>125755850</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523620</v>
+        <v>523417</v>
       </c>
       <c r="R18" t="n">
-        <v>6846303</v>
+        <v>6846164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,17 +2341,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,42 +2359,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R19" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2438,19 +2433,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125740874</v>
+        <v>125742673</v>
       </c>
       <c r="B20" t="n">
         <v>78967</v>
@@ -2481,17 +2476,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523432</v>
+        <v>523590</v>
       </c>
       <c r="R20" t="n">
-        <v>6846118</v>
+        <v>6846277</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2535,22 +2530,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125742673</v>
+        <v>125755812</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2558,34 +2553,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523590</v>
+        <v>523437</v>
       </c>
       <c r="R21" t="n">
-        <v>6846277</v>
+        <v>6846102</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,19 +2632,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755839</v>
+        <v>125755836</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523537</v>
+        <v>523502</v>
       </c>
       <c r="R22" t="n">
-        <v>6846261</v>
+        <v>6846299</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755874</v>
+        <v>125755839</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523446</v>
+        <v>523537</v>
       </c>
       <c r="R23" t="n">
-        <v>6846093</v>
+        <v>6846261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755836</v>
+        <v>125755874</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523502</v>
+        <v>523446</v>
       </c>
       <c r="R24" t="n">
-        <v>6846299</v>
+        <v>6846093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2928,56 +2928,42 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125742433</v>
+        <v>125741338</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
@@ -3046,10 +3032,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125741338</v>
+        <v>125755864</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3057,21 +3043,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3081,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523403</v>
+        <v>523381</v>
       </c>
       <c r="R26" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,22 +3117,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3154,21 +3140,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3178,10 +3164,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R27" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,17 +3219,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755802</v>
+        <v>125755842</v>
       </c>
       <c r="B28" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523478</v>
+        <v>523656</v>
       </c>
       <c r="R28" t="n">
-        <v>6846087</v>
+        <v>6846239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,32 +3323,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755842</v>
+        <v>125755909</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>91811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3372,10 +3358,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523656</v>
+        <v>523407</v>
       </c>
       <c r="R29" t="n">
-        <v>6846239</v>
+        <v>6846172</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,52 +3413,66 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755909</v>
+        <v>125742433</v>
       </c>
       <c r="B30" t="n">
-        <v>91811</v>
+        <v>56843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1179</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523407</v>
+        <v>523403</v>
       </c>
       <c r="R30" t="n">
-        <v>6846172</v>
+        <v>6846072</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3519,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755840</v>
+        <v>125740278</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523595</v>
+        <v>523522</v>
       </c>
       <c r="R31" t="n">
-        <v>6846194</v>
+        <v>6846208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755877</v>
+        <v>125740942</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523461</v>
+        <v>523475</v>
       </c>
       <c r="R32" t="n">
-        <v>6846105</v>
+        <v>6846068</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,19 +3713,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125740278</v>
+        <v>125742754</v>
       </c>
       <c r="B33" t="n">
         <v>78967</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523522</v>
+        <v>523569</v>
       </c>
       <c r="R33" t="n">
-        <v>6846208</v>
+        <v>6846303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125740942</v>
+        <v>125755840</v>
       </c>
       <c r="B34" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523475</v>
+        <v>523595</v>
       </c>
       <c r="R34" t="n">
-        <v>6846068</v>
+        <v>6846194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,19 +3907,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125742754</v>
+        <v>125755877</v>
       </c>
       <c r="B35" t="n">
         <v>78967</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523569</v>
+        <v>523461</v>
       </c>
       <c r="R35" t="n">
-        <v>6846303</v>
+        <v>6846105</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,12 +4004,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5379,45 +5379,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755813</v>
+        <v>125755831</v>
       </c>
       <c r="B50" t="n">
-        <v>97209</v>
+        <v>98331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523458</v>
+        <v>523491</v>
       </c>
       <c r="R50" t="n">
-        <v>6846106</v>
+        <v>6846097</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5476,54 +5485,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755831</v>
+        <v>125755813</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>97209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523491</v>
+        <v>523458</v>
       </c>
       <c r="R51" t="n">
-        <v>6846097</v>
+        <v>6846106</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755823</v>
+        <v>125740194</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523377</v>
+        <v>523518</v>
       </c>
       <c r="R52" t="n">
-        <v>6846073</v>
+        <v>6846232</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125740194</v>
+        <v>125742527</v>
       </c>
       <c r="B53" t="n">
         <v>78967</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523518</v>
+        <v>523403</v>
       </c>
       <c r="R53" t="n">
-        <v>6846232</v>
+        <v>6846072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125742527</v>
+        <v>125755859</v>
       </c>
       <c r="B54" t="n">
         <v>78967</v>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523403</v>
+        <v>523396</v>
       </c>
       <c r="R54" t="n">
-        <v>6846072</v>
+        <v>6846092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5861,22 +5861,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755859</v>
+        <v>125755798</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523396</v>
+        <v>523586</v>
       </c>
       <c r="R55" t="n">
-        <v>6846092</v>
+        <v>6846194</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5963,17 +5963,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755798</v>
+        <v>125755878</v>
       </c>
       <c r="B56" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523586</v>
+        <v>523484</v>
       </c>
       <c r="R56" t="n">
-        <v>6846194</v>
+        <v>6846075</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755878</v>
+        <v>125755823</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523484</v>
+        <v>523377</v>
       </c>
       <c r="R57" t="n">
-        <v>6846075</v>
+        <v>6846073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6157,55 +6157,64 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125740221</v>
+        <v>125755828</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523538</v>
+        <v>523512</v>
       </c>
       <c r="R58" t="n">
-        <v>6846149</v>
+        <v>6846071</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6249,19 +6258,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755875</v>
+        <v>125740221</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6292,17 +6301,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523436</v>
+        <v>523538</v>
       </c>
       <c r="R59" t="n">
-        <v>6846102</v>
+        <v>6846149</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6346,22 +6355,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755806</v>
+        <v>125755875</v>
       </c>
       <c r="B60" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6369,21 +6378,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6393,10 +6402,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523381</v>
+        <v>523436</v>
       </c>
       <c r="R60" t="n">
-        <v>6846064</v>
+        <v>6846102</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6448,61 +6457,52 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>78999</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R61" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125740592</v>
+        <v>125755855</v>
       </c>
       <c r="B76" t="n">
         <v>78967</v>
@@ -7950,17 +7950,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523450</v>
+        <v>523410</v>
       </c>
       <c r="R76" t="n">
-        <v>6846113</v>
+        <v>6846095</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,19 +8004,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755855</v>
+        <v>125755862</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523410</v>
+        <v>523377</v>
       </c>
       <c r="R77" t="n">
-        <v>6846095</v>
+        <v>6846085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755862</v>
+        <v>125755883</v>
       </c>
       <c r="B78" t="n">
         <v>78967</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523377</v>
+        <v>523485</v>
       </c>
       <c r="R78" t="n">
-        <v>6846085</v>
+        <v>6846121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755883</v>
+        <v>125755847</v>
       </c>
       <c r="B79" t="n">
         <v>78967</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523485</v>
+        <v>523553</v>
       </c>
       <c r="R79" t="n">
-        <v>6846121</v>
+        <v>6846192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755847</v>
+        <v>125755852</v>
       </c>
       <c r="B80" t="n">
         <v>78967</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523553</v>
+        <v>523420</v>
       </c>
       <c r="R80" t="n">
-        <v>6846192</v>
+        <v>6846145</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755852</v>
+        <v>125740592</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8435,17 +8435,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523420</v>
+        <v>523450</v>
       </c>
       <c r="R81" t="n">
-        <v>6846145</v>
+        <v>6846113</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8489,12 +8489,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8792,32 +8792,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755888</v>
+        <v>125755898</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523478</v>
+        <v>523635</v>
       </c>
       <c r="R85" t="n">
-        <v>6846168</v>
+        <v>6846293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755827</v>
+        <v>125755886</v>
       </c>
       <c r="B86" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523501</v>
+        <v>523485</v>
       </c>
       <c r="R86" t="n">
-        <v>6846078</v>
+        <v>6846156</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8979,14 +8979,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755837</v>
+        <v>125755889</v>
       </c>
       <c r="B87" t="n">
         <v>78967</v>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523530</v>
+        <v>523490</v>
       </c>
       <c r="R87" t="n">
-        <v>6846281</v>
+        <v>6846171</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9076,39 +9076,39 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755898</v>
+        <v>125755888</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>78967</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523635</v>
+        <v>523478</v>
       </c>
       <c r="R88" t="n">
-        <v>6846293</v>
+        <v>6846168</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9180,10 +9180,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755886</v>
+        <v>125755827</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9191,21 +9191,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523485</v>
+        <v>523501</v>
       </c>
       <c r="R89" t="n">
-        <v>6846156</v>
+        <v>6846078</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9270,14 +9270,14 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755889</v>
+        <v>125755837</v>
       </c>
       <c r="B90" t="n">
         <v>78967</v>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523490</v>
+        <v>523530</v>
       </c>
       <c r="R90" t="n">
-        <v>6846171</v>
+        <v>6846281</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9367,17 +9367,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B91" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R91" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9464,17 +9464,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755905</v>
+        <v>125755825</v>
       </c>
       <c r="B92" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R92" t="n">
-        <v>6846102</v>
+        <v>6846224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9561,17 +9561,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B93" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R93" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9658,17 +9658,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755885</v>
+        <v>125755905</v>
       </c>
       <c r="B94" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R94" t="n">
-        <v>6846151</v>
+        <v>6846102</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755825</v>
+        <v>125755904</v>
       </c>
       <c r="B95" t="n">
-        <v>78725</v>
+        <v>78634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R95" t="n">
-        <v>6846224</v>
+        <v>6846179</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10732,10 +10732,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755820</v>
+        <v>125742574</v>
       </c>
       <c r="B105" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,37 +10743,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523410</v>
+        <v>523592</v>
       </c>
       <c r="R105" t="n">
-        <v>6846112</v>
+        <v>6846248</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10817,22 +10817,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,37 +10840,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R106" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125741230</v>
+        <v>125755851</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523475</v>
+        <v>523422</v>
       </c>
       <c r="R4" t="n">
-        <v>6846068</v>
+        <v>6846155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,60 +954,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755851</v>
+        <v>125755807</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523422</v>
+        <v>523379</v>
       </c>
       <c r="R5" t="n">
-        <v>6846155</v>
+        <v>6846064</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,60 +1061,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755807</v>
+        <v>125755824</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523379</v>
+        <v>523501</v>
       </c>
       <c r="R6" t="n">
-        <v>6846064</v>
+        <v>6846078</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755824</v>
+        <v>125741230</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523501</v>
+        <v>523475</v>
       </c>
       <c r="R8" t="n">
-        <v>6846078</v>
+        <v>6846068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755836</v>
+        <v>125755839</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523502</v>
+        <v>523537</v>
       </c>
       <c r="R22" t="n">
-        <v>6846299</v>
+        <v>6846261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755839</v>
+        <v>125755874</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523537</v>
+        <v>523446</v>
       </c>
       <c r="R23" t="n">
-        <v>6846261</v>
+        <v>6846093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R24" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2928,42 +2928,56 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125741338</v>
+        <v>125742433</v>
       </c>
       <c r="B25" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
@@ -3032,10 +3046,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755864</v>
+        <v>125741338</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,21 +3057,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3067,10 +3081,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523381</v>
+        <v>523403</v>
       </c>
       <c r="R26" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,22 +3131,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755802</v>
+        <v>125755864</v>
       </c>
       <c r="B27" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3140,21 +3154,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3164,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523478</v>
+        <v>523381</v>
       </c>
       <c r="R27" t="n">
-        <v>6846087</v>
+        <v>6846064</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3219,17 +3233,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755842</v>
+        <v>125755802</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3251,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523656</v>
+        <v>523478</v>
       </c>
       <c r="R28" t="n">
-        <v>6846239</v>
+        <v>6846087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,32 +3337,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755909</v>
+        <v>125755842</v>
       </c>
       <c r="B29" t="n">
-        <v>91811</v>
+        <v>78967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3358,10 +3372,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523407</v>
+        <v>523656</v>
       </c>
       <c r="R29" t="n">
-        <v>6846172</v>
+        <v>6846239</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3413,66 +3427,52 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125742433</v>
+        <v>125755909</v>
       </c>
       <c r="B30" t="n">
-        <v>56843</v>
+        <v>91811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1179</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523403</v>
+        <v>523407</v>
       </c>
       <c r="R30" t="n">
-        <v>6846072</v>
+        <v>6846172</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,12 +3519,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755873</v>
+        <v>125740933</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,37 +4905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523443</v>
+        <v>523405</v>
       </c>
       <c r="R45" t="n">
-        <v>6846083</v>
+        <v>6846104</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,22 +4979,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755833</v>
+        <v>125755831</v>
       </c>
       <c r="B46" t="n">
-        <v>91387</v>
+        <v>98331</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,34 +5002,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523511</v>
+        <v>523491</v>
       </c>
       <c r="R46" t="n">
-        <v>6846118</v>
+        <v>6846097</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,7 +5097,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755848</v>
+        <v>125755879</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5123,10 +5132,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523515</v>
+        <v>523502</v>
       </c>
       <c r="R47" t="n">
-        <v>6846181</v>
+        <v>6846082</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,10 +5194,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125740933</v>
+        <v>125755873</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,37 +5205,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523405</v>
+        <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846104</v>
+        <v>6846083</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5270,44 +5279,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755879</v>
+        <v>125755833</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>91387</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5317,10 +5326,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523502</v>
+        <v>523511</v>
       </c>
       <c r="R49" t="n">
-        <v>6846082</v>
+        <v>6846118</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5372,61 +5381,52 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755831</v>
+        <v>125755848</v>
       </c>
       <c r="B50" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523491</v>
+        <v>523515</v>
       </c>
       <c r="R50" t="n">
-        <v>6846097</v>
+        <v>6846181</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755846</v>
+        <v>125740764</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523604</v>
+        <v>523443</v>
       </c>
       <c r="R62" t="n">
-        <v>6846240</v>
+        <v>6846070</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,19 +6646,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755863</v>
+        <v>125755880</v>
       </c>
       <c r="B63" t="n">
         <v>78967</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523376</v>
+        <v>523488</v>
       </c>
       <c r="R63" t="n">
-        <v>6846074</v>
+        <v>6846089</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,10 +6755,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125740764</v>
+        <v>125755854</v>
       </c>
       <c r="B64" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6766,37 +6766,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523443</v>
+        <v>523410</v>
       </c>
       <c r="R64" t="n">
-        <v>6846070</v>
+        <v>6846112</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6840,22 +6840,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755880</v>
+        <v>125755796</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6863,21 +6863,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523488</v>
+        <v>523627</v>
       </c>
       <c r="R65" t="n">
-        <v>6846089</v>
+        <v>6846239</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755854</v>
+        <v>125755846</v>
       </c>
       <c r="B66" t="n">
         <v>78967</v>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523410</v>
+        <v>523604</v>
       </c>
       <c r="R66" t="n">
-        <v>6846112</v>
+        <v>6846240</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755796</v>
+        <v>125755863</v>
       </c>
       <c r="B67" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523627</v>
+        <v>523376</v>
       </c>
       <c r="R67" t="n">
-        <v>6846239</v>
+        <v>6846074</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7136,17 +7136,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755805</v>
+        <v>125740179</v>
       </c>
       <c r="B68" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523478</v>
+        <v>523507</v>
       </c>
       <c r="R68" t="n">
-        <v>6846168</v>
+        <v>6846247</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7228,19 +7228,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755804</v>
+        <v>125755805</v>
       </c>
       <c r="B69" t="n">
         <v>79585</v>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523485</v>
+        <v>523478</v>
       </c>
       <c r="R69" t="n">
-        <v>6846156</v>
+        <v>6846168</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755882</v>
+        <v>125755804</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7348,21 +7348,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523515</v>
+        <v>523485</v>
       </c>
       <c r="R70" t="n">
-        <v>6846106</v>
+        <v>6846156</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7427,14 +7427,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125740179</v>
+        <v>125755882</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523507</v>
+        <v>523515</v>
       </c>
       <c r="R71" t="n">
-        <v>6846247</v>
+        <v>6846106</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,12 +7519,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755855</v>
+        <v>125740592</v>
       </c>
       <c r="B76" t="n">
         <v>78967</v>
@@ -7950,17 +7950,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523410</v>
+        <v>523450</v>
       </c>
       <c r="R76" t="n">
-        <v>6846095</v>
+        <v>6846113</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,19 +8004,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755862</v>
+        <v>125755855</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523377</v>
+        <v>523410</v>
       </c>
       <c r="R77" t="n">
-        <v>6846085</v>
+        <v>6846095</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755883</v>
+        <v>125755862</v>
       </c>
       <c r="B78" t="n">
         <v>78967</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523485</v>
+        <v>523377</v>
       </c>
       <c r="R78" t="n">
-        <v>6846121</v>
+        <v>6846085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755847</v>
+        <v>125755883</v>
       </c>
       <c r="B79" t="n">
         <v>78967</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523553</v>
+        <v>523485</v>
       </c>
       <c r="R79" t="n">
-        <v>6846192</v>
+        <v>6846121</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B80" t="n">
         <v>78967</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R80" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125740592</v>
+        <v>125755852</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8435,17 +8435,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523450</v>
+        <v>523420</v>
       </c>
       <c r="R81" t="n">
-        <v>6846113</v>
+        <v>6846145</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8489,12 +8489,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10732,10 +10732,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,37 +10743,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R105" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10817,22 +10817,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755820</v>
+        <v>125742574</v>
       </c>
       <c r="B106" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,37 +10840,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523410</v>
+        <v>523592</v>
       </c>
       <c r="R106" t="n">
-        <v>6846112</v>
+        <v>6846248</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125742098</v>
+        <v>125755807</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523403</v>
+        <v>523379</v>
       </c>
       <c r="R2" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125740330</v>
+        <v>125755851</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523527</v>
+        <v>523422</v>
       </c>
       <c r="R3" t="n">
-        <v>6846185</v>
+        <v>6846155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755851</v>
+        <v>125741230</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523422</v>
+        <v>523475</v>
       </c>
       <c r="R4" t="n">
-        <v>6846155</v>
+        <v>6846068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,65 +959,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755807</v>
+        <v>125742098</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>79586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523379</v>
+        <v>523403</v>
       </c>
       <c r="R5" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>125755824</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,50 +1165,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755815</v>
+        <v>125740307</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523605</v>
+        <v>523527</v>
       </c>
       <c r="R7" t="n">
-        <v>6846199</v>
+        <v>6846185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,57 +1250,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125741230</v>
+        <v>125755815</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523475</v>
+        <v>523605</v>
       </c>
       <c r="R8" t="n">
-        <v>6846068</v>
+        <v>6846199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
         <v>125740292</v>
       </c>
       <c r="B9" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755799</v>
+        <v>125741174</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523708</v>
+        <v>523475</v>
       </c>
       <c r="R10" t="n">
-        <v>6846300</v>
+        <v>6846068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,22 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755818</v>
+        <v>125742564</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523628</v>
+        <v>523612</v>
       </c>
       <c r="R11" t="n">
-        <v>6846224</v>
+        <v>6846245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125742564</v>
+        <v>125755818</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523612</v>
+        <v>523628</v>
       </c>
       <c r="R12" t="n">
-        <v>6846245</v>
+        <v>6846224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,22 +1740,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125741174</v>
+        <v>125755799</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523475</v>
+        <v>523708</v>
       </c>
       <c r="R13" t="n">
-        <v>6846068</v>
+        <v>6846300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,12 +1837,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
         <v>125755896</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755892</v>
+        <v>125755850</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523495</v>
+        <v>523417</v>
       </c>
       <c r="R15" t="n">
-        <v>6846328</v>
+        <v>6846164</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,61 +2036,52 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755829</v>
+        <v>125755892</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523458</v>
+        <v>523495</v>
       </c>
       <c r="R16" t="n">
-        <v>6846108</v>
+        <v>6846328</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,45 +2242,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755850</v>
+        <v>125755829</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523417</v>
+        <v>523458</v>
       </c>
       <c r="R18" t="n">
-        <v>6846164</v>
+        <v>6846108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,17 +2341,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,37 +2359,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R19" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2433,22 +2438,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125742673</v>
+        <v>125740874</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,17 +2481,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523590</v>
+        <v>523432</v>
       </c>
       <c r="R20" t="n">
-        <v>6846277</v>
+        <v>6846118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2530,22 +2535,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755812</v>
+        <v>125742673</v>
       </c>
       <c r="B21" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,39 +2558,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523437</v>
+        <v>523590</v>
       </c>
       <c r="R21" t="n">
-        <v>6846102</v>
+        <v>6846277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,22 +2632,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755839</v>
+        <v>125755874</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523537</v>
+        <v>523446</v>
       </c>
       <c r="R22" t="n">
-        <v>6846261</v>
+        <v>6846093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R23" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2831,17 +2831,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755836</v>
+        <v>125755839</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523502</v>
+        <v>523537</v>
       </c>
       <c r="R24" t="n">
-        <v>6846299</v>
+        <v>6846261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,49 +2935,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125742433</v>
+        <v>125741338</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
@@ -3046,10 +3032,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125741338</v>
+        <v>125755842</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3057,21 +3043,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3081,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523403</v>
+        <v>523656</v>
       </c>
       <c r="R26" t="n">
-        <v>6846072</v>
+        <v>6846239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,22 +3117,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3154,21 +3140,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3178,10 +3164,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R27" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,17 +3219,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755802</v>
+        <v>125755864</v>
       </c>
       <c r="B28" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523478</v>
+        <v>523381</v>
       </c>
       <c r="R28" t="n">
-        <v>6846087</v>
+        <v>6846064</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,45 +3323,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755842</v>
+        <v>125742433</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523656</v>
+        <v>523403</v>
       </c>
       <c r="R29" t="n">
-        <v>6846239</v>
+        <v>6846072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,12 +3422,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
         <v>125755909</v>
       </c>
       <c r="B30" t="n">
-        <v>91811</v>
+        <v>91815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,17 +3524,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740278</v>
+        <v>125740942</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523522</v>
+        <v>523475</v>
       </c>
       <c r="R31" t="n">
-        <v>6846208</v>
+        <v>6846068</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R32" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,7 +3728,7 @@
         <v>125742754</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755840</v>
+        <v>125755877</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523595</v>
+        <v>523461</v>
       </c>
       <c r="R34" t="n">
-        <v>6846194</v>
+        <v>6846105</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755877</v>
+        <v>125755853</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523461</v>
+        <v>523425</v>
       </c>
       <c r="R35" t="n">
-        <v>6846105</v>
+        <v>6846130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755853</v>
+        <v>125755840</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523425</v>
+        <v>523595</v>
       </c>
       <c r="R36" t="n">
-        <v>6846130</v>
+        <v>6846194</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,17 +4106,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125740148</v>
+        <v>125755857</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523497</v>
+        <v>523398</v>
       </c>
       <c r="R37" t="n">
-        <v>6846271</v>
+        <v>6846095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,12 +4198,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         <v>125755890</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4300,17 +4300,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755857</v>
+        <v>125740148</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523398</v>
+        <v>523497</v>
       </c>
       <c r="R39" t="n">
-        <v>6846095</v>
+        <v>6846271</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755881</v>
+        <v>125755814</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>92710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523499</v>
+        <v>523456</v>
       </c>
       <c r="R40" t="n">
-        <v>6846107</v>
+        <v>6846109</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755901</v>
+        <v>125755881</v>
       </c>
       <c r="B41" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523588</v>
+        <v>523499</v>
       </c>
       <c r="R41" t="n">
-        <v>6846217</v>
+        <v>6846107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4574,11 +4574,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4596,17 +4591,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755814</v>
+        <v>125755901</v>
       </c>
       <c r="B42" t="n">
-        <v>92707</v>
+        <v>78635</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523456</v>
+        <v>523588</v>
       </c>
       <c r="R42" t="n">
-        <v>6846109</v>
+        <v>6846217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4703,7 +4703,7 @@
         <v>125740970</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>125742499</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125740933</v>
+        <v>125755848</v>
       </c>
       <c r="B45" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,37 +4905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523405</v>
+        <v>523515</v>
       </c>
       <c r="R45" t="n">
-        <v>6846104</v>
+        <v>6846181</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,66 +4979,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755831</v>
+        <v>125755879</v>
       </c>
       <c r="B46" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523491</v>
+        <v>523502</v>
       </c>
       <c r="R46" t="n">
-        <v>6846097</v>
+        <v>6846082</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5097,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755879</v>
+        <v>125755873</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5132,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523502</v>
+        <v>523443</v>
       </c>
       <c r="R47" t="n">
-        <v>6846082</v>
+        <v>6846083</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5187,39 +5178,39 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755873</v>
+        <v>125755833</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>91389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5229,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523443</v>
+        <v>523511</v>
       </c>
       <c r="R48" t="n">
-        <v>6846083</v>
+        <v>6846118</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5284,17 +5275,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755833</v>
+        <v>125755831</v>
       </c>
       <c r="B49" t="n">
-        <v>91387</v>
+        <v>98334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5302,34 +5293,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523511</v>
+        <v>523491</v>
       </c>
       <c r="R49" t="n">
-        <v>6846118</v>
+        <v>6846097</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5388,32 +5388,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755848</v>
+        <v>125755813</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>97212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523515</v>
+        <v>523458</v>
       </c>
       <c r="R50" t="n">
-        <v>6846181</v>
+        <v>6846106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,55 +5478,55 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755813</v>
+        <v>125740933</v>
       </c>
       <c r="B51" t="n">
-        <v>97209</v>
+        <v>78727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523458</v>
+        <v>523405</v>
       </c>
       <c r="R51" t="n">
-        <v>6846106</v>
+        <v>6846104</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,22 +5570,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125740194</v>
+        <v>125755859</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523518</v>
+        <v>523396</v>
       </c>
       <c r="R52" t="n">
-        <v>6846232</v>
+        <v>6846092</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,22 +5667,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125742527</v>
+        <v>125755798</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5690,21 +5690,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523403</v>
+        <v>523586</v>
       </c>
       <c r="R53" t="n">
-        <v>6846072</v>
+        <v>6846194</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,22 +5764,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R54" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5866,17 +5866,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755798</v>
+        <v>125755823</v>
       </c>
       <c r="B55" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523586</v>
+        <v>523377</v>
       </c>
       <c r="R55" t="n">
-        <v>6846194</v>
+        <v>6846073</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755878</v>
+        <v>125740194</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523484</v>
+        <v>523518</v>
       </c>
       <c r="R56" t="n">
-        <v>6846075</v>
+        <v>6846232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6055,22 +6055,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755823</v>
+        <v>125742527</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523377</v>
+        <v>523403</v>
       </c>
       <c r="R57" t="n">
-        <v>6846073</v>
+        <v>6846072</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6152,66 +6152,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B58" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R58" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6270,10 +6261,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125740221</v>
+        <v>125755875</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6301,17 +6292,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523538</v>
+        <v>523436</v>
       </c>
       <c r="R59" t="n">
-        <v>6846149</v>
+        <v>6846102</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6355,57 +6346,66 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R60" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6457,17 +6457,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755806</v>
+        <v>125740221</v>
       </c>
       <c r="B61" t="n">
-        <v>78999</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6475,37 +6475,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523381</v>
+        <v>523538</v>
       </c>
       <c r="R61" t="n">
-        <v>6846064</v>
+        <v>6846149</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6549,22 +6549,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125740764</v>
+        <v>125755846</v>
       </c>
       <c r="B62" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523443</v>
+        <v>523604</v>
       </c>
       <c r="R62" t="n">
-        <v>6846070</v>
+        <v>6846240</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,22 +6646,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755880</v>
+        <v>125755796</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523488</v>
+        <v>523627</v>
       </c>
       <c r="R63" t="n">
-        <v>6846089</v>
+        <v>6846239</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R64" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6845,17 +6845,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755796</v>
+        <v>125755854</v>
       </c>
       <c r="B65" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6863,21 +6863,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523627</v>
+        <v>523410</v>
       </c>
       <c r="R65" t="n">
-        <v>6846239</v>
+        <v>6846112</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755846</v>
+        <v>125755880</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523604</v>
+        <v>523488</v>
       </c>
       <c r="R66" t="n">
-        <v>6846240</v>
+        <v>6846089</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7039,17 +7039,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755863</v>
+        <v>125740764</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523376</v>
+        <v>523443</v>
       </c>
       <c r="R67" t="n">
-        <v>6846074</v>
+        <v>6846070</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,22 +7131,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125740179</v>
+        <v>125755882</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523507</v>
+        <v>523515</v>
       </c>
       <c r="R68" t="n">
-        <v>6846247</v>
+        <v>6846106</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7228,22 +7228,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755805</v>
+        <v>125755804</v>
       </c>
       <c r="B69" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523478</v>
+        <v>523485</v>
       </c>
       <c r="R69" t="n">
-        <v>6846168</v>
+        <v>6846156</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755804</v>
+        <v>125755805</v>
       </c>
       <c r="B70" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523485</v>
+        <v>523478</v>
       </c>
       <c r="R70" t="n">
-        <v>6846156</v>
+        <v>6846168</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755882</v>
+        <v>125740179</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523515</v>
+        <v>523507</v>
       </c>
       <c r="R71" t="n">
-        <v>6846106</v>
+        <v>6846247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7519,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755891</v>
+        <v>125755826</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523501</v>
+        <v>523408</v>
       </c>
       <c r="R72" t="n">
-        <v>6846327</v>
+        <v>6846116</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7621,17 +7621,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B73" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R73" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7736,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R74" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755843</v>
+        <v>125755817</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7833,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523662</v>
+        <v>523587</v>
       </c>
       <c r="R75" t="n">
-        <v>6846272</v>
+        <v>6846194</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7919,48 +7919,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125740592</v>
+        <v>125755897</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523450</v>
+        <v>523669</v>
       </c>
       <c r="R76" t="n">
-        <v>6846113</v>
+        <v>6846274</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,22 +8004,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755855</v>
+        <v>125755862</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523410</v>
+        <v>523377</v>
       </c>
       <c r="R77" t="n">
-        <v>6846095</v>
+        <v>6846085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8106,17 +8106,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755862</v>
+        <v>125755852</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523377</v>
+        <v>523420</v>
       </c>
       <c r="R78" t="n">
-        <v>6846085</v>
+        <v>6846145</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
         <v>125755883</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8310,7 +8310,7 @@
         <v>125755847</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,17 +8397,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755852</v>
+        <v>125755841</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523420</v>
+        <v>523605</v>
       </c>
       <c r="R81" t="n">
-        <v>6846145</v>
+        <v>6846199</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8494,39 +8494,39 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755897</v>
+        <v>125755855</v>
       </c>
       <c r="B82" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523669</v>
+        <v>523410</v>
       </c>
       <c r="R82" t="n">
-        <v>6846274</v>
+        <v>6846095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8591,17 +8591,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755841</v>
+        <v>125755858</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523605</v>
+        <v>523393</v>
       </c>
       <c r="R83" t="n">
-        <v>6846199</v>
+        <v>6846095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,10 +8695,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755858</v>
+        <v>125740592</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,17 +8726,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523393</v>
+        <v>523450</v>
       </c>
       <c r="R84" t="n">
-        <v>6846095</v>
+        <v>6846113</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8780,44 +8780,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755898</v>
+        <v>125755837</v>
       </c>
       <c r="B85" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523635</v>
+        <v>523530</v>
       </c>
       <c r="R85" t="n">
-        <v>6846293</v>
+        <v>6846281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8882,17 +8882,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755886</v>
+        <v>125755827</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523485</v>
+        <v>523501</v>
       </c>
       <c r="R86" t="n">
-        <v>6846156</v>
+        <v>6846078</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8979,39 +8979,39 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755889</v>
+        <v>125755898</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523490</v>
+        <v>523635</v>
       </c>
       <c r="R87" t="n">
-        <v>6846171</v>
+        <v>6846293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
         <v>125755888</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9173,17 +9173,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755827</v>
+        <v>125755886</v>
       </c>
       <c r="B89" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9191,21 +9191,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523501</v>
+        <v>523485</v>
       </c>
       <c r="R89" t="n">
-        <v>6846078</v>
+        <v>6846156</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9277,10 +9277,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755837</v>
+        <v>125755889</v>
       </c>
       <c r="B90" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523530</v>
+        <v>523490</v>
       </c>
       <c r="R90" t="n">
-        <v>6846281</v>
+        <v>6846171</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
         <v>125755885</v>
       </c>
       <c r="B91" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
         <v>125755825</v>
       </c>
       <c r="B92" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755819</v>
+        <v>125755905</v>
       </c>
       <c r="B93" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523628</v>
+        <v>523497</v>
       </c>
       <c r="R93" t="n">
-        <v>6846238</v>
+        <v>6846102</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755905</v>
+        <v>125755904</v>
       </c>
       <c r="B94" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523497</v>
+        <v>523504</v>
       </c>
       <c r="R94" t="n">
-        <v>6846102</v>
+        <v>6846179</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9755,17 +9755,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B95" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R95" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9852,17 +9852,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755845</v>
+        <v>125755849</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523663</v>
+        <v>523414</v>
       </c>
       <c r="R96" t="n">
-        <v>6846295</v>
+        <v>6846169</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9949,17 +9949,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755844</v>
+        <v>125755884</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523705</v>
+        <v>523471</v>
       </c>
       <c r="R97" t="n">
-        <v>6846300</v>
+        <v>6846134</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10046,17 +10046,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755884</v>
+        <v>125755834</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523471</v>
+        <v>523489</v>
       </c>
       <c r="R98" t="n">
-        <v>6846134</v>
+        <v>6846326</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10143,17 +10143,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755834</v>
+        <v>125755844</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523489</v>
+        <v>523705</v>
       </c>
       <c r="R99" t="n">
-        <v>6846326</v>
+        <v>6846300</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10247,10 +10247,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755861</v>
+        <v>125755845</v>
       </c>
       <c r="B100" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523389</v>
+        <v>523663</v>
       </c>
       <c r="R100" t="n">
-        <v>6846092</v>
+        <v>6846295</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10347,7 +10347,7 @@
         <v>125755876</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10434,17 +10434,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755849</v>
+        <v>125755861</v>
       </c>
       <c r="B102" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523414</v>
+        <v>523389</v>
       </c>
       <c r="R102" t="n">
-        <v>6846169</v>
+        <v>6846092</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10531,17 +10531,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10569,17 +10569,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R103" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10623,22 +10623,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755903</v>
+        <v>125755820</v>
       </c>
       <c r="B104" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523586</v>
+        <v>523410</v>
       </c>
       <c r="R104" t="n">
-        <v>6846193</v>
+        <v>6846112</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10725,17 +10725,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755820</v>
+        <v>125755903</v>
       </c>
       <c r="B105" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,21 +10743,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523410</v>
+        <v>523586</v>
       </c>
       <c r="R105" t="n">
-        <v>6846112</v>
+        <v>6846193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10829,10 +10829,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125742574</v>
+        <v>125755887</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10860,17 +10860,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523592</v>
+        <v>523473</v>
       </c>
       <c r="R106" t="n">
-        <v>6846248</v>
+        <v>6846157</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125742564</v>
+        <v>125755799</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523612</v>
+        <v>523708</v>
       </c>
       <c r="R11" t="n">
-        <v>6846245</v>
+        <v>6846300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R12" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755799</v>
+        <v>125742564</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523708</v>
+        <v>523612</v>
       </c>
       <c r="R13" t="n">
-        <v>6846300</v>
+        <v>6846245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,22 +1837,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755896</v>
+        <v>125755818</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523465</v>
+        <v>523628</v>
       </c>
       <c r="R14" t="n">
-        <v>6846335</v>
+        <v>6846224</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,38 +2140,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755816</v>
+        <v>125755829</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2180,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523620</v>
+        <v>523458</v>
       </c>
       <c r="R17" t="n">
-        <v>6846303</v>
+        <v>6846108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,42 +2246,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755829</v>
+        <v>125755816</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523458</v>
+        <v>523620</v>
       </c>
       <c r="R18" t="n">
-        <v>6846108</v>
+        <v>6846303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,42 +2359,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R19" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2438,22 +2433,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2461,37 +2456,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R20" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2535,12 +2535,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4894,7 +4894,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755848</v>
+        <v>125755873</v>
       </c>
       <c r="B45" t="n">
         <v>78968</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523515</v>
+        <v>523443</v>
       </c>
       <c r="R45" t="n">
-        <v>6846181</v>
+        <v>6846083</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755879</v>
+        <v>125755833</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>91389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523502</v>
+        <v>523511</v>
       </c>
       <c r="R46" t="n">
-        <v>6846082</v>
+        <v>6846118</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,45 +5088,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755873</v>
+        <v>125755831</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523443</v>
+        <v>523491</v>
       </c>
       <c r="R47" t="n">
-        <v>6846083</v>
+        <v>6846097</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,32 +5194,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755833</v>
+        <v>125755813</v>
       </c>
       <c r="B48" t="n">
-        <v>91389</v>
+        <v>97212</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5229,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523511</v>
+        <v>523458</v>
       </c>
       <c r="R48" t="n">
-        <v>6846118</v>
+        <v>6846106</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5282,57 +5291,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755831</v>
+        <v>125740933</v>
       </c>
       <c r="B49" t="n">
-        <v>98334</v>
+        <v>78727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523491</v>
+        <v>523405</v>
       </c>
       <c r="R49" t="n">
-        <v>6846097</v>
+        <v>6846104</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5376,44 +5376,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755813</v>
+        <v>125755848</v>
       </c>
       <c r="B50" t="n">
-        <v>97212</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523458</v>
+        <v>523515</v>
       </c>
       <c r="R50" t="n">
-        <v>6846106</v>
+        <v>6846181</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125740933</v>
+        <v>125755879</v>
       </c>
       <c r="B51" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5496,37 +5496,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523405</v>
+        <v>523502</v>
       </c>
       <c r="R51" t="n">
-        <v>6846104</v>
+        <v>6846082</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,12 +5570,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755823</v>
+        <v>125740194</v>
       </c>
       <c r="B55" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523377</v>
+        <v>523518</v>
       </c>
       <c r="R55" t="n">
-        <v>6846073</v>
+        <v>6846232</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,19 +5958,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125740194</v>
+        <v>125742527</v>
       </c>
       <c r="B56" t="n">
         <v>78968</v>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523518</v>
+        <v>523403</v>
       </c>
       <c r="R56" t="n">
-        <v>6846232</v>
+        <v>6846072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125742527</v>
+        <v>125755823</v>
       </c>
       <c r="B57" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523403</v>
+        <v>523377</v>
       </c>
       <c r="R57" t="n">
-        <v>6846072</v>
+        <v>6846073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6152,12 +6152,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7919,48 +7919,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755897</v>
+        <v>125740592</v>
       </c>
       <c r="B76" t="n">
-        <v>92518</v>
+        <v>78968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523669</v>
+        <v>523450</v>
       </c>
       <c r="R76" t="n">
-        <v>6846274</v>
+        <v>6846113</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,44 +8004,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755862</v>
+        <v>125755897</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>92518</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523377</v>
+        <v>523669</v>
       </c>
       <c r="R77" t="n">
-        <v>6846085</v>
+        <v>6846274</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755852</v>
+        <v>125755862</v>
       </c>
       <c r="B78" t="n">
         <v>78968</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523420</v>
+        <v>523377</v>
       </c>
       <c r="R78" t="n">
-        <v>6846145</v>
+        <v>6846085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755883</v>
+        <v>125755852</v>
       </c>
       <c r="B79" t="n">
         <v>78968</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523485</v>
+        <v>523420</v>
       </c>
       <c r="R79" t="n">
-        <v>6846121</v>
+        <v>6846145</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755847</v>
+        <v>125755883</v>
       </c>
       <c r="B80" t="n">
         <v>78968</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523553</v>
+        <v>523485</v>
       </c>
       <c r="R80" t="n">
-        <v>6846192</v>
+        <v>6846121</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755841</v>
+        <v>125755847</v>
       </c>
       <c r="B81" t="n">
         <v>78968</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523605</v>
+        <v>523553</v>
       </c>
       <c r="R81" t="n">
-        <v>6846199</v>
+        <v>6846192</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755855</v>
+        <v>125755841</v>
       </c>
       <c r="B82" t="n">
         <v>78968</v>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523410</v>
+        <v>523605</v>
       </c>
       <c r="R82" t="n">
-        <v>6846095</v>
+        <v>6846199</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755858</v>
+        <v>125755855</v>
       </c>
       <c r="B83" t="n">
         <v>78968</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523393</v>
+        <v>523410</v>
       </c>
       <c r="R83" t="n">
         <v>6846095</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125740592</v>
+        <v>125755858</v>
       </c>
       <c r="B84" t="n">
         <v>78968</v>
@@ -8726,17 +8726,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523450</v>
+        <v>523393</v>
       </c>
       <c r="R84" t="n">
-        <v>6846113</v>
+        <v>6846095</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8780,12 +8780,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755807</v>
+        <v>125755824</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523379</v>
+        <v>523501</v>
       </c>
       <c r="R2" t="n">
-        <v>6846064</v>
+        <v>6846078</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755851</v>
+        <v>125740307</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523422</v>
+        <v>523527</v>
       </c>
       <c r="R3" t="n">
-        <v>6846155</v>
+        <v>6846185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125741230</v>
+        <v>125742098</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523475</v>
+        <v>523403</v>
       </c>
       <c r="R4" t="n">
-        <v>6846068</v>
+        <v>6846072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R5" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755824</v>
+        <v>125755851</v>
       </c>
       <c r="B6" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523501</v>
+        <v>523422</v>
       </c>
       <c r="R6" t="n">
-        <v>6846078</v>
+        <v>6846155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,48 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125740307</v>
+        <v>125755807</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523527</v>
+        <v>523379</v>
       </c>
       <c r="R7" t="n">
-        <v>6846185</v>
+        <v>6846064</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1250,12 +1250,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1364,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125740292</v>
+        <v>125755799</v>
       </c>
       <c r="B9" t="n">
-        <v>98251</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523521</v>
+        <v>523708</v>
       </c>
       <c r="R9" t="n">
-        <v>6846131</v>
+        <v>6846300</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,22 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125741174</v>
+        <v>125755818</v>
       </c>
       <c r="B10" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523475</v>
+        <v>523628</v>
       </c>
       <c r="R10" t="n">
-        <v>6846068</v>
+        <v>6846224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,22 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755799</v>
+        <v>125755896</v>
       </c>
       <c r="B11" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523708</v>
+        <v>523465</v>
       </c>
       <c r="R11" t="n">
-        <v>6846300</v>
+        <v>6846335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,48 +1655,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755896</v>
+        <v>125740292</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>98255</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523465</v>
+        <v>523521</v>
       </c>
       <c r="R12" t="n">
-        <v>6846335</v>
+        <v>6846131</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1740,22 +1740,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R13" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755818</v>
+        <v>125742564</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523628</v>
+        <v>523612</v>
       </c>
       <c r="R14" t="n">
-        <v>6846224</v>
+        <v>6846245</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,12 +1934,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
         <v>125755850</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>125755892</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,42 +2140,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755829</v>
+        <v>125755816</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2184,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523458</v>
+        <v>523620</v>
       </c>
       <c r="R17" t="n">
-        <v>6846108</v>
+        <v>6846303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,38 +2242,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755816</v>
+        <v>125755829</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523620</v>
+        <v>523458</v>
       </c>
       <c r="R18" t="n">
-        <v>6846303</v>
+        <v>6846108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,37 +2359,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R19" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2433,22 +2438,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B20" t="n">
-        <v>57648</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,42 +2461,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R20" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2535,12 +2535,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2550,7 +2550,7 @@
         <v>125742673</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755874</v>
+        <v>125755839</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523446</v>
+        <v>523537</v>
       </c>
       <c r="R22" t="n">
-        <v>6846093</v>
+        <v>6846261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755836</v>
+        <v>125755874</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523502</v>
+        <v>523446</v>
       </c>
       <c r="R23" t="n">
-        <v>6846299</v>
+        <v>6846093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755839</v>
+        <v>125755836</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523537</v>
+        <v>523502</v>
       </c>
       <c r="R24" t="n">
-        <v>6846261</v>
+        <v>6846299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>125741338</v>
       </c>
       <c r="B25" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,45 +3032,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755842</v>
+        <v>125742433</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523656</v>
+        <v>523403</v>
       </c>
       <c r="R26" t="n">
-        <v>6846239</v>
+        <v>6846072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,44 +3131,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755802</v>
+        <v>125755909</v>
       </c>
       <c r="B27" t="n">
-        <v>79586</v>
+        <v>91819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1179</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3164,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523478</v>
+        <v>523407</v>
       </c>
       <c r="R27" t="n">
-        <v>6846087</v>
+        <v>6846172</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755864</v>
+        <v>125755842</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3261,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523381</v>
+        <v>523656</v>
       </c>
       <c r="R28" t="n">
-        <v>6846064</v>
+        <v>6846239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,59 +3337,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125742433</v>
+        <v>125755864</v>
       </c>
       <c r="B29" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523403</v>
+        <v>523381</v>
       </c>
       <c r="R29" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,44 +3422,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755909</v>
+        <v>125755802</v>
       </c>
       <c r="B30" t="n">
-        <v>91815</v>
+        <v>79590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1179</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523407</v>
+        <v>523478</v>
       </c>
       <c r="R30" t="n">
-        <v>6846172</v>
+        <v>6846087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740942</v>
+        <v>125755877</v>
       </c>
       <c r="B31" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523475</v>
+        <v>523461</v>
       </c>
       <c r="R31" t="n">
-        <v>6846068</v>
+        <v>6846105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125740278</v>
+        <v>125755840</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523522</v>
+        <v>523595</v>
       </c>
       <c r="R32" t="n">
-        <v>6846208</v>
+        <v>6846194</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,22 +3713,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125742754</v>
+        <v>125755853</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523569</v>
+        <v>523425</v>
       </c>
       <c r="R33" t="n">
-        <v>6846303</v>
+        <v>6846130</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,22 +3810,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755877</v>
+        <v>125740278</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523461</v>
+        <v>523522</v>
       </c>
       <c r="R34" t="n">
-        <v>6846105</v>
+        <v>6846208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,22 +3907,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755853</v>
+        <v>125740942</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523425</v>
+        <v>523475</v>
       </c>
       <c r="R35" t="n">
-        <v>6846130</v>
+        <v>6846068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,22 +4004,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755840</v>
+        <v>125742754</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523595</v>
+        <v>523569</v>
       </c>
       <c r="R36" t="n">
-        <v>6846194</v>
+        <v>6846303</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,12 +4101,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
         <v>125755857</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>125755890</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>125740148</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755814</v>
+        <v>125740970</v>
       </c>
       <c r="B40" t="n">
-        <v>92710</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,34 +4415,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523456</v>
+        <v>523383</v>
       </c>
       <c r="R40" t="n">
-        <v>6846109</v>
+        <v>6846110</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4532,17 +4532,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R41" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4586,22 +4586,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755901</v>
+        <v>125755814</v>
       </c>
       <c r="B42" t="n">
-        <v>78635</v>
+        <v>92714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523588</v>
+        <v>523456</v>
       </c>
       <c r="R42" t="n">
-        <v>6846217</v>
+        <v>6846109</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4669,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,34 +4706,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R43" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4773,6 +4768,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4785,22 +4785,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125742499</v>
+        <v>125755881</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4828,17 +4828,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523622</v>
+        <v>523499</v>
       </c>
       <c r="R44" t="n">
-        <v>6846233</v>
+        <v>6846107</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4882,22 +4882,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755873</v>
+        <v>125740933</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,37 +4905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523443</v>
+        <v>523405</v>
       </c>
       <c r="R45" t="n">
-        <v>6846083</v>
+        <v>6846104</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,12 +4979,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4994,7 +4994,7 @@
         <v>125755833</v>
       </c>
       <c r="B46" t="n">
-        <v>91389</v>
+        <v>91393</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,54 +5088,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755831</v>
+        <v>125755873</v>
       </c>
       <c r="B47" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523491</v>
+        <v>523443</v>
       </c>
       <c r="R47" t="n">
-        <v>6846097</v>
+        <v>6846083</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5194,32 +5185,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755813</v>
+        <v>125755879</v>
       </c>
       <c r="B48" t="n">
-        <v>97212</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5229,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523458</v>
+        <v>523502</v>
       </c>
       <c r="R48" t="n">
-        <v>6846106</v>
+        <v>6846082</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5291,10 +5282,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125740933</v>
+        <v>125755848</v>
       </c>
       <c r="B49" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5302,37 +5293,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523405</v>
+        <v>523515</v>
       </c>
       <c r="R49" t="n">
-        <v>6846104</v>
+        <v>6846181</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5376,57 +5367,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755848</v>
+        <v>125755831</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523515</v>
+        <v>523491</v>
       </c>
       <c r="R50" t="n">
-        <v>6846181</v>
+        <v>6846097</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,32 +5485,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755879</v>
+        <v>125755813</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>97216</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523502</v>
+        <v>523458</v>
       </c>
       <c r="R51" t="n">
-        <v>6846082</v>
+        <v>6846106</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755859</v>
+        <v>125740194</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523396</v>
+        <v>523518</v>
       </c>
       <c r="R52" t="n">
-        <v>6846092</v>
+        <v>6846232</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,22 +5667,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755798</v>
+        <v>125742527</v>
       </c>
       <c r="B53" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5690,21 +5690,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523586</v>
+        <v>523403</v>
       </c>
       <c r="R53" t="n">
-        <v>6846194</v>
+        <v>6846072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,22 +5764,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755878</v>
+        <v>125755859</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523484</v>
+        <v>523396</v>
       </c>
       <c r="R54" t="n">
-        <v>6846075</v>
+        <v>6846092</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125740194</v>
+        <v>125755823</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523518</v>
+        <v>523377</v>
       </c>
       <c r="R55" t="n">
-        <v>6846232</v>
+        <v>6846073</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,22 +5958,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125742527</v>
+        <v>125755798</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523403</v>
+        <v>523586</v>
       </c>
       <c r="R56" t="n">
-        <v>6846072</v>
+        <v>6846194</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6055,22 +6055,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755823</v>
+        <v>125755878</v>
       </c>
       <c r="B57" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523377</v>
+        <v>523484</v>
       </c>
       <c r="R57" t="n">
-        <v>6846073</v>
+        <v>6846075</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6164,10 +6164,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755806</v>
+        <v>125740221</v>
       </c>
       <c r="B58" t="n">
-        <v>79000</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6175,37 +6175,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523381</v>
+        <v>523538</v>
       </c>
       <c r="R58" t="n">
-        <v>6846064</v>
+        <v>6846149</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6249,22 +6249,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755875</v>
+        <v>125755806</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>79004</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6272,21 +6272,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523436</v>
+        <v>523381</v>
       </c>
       <c r="R59" t="n">
-        <v>6846102</v>
+        <v>6846064</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6358,54 +6358,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B60" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R60" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6464,48 +6455,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125740221</v>
+        <v>125755828</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523538</v>
+        <v>523512</v>
       </c>
       <c r="R61" t="n">
-        <v>6846149</v>
+        <v>6846071</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6549,22 +6549,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755846</v>
+        <v>125740764</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523604</v>
+        <v>523443</v>
       </c>
       <c r="R62" t="n">
-        <v>6846240</v>
+        <v>6846070</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,22 +6646,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755796</v>
+        <v>125755846</v>
       </c>
       <c r="B63" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523627</v>
+        <v>523604</v>
       </c>
       <c r="R63" t="n">
-        <v>6846239</v>
+        <v>6846240</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6758,7 +6758,7 @@
         <v>125755863</v>
       </c>
       <c r="B64" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>125755854</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>125755880</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125740764</v>
+        <v>125755796</v>
       </c>
       <c r="B67" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523443</v>
+        <v>523627</v>
       </c>
       <c r="R67" t="n">
-        <v>6846070</v>
+        <v>6846239</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7146,7 +7146,7 @@
         <v>125755882</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>125755804</v>
       </c>
       <c r="B69" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>125755805</v>
       </c>
       <c r="B70" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>125740179</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>125755826</v>
       </c>
       <c r="B72" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>125755843</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>125755891</v>
       </c>
       <c r="B74" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>125755817</v>
       </c>
       <c r="B75" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>125740592</v>
       </c>
       <c r="B76" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8016,32 +8016,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755897</v>
+        <v>125755862</v>
       </c>
       <c r="B77" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523669</v>
+        <v>523377</v>
       </c>
       <c r="R77" t="n">
-        <v>6846274</v>
+        <v>6846085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755862</v>
+        <v>125755883</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523377</v>
+        <v>523485</v>
       </c>
       <c r="R78" t="n">
-        <v>6846085</v>
+        <v>6846121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R79" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,32 +8307,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755883</v>
+        <v>125755897</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523485</v>
+        <v>523669</v>
       </c>
       <c r="R80" t="n">
-        <v>6846121</v>
+        <v>6846274</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,10 +8404,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755847</v>
+        <v>125755852</v>
       </c>
       <c r="B81" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523553</v>
+        <v>523420</v>
       </c>
       <c r="R81" t="n">
-        <v>6846192</v>
+        <v>6846145</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8504,7 +8504,7 @@
         <v>125755841</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>125755855</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>125755858</v>
       </c>
       <c r="B84" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8792,32 +8792,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755837</v>
+        <v>125755898</v>
       </c>
       <c r="B85" t="n">
-        <v>78968</v>
+        <v>92522</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523530</v>
+        <v>523635</v>
       </c>
       <c r="R85" t="n">
-        <v>6846281</v>
+        <v>6846293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755827</v>
+        <v>125755888</v>
       </c>
       <c r="B86" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523501</v>
+        <v>523478</v>
       </c>
       <c r="R86" t="n">
-        <v>6846078</v>
+        <v>6846168</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8986,32 +8986,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755898</v>
+        <v>125755837</v>
       </c>
       <c r="B87" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523635</v>
+        <v>523530</v>
       </c>
       <c r="R87" t="n">
-        <v>6846293</v>
+        <v>6846281</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9083,10 +9083,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755888</v>
+        <v>125755827</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9094,21 +9094,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523478</v>
+        <v>523501</v>
       </c>
       <c r="R88" t="n">
-        <v>6846168</v>
+        <v>6846078</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9183,7 +9183,7 @@
         <v>125755886</v>
       </c>
       <c r="B89" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>125755889</v>
       </c>
       <c r="B90" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755885</v>
+        <v>125755905</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R91" t="n">
-        <v>6846151</v>
+        <v>6846102</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755825</v>
+        <v>125755904</v>
       </c>
       <c r="B92" t="n">
-        <v>78726</v>
+        <v>78639</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R92" t="n">
-        <v>6846224</v>
+        <v>6846179</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755905</v>
+        <v>125755825</v>
       </c>
       <c r="B93" t="n">
-        <v>78635</v>
+        <v>78730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R93" t="n">
-        <v>6846102</v>
+        <v>6846224</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B94" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R94" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B95" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R95" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9862,7 +9862,7 @@
         <v>125755849</v>
       </c>
       <c r="B96" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9956,10 +9956,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755884</v>
+        <v>125755834</v>
       </c>
       <c r="B97" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523471</v>
+        <v>523489</v>
       </c>
       <c r="R97" t="n">
-        <v>6846134</v>
+        <v>6846326</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10053,10 +10053,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755834</v>
+        <v>125755844</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523489</v>
+        <v>523705</v>
       </c>
       <c r="R98" t="n">
-        <v>6846326</v>
+        <v>6846300</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10150,10 +10150,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755844</v>
+        <v>125755845</v>
       </c>
       <c r="B99" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523705</v>
+        <v>523663</v>
       </c>
       <c r="R99" t="n">
-        <v>6846300</v>
+        <v>6846295</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10247,10 +10247,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755845</v>
+        <v>125755876</v>
       </c>
       <c r="B100" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523663</v>
+        <v>523457</v>
       </c>
       <c r="R100" t="n">
-        <v>6846295</v>
+        <v>6846106</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10344,10 +10344,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755876</v>
+        <v>125755861</v>
       </c>
       <c r="B101" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523457</v>
+        <v>523389</v>
       </c>
       <c r="R101" t="n">
-        <v>6846106</v>
+        <v>6846092</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755861</v>
+        <v>125755884</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523389</v>
+        <v>523471</v>
       </c>
       <c r="R102" t="n">
-        <v>6846092</v>
+        <v>6846134</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10541,7 +10541,7 @@
         <v>125742574</v>
       </c>
       <c r="B103" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755820</v>
+        <v>125755903</v>
       </c>
       <c r="B104" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523410</v>
+        <v>523586</v>
       </c>
       <c r="R104" t="n">
-        <v>6846112</v>
+        <v>6846193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10732,10 +10732,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B105" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,21 +10743,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R105" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10829,10 +10829,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755887</v>
+        <v>125755820</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,21 +10840,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10864,10 +10864,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523473</v>
+        <v>523410</v>
       </c>
       <c r="R106" t="n">
-        <v>6846157</v>
+        <v>6846112</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755824</v>
+        <v>125740307</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523501</v>
+        <v>523527</v>
       </c>
       <c r="R2" t="n">
-        <v>6846078</v>
+        <v>6846185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125740307</v>
+        <v>125742098</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523527</v>
+        <v>523403</v>
       </c>
       <c r="R3" t="n">
-        <v>6846185</v>
+        <v>6846072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R4" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,48 +966,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125741230</v>
+        <v>125755807</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523475</v>
+        <v>523379</v>
       </c>
       <c r="R5" t="n">
-        <v>6846068</v>
+        <v>6846064</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755807</v>
+        <v>125755815</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,27 +1176,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1200,13 +1205,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523379</v>
+        <v>523605</v>
       </c>
       <c r="R7" t="n">
-        <v>6846064</v>
+        <v>6846199</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1262,50 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755815</v>
+        <v>125755824</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523605</v>
+        <v>523501</v>
       </c>
       <c r="R8" t="n">
-        <v>6846199</v>
+        <v>6846078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755799</v>
+        <v>125755818</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523708</v>
+        <v>523628</v>
       </c>
       <c r="R9" t="n">
-        <v>6846300</v>
+        <v>6846224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R10" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755896</v>
+        <v>125755799</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523465</v>
+        <v>523708</v>
       </c>
       <c r="R11" t="n">
-        <v>6846335</v>
+        <v>6846300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,48 +1655,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125740292</v>
+        <v>125741174</v>
       </c>
       <c r="B12" t="n">
-        <v>98255</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523521</v>
+        <v>523475</v>
       </c>
       <c r="R12" t="n">
-        <v>6846131</v>
+        <v>6846068</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1740,60 +1740,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125741174</v>
+        <v>125740292</v>
       </c>
       <c r="B13" t="n">
-        <v>78731</v>
+        <v>98255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523475</v>
+        <v>523521</v>
       </c>
       <c r="R13" t="n">
-        <v>6846068</v>
+        <v>6846131</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1837,12 +1837,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755877</v>
+        <v>125740278</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523461</v>
+        <v>523522</v>
       </c>
       <c r="R31" t="n">
-        <v>6846105</v>
+        <v>6846208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755840</v>
+        <v>125740942</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523595</v>
+        <v>523475</v>
       </c>
       <c r="R32" t="n">
-        <v>6846194</v>
+        <v>6846068</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,19 +3713,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755853</v>
+        <v>125742754</v>
       </c>
       <c r="B33" t="n">
         <v>78972</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523425</v>
+        <v>523569</v>
       </c>
       <c r="R33" t="n">
-        <v>6846130</v>
+        <v>6846303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,19 +3810,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125740278</v>
+        <v>125755853</v>
       </c>
       <c r="B34" t="n">
         <v>78972</v>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523522</v>
+        <v>523425</v>
       </c>
       <c r="R34" t="n">
-        <v>6846208</v>
+        <v>6846130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,22 +3907,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125740942</v>
+        <v>125755877</v>
       </c>
       <c r="B35" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523475</v>
+        <v>523461</v>
       </c>
       <c r="R35" t="n">
-        <v>6846068</v>
+        <v>6846105</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,19 +4004,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125742754</v>
+        <v>125755840</v>
       </c>
       <c r="B36" t="n">
         <v>78972</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523569</v>
+        <v>523595</v>
       </c>
       <c r="R36" t="n">
-        <v>6846303</v>
+        <v>6846194</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,19 +4101,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755857</v>
+        <v>125740148</v>
       </c>
       <c r="B37" t="n">
         <v>78972</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523398</v>
+        <v>523497</v>
       </c>
       <c r="R37" t="n">
-        <v>6846095</v>
+        <v>6846271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,19 +4198,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755890</v>
+        <v>125755857</v>
       </c>
       <c r="B38" t="n">
         <v>78972</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523496</v>
+        <v>523398</v>
       </c>
       <c r="R38" t="n">
-        <v>6846308</v>
+        <v>6846095</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125740148</v>
+        <v>125755890</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523497</v>
+        <v>523496</v>
       </c>
       <c r="R39" t="n">
-        <v>6846271</v>
+        <v>6846308</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,12 +4392,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6164,48 +6164,57 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125740221</v>
+        <v>125755828</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>98338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523538</v>
+        <v>523512</v>
       </c>
       <c r="R58" t="n">
-        <v>6846149</v>
+        <v>6846071</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6249,22 +6258,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755806</v>
+        <v>125740221</v>
       </c>
       <c r="B59" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6272,37 +6281,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523381</v>
+        <v>523538</v>
       </c>
       <c r="R59" t="n">
-        <v>6846064</v>
+        <v>6846149</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6346,22 +6355,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755875</v>
+        <v>125755806</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6369,21 +6378,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6393,10 +6402,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523436</v>
+        <v>523381</v>
       </c>
       <c r="R60" t="n">
-        <v>6846102</v>
+        <v>6846064</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6455,54 +6464,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R61" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7919,48 +7919,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125740592</v>
+        <v>125755897</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523450</v>
+        <v>523669</v>
       </c>
       <c r="R76" t="n">
-        <v>6846113</v>
+        <v>6846274</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,19 +8004,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755862</v>
+        <v>125755852</v>
       </c>
       <c r="B77" t="n">
         <v>78972</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523377</v>
+        <v>523420</v>
       </c>
       <c r="R77" t="n">
-        <v>6846085</v>
+        <v>6846145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755883</v>
+        <v>125755841</v>
       </c>
       <c r="B78" t="n">
         <v>78972</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523485</v>
+        <v>523605</v>
       </c>
       <c r="R78" t="n">
-        <v>6846121</v>
+        <v>6846199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755847</v>
+        <v>125755855</v>
       </c>
       <c r="B79" t="n">
         <v>78972</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523553</v>
+        <v>523410</v>
       </c>
       <c r="R79" t="n">
-        <v>6846192</v>
+        <v>6846095</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,32 +8307,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755897</v>
+        <v>125755858</v>
       </c>
       <c r="B80" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523669</v>
+        <v>523393</v>
       </c>
       <c r="R80" t="n">
-        <v>6846274</v>
+        <v>6846095</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755852</v>
+        <v>125740592</v>
       </c>
       <c r="B81" t="n">
         <v>78972</v>
@@ -8435,17 +8435,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523420</v>
+        <v>523450</v>
       </c>
       <c r="R81" t="n">
-        <v>6846145</v>
+        <v>6846113</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8489,19 +8489,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755841</v>
+        <v>125755862</v>
       </c>
       <c r="B82" t="n">
         <v>78972</v>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523605</v>
+        <v>523377</v>
       </c>
       <c r="R82" t="n">
-        <v>6846199</v>
+        <v>6846085</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755855</v>
+        <v>125755883</v>
       </c>
       <c r="B83" t="n">
         <v>78972</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523410</v>
+        <v>523485</v>
       </c>
       <c r="R83" t="n">
-        <v>6846095</v>
+        <v>6846121</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755858</v>
+        <v>125755847</v>
       </c>
       <c r="B84" t="n">
         <v>78972</v>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523393</v>
+        <v>523553</v>
       </c>
       <c r="R84" t="n">
-        <v>6846095</v>
+        <v>6846192</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10538,10 +10538,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125742574</v>
+        <v>125755903</v>
       </c>
       <c r="B103" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10549,37 +10549,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523592</v>
+        <v>523586</v>
       </c>
       <c r="R103" t="n">
-        <v>6846248</v>
+        <v>6846193</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10623,22 +10623,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755903</v>
+        <v>125755820</v>
       </c>
       <c r="B104" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523586</v>
+        <v>523410</v>
       </c>
       <c r="R104" t="n">
-        <v>6846193</v>
+        <v>6846112</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10829,10 +10829,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755820</v>
+        <v>125742574</v>
       </c>
       <c r="B106" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,37 +10840,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523410</v>
+        <v>523592</v>
       </c>
       <c r="R106" t="n">
-        <v>6846112</v>
+        <v>6846248</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125740307</v>
+        <v>125755851</v>
       </c>
       <c r="B2" t="n">
         <v>78972</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523527</v>
+        <v>523422</v>
       </c>
       <c r="R2" t="n">
-        <v>6846185</v>
+        <v>6846155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125742098</v>
+        <v>125755807</v>
       </c>
       <c r="B3" t="n">
-        <v>79590</v>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523403</v>
+        <v>523379</v>
       </c>
       <c r="R3" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,57 +862,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125741230</v>
+        <v>125755815</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523475</v>
+        <v>523605</v>
       </c>
       <c r="R4" t="n">
-        <v>6846068</v>
+        <v>6846199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,65 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755807</v>
+        <v>125755824</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523379</v>
+        <v>523501</v>
       </c>
       <c r="R5" t="n">
-        <v>6846064</v>
+        <v>6846078</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755851</v>
+        <v>125740330</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523422</v>
+        <v>523527</v>
       </c>
       <c r="R6" t="n">
-        <v>6846155</v>
+        <v>6846185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,62 +1158,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755815</v>
+        <v>125741230</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523605</v>
+        <v>523475</v>
       </c>
       <c r="R7" t="n">
-        <v>6846199</v>
+        <v>6846068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755824</v>
+        <v>125742098</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523501</v>
+        <v>523403</v>
       </c>
       <c r="R8" t="n">
-        <v>6846078</v>
+        <v>6846072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755818</v>
+        <v>125755799</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523628</v>
+        <v>523708</v>
       </c>
       <c r="R9" t="n">
-        <v>6846224</v>
+        <v>6846300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755799</v>
+        <v>125755818</v>
       </c>
       <c r="B11" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523708</v>
+        <v>523628</v>
       </c>
       <c r="R11" t="n">
-        <v>6846300</v>
+        <v>6846224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125741174</v>
+        <v>125742564</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523475</v>
+        <v>523612</v>
       </c>
       <c r="R12" t="n">
-        <v>6846068</v>
+        <v>6846245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
         <v>125740292</v>
       </c>
       <c r="B13" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R14" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>125755829</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R23" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755836</v>
+        <v>125755874</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523502</v>
+        <v>523446</v>
       </c>
       <c r="R24" t="n">
-        <v>6846299</v>
+        <v>6846093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125741338</v>
+        <v>125755802</v>
       </c>
       <c r="B25" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523403</v>
+        <v>523478</v>
       </c>
       <c r="R25" t="n">
-        <v>6846072</v>
+        <v>6846087</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,71 +3020,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125742433</v>
+        <v>125755842</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523403</v>
+        <v>523656</v>
       </c>
       <c r="R26" t="n">
-        <v>6846072</v>
+        <v>6846239</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,12 +3117,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3240,7 +3226,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755842</v>
+        <v>125755864</v>
       </c>
       <c r="B28" t="n">
         <v>78972</v>
@@ -3275,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523656</v>
+        <v>523381</v>
       </c>
       <c r="R28" t="n">
-        <v>6846239</v>
+        <v>6846064</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,45 +3323,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755864</v>
+        <v>125742433</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>56843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523381</v>
+        <v>523403</v>
       </c>
       <c r="R29" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,22 +3422,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755802</v>
+        <v>125741338</v>
       </c>
       <c r="B30" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523478</v>
+        <v>523403</v>
       </c>
       <c r="R30" t="n">
-        <v>6846087</v>
+        <v>6846072</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3519,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740278</v>
+        <v>125755877</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523522</v>
+        <v>523461</v>
       </c>
       <c r="R31" t="n">
-        <v>6846208</v>
+        <v>6846105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125740942</v>
+        <v>125755853</v>
       </c>
       <c r="B32" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523475</v>
+        <v>523425</v>
       </c>
       <c r="R32" t="n">
-        <v>6846068</v>
+        <v>6846130</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,19 +3713,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125742754</v>
+        <v>125755840</v>
       </c>
       <c r="B33" t="n">
         <v>78972</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523569</v>
+        <v>523595</v>
       </c>
       <c r="R33" t="n">
-        <v>6846303</v>
+        <v>6846194</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,19 +3810,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755853</v>
+        <v>125742754</v>
       </c>
       <c r="B34" t="n">
         <v>78972</v>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523425</v>
+        <v>523569</v>
       </c>
       <c r="R34" t="n">
-        <v>6846130</v>
+        <v>6846303</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,19 +3907,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755877</v>
+        <v>125740278</v>
       </c>
       <c r="B35" t="n">
         <v>78972</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523461</v>
+        <v>523522</v>
       </c>
       <c r="R35" t="n">
-        <v>6846105</v>
+        <v>6846208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,22 +4004,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755840</v>
+        <v>125740942</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523595</v>
+        <v>523475</v>
       </c>
       <c r="R36" t="n">
-        <v>6846194</v>
+        <v>6846068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,19 +4101,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125740148</v>
+        <v>125755857</v>
       </c>
       <c r="B37" t="n">
         <v>78972</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523497</v>
+        <v>523398</v>
       </c>
       <c r="R37" t="n">
-        <v>6846271</v>
+        <v>6846095</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,19 +4198,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755857</v>
+        <v>125755890</v>
       </c>
       <c r="B38" t="n">
         <v>78972</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523398</v>
+        <v>523496</v>
       </c>
       <c r="R38" t="n">
-        <v>6846095</v>
+        <v>6846308</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755890</v>
+        <v>125740148</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523496</v>
+        <v>523497</v>
       </c>
       <c r="R39" t="n">
-        <v>6846308</v>
+        <v>6846271</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,19 +4392,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125740970</v>
+        <v>125755881</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4435,14 +4435,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523383</v>
+        <v>523499</v>
       </c>
       <c r="R40" t="n">
-        <v>6846110</v>
+        <v>6846107</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,37 +4512,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R41" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4572,6 +4572,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4586,12 +4591,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4695,10 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755901</v>
+        <v>125740970</v>
       </c>
       <c r="B43" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,34 +4711,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523588</v>
+        <v>523383</v>
       </c>
       <c r="R43" t="n">
-        <v>6846217</v>
+        <v>6846110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4768,11 +4773,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4785,19 +4785,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4828,17 +4828,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R44" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4882,22 +4882,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125740933</v>
+        <v>125755873</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,37 +4905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523405</v>
+        <v>523443</v>
       </c>
       <c r="R45" t="n">
-        <v>6846104</v>
+        <v>6846083</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,12 +4979,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755873</v>
+        <v>125755879</v>
       </c>
       <c r="B47" t="n">
         <v>78972</v>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523443</v>
+        <v>523502</v>
       </c>
       <c r="R47" t="n">
-        <v>6846083</v>
+        <v>6846082</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,45 +5185,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755879</v>
+        <v>125755831</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523502</v>
+        <v>523491</v>
       </c>
       <c r="R48" t="n">
-        <v>6846082</v>
+        <v>6846097</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5282,32 +5291,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755848</v>
+        <v>125755813</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>97217</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5317,10 +5326,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523515</v>
+        <v>523458</v>
       </c>
       <c r="R49" t="n">
-        <v>6846181</v>
+        <v>6846106</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5379,54 +5388,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755831</v>
+        <v>125755848</v>
       </c>
       <c r="B50" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523491</v>
+        <v>523515</v>
       </c>
       <c r="R50" t="n">
-        <v>6846097</v>
+        <v>6846181</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,48 +5485,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755813</v>
+        <v>125740933</v>
       </c>
       <c r="B51" t="n">
-        <v>97216</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523458</v>
+        <v>523405</v>
       </c>
       <c r="R51" t="n">
-        <v>6846106</v>
+        <v>6846104</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,22 +5570,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125740194</v>
+        <v>125755798</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523518</v>
+        <v>523586</v>
       </c>
       <c r="R52" t="n">
-        <v>6846232</v>
+        <v>6846194</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125742527</v>
+        <v>125755859</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523403</v>
+        <v>523396</v>
       </c>
       <c r="R53" t="n">
-        <v>6846072</v>
+        <v>6846092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,19 +5764,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B54" t="n">
         <v>78972</v>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R54" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755798</v>
+        <v>125740194</v>
       </c>
       <c r="B56" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523586</v>
+        <v>523518</v>
       </c>
       <c r="R56" t="n">
-        <v>6846194</v>
+        <v>6846232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6055,19 +6055,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755878</v>
+        <v>125742527</v>
       </c>
       <c r="B57" t="n">
         <v>78972</v>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523484</v>
+        <v>523403</v>
       </c>
       <c r="R57" t="n">
-        <v>6846075</v>
+        <v>6846072</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6152,66 +6152,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B58" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R58" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6270,7 +6261,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125740221</v>
+        <v>125755875</v>
       </c>
       <c r="B59" t="n">
         <v>78972</v>
@@ -6301,17 +6292,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523538</v>
+        <v>523436</v>
       </c>
       <c r="R59" t="n">
-        <v>6846149</v>
+        <v>6846102</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6355,22 +6346,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755806</v>
+        <v>125740221</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6378,37 +6369,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523381</v>
+        <v>523538</v>
       </c>
       <c r="R60" t="n">
-        <v>6846064</v>
+        <v>6846149</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6452,57 +6443,66 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R61" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125740764</v>
+        <v>125755846</v>
       </c>
       <c r="B62" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523443</v>
+        <v>523604</v>
       </c>
       <c r="R62" t="n">
-        <v>6846070</v>
+        <v>6846240</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,19 +6646,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755846</v>
+        <v>125755863</v>
       </c>
       <c r="B63" t="n">
         <v>78972</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523604</v>
+        <v>523376</v>
       </c>
       <c r="R63" t="n">
-        <v>6846240</v>
+        <v>6846074</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755863</v>
+        <v>125755854</v>
       </c>
       <c r="B64" t="n">
         <v>78972</v>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523376</v>
+        <v>523410</v>
       </c>
       <c r="R64" t="n">
-        <v>6846074</v>
+        <v>6846112</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755854</v>
+        <v>125755880</v>
       </c>
       <c r="B65" t="n">
         <v>78972</v>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523410</v>
+        <v>523488</v>
       </c>
       <c r="R65" t="n">
-        <v>6846112</v>
+        <v>6846089</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755880</v>
+        <v>125755796</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523488</v>
+        <v>523627</v>
       </c>
       <c r="R66" t="n">
-        <v>6846089</v>
+        <v>6846239</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755796</v>
+        <v>125740764</v>
       </c>
       <c r="B67" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523627</v>
+        <v>523443</v>
       </c>
       <c r="R67" t="n">
-        <v>6846239</v>
+        <v>6846070</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,22 +7131,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755882</v>
+        <v>125755805</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523515</v>
+        <v>523478</v>
       </c>
       <c r="R68" t="n">
-        <v>6846106</v>
+        <v>6846168</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,10 +7337,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755805</v>
+        <v>125755882</v>
       </c>
       <c r="B70" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7348,21 +7348,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523478</v>
+        <v>523515</v>
       </c>
       <c r="R70" t="n">
-        <v>6846168</v>
+        <v>6846106</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B73" t="n">
         <v>78972</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R73" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755891</v>
+        <v>125755817</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7736,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523501</v>
+        <v>523587</v>
       </c>
       <c r="R74" t="n">
-        <v>6846327</v>
+        <v>6846194</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755817</v>
+        <v>125755843</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7833,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523587</v>
+        <v>523662</v>
       </c>
       <c r="R75" t="n">
-        <v>6846194</v>
+        <v>6846272</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7919,48 +7919,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755897</v>
+        <v>125740592</v>
       </c>
       <c r="B76" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523669</v>
+        <v>523450</v>
       </c>
       <c r="R76" t="n">
-        <v>6846274</v>
+        <v>6846113</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,44 +8004,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755852</v>
+        <v>125755897</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523420</v>
+        <v>523669</v>
       </c>
       <c r="R77" t="n">
-        <v>6846145</v>
+        <v>6846274</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755841</v>
+        <v>125755862</v>
       </c>
       <c r="B78" t="n">
         <v>78972</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523605</v>
+        <v>523377</v>
       </c>
       <c r="R78" t="n">
-        <v>6846199</v>
+        <v>6846085</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755855</v>
+        <v>125755852</v>
       </c>
       <c r="B79" t="n">
         <v>78972</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523410</v>
+        <v>523420</v>
       </c>
       <c r="R79" t="n">
-        <v>6846095</v>
+        <v>6846145</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755858</v>
+        <v>125755883</v>
       </c>
       <c r="B80" t="n">
         <v>78972</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523393</v>
+        <v>523485</v>
       </c>
       <c r="R80" t="n">
-        <v>6846095</v>
+        <v>6846121</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125740592</v>
+        <v>125755847</v>
       </c>
       <c r="B81" t="n">
         <v>78972</v>
@@ -8435,17 +8435,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523450</v>
+        <v>523553</v>
       </c>
       <c r="R81" t="n">
-        <v>6846113</v>
+        <v>6846192</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8489,19 +8489,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755862</v>
+        <v>125755841</v>
       </c>
       <c r="B82" t="n">
         <v>78972</v>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523377</v>
+        <v>523605</v>
       </c>
       <c r="R82" t="n">
-        <v>6846085</v>
+        <v>6846199</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755883</v>
+        <v>125755855</v>
       </c>
       <c r="B83" t="n">
         <v>78972</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523485</v>
+        <v>523410</v>
       </c>
       <c r="R83" t="n">
-        <v>6846121</v>
+        <v>6846095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755847</v>
+        <v>125755858</v>
       </c>
       <c r="B84" t="n">
         <v>78972</v>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523553</v>
+        <v>523393</v>
       </c>
       <c r="R84" t="n">
-        <v>6846192</v>
+        <v>6846095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8792,32 +8792,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755898</v>
+        <v>125755827</v>
       </c>
       <c r="B85" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523635</v>
+        <v>523501</v>
       </c>
       <c r="R85" t="n">
-        <v>6846293</v>
+        <v>6846078</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8889,7 +8889,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755888</v>
+        <v>125755837</v>
       </c>
       <c r="B86" t="n">
         <v>78972</v>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523478</v>
+        <v>523530</v>
       </c>
       <c r="R86" t="n">
-        <v>6846168</v>
+        <v>6846281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8986,32 +8986,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755837</v>
+        <v>125755898</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523530</v>
+        <v>523635</v>
       </c>
       <c r="R87" t="n">
-        <v>6846281</v>
+        <v>6846293</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9083,10 +9083,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755827</v>
+        <v>125755888</v>
       </c>
       <c r="B88" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9094,21 +9094,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523501</v>
+        <v>523478</v>
       </c>
       <c r="R88" t="n">
-        <v>6846078</v>
+        <v>6846168</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755825</v>
+        <v>125755819</v>
       </c>
       <c r="B93" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9606,7 +9606,7 @@
         <v>523628</v>
       </c>
       <c r="R93" t="n">
-        <v>6846224</v>
+        <v>6846238</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755819</v>
+        <v>125755825</v>
       </c>
       <c r="B94" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9703,7 +9703,7 @@
         <v>523628</v>
       </c>
       <c r="R94" t="n">
-        <v>6846238</v>
+        <v>6846224</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9859,7 +9859,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755849</v>
+        <v>125755884</v>
       </c>
       <c r="B96" t="n">
         <v>78972</v>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523414</v>
+        <v>523471</v>
       </c>
       <c r="R96" t="n">
-        <v>6846169</v>
+        <v>6846134</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755834</v>
+        <v>125755849</v>
       </c>
       <c r="B97" t="n">
         <v>78972</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523489</v>
+        <v>523414</v>
       </c>
       <c r="R97" t="n">
-        <v>6846326</v>
+        <v>6846169</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755844</v>
+        <v>125755834</v>
       </c>
       <c r="B98" t="n">
         <v>78972</v>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523705</v>
+        <v>523489</v>
       </c>
       <c r="R98" t="n">
-        <v>6846300</v>
+        <v>6846326</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755845</v>
+        <v>125755844</v>
       </c>
       <c r="B99" t="n">
         <v>78972</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523663</v>
+        <v>523705</v>
       </c>
       <c r="R99" t="n">
-        <v>6846295</v>
+        <v>6846300</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10247,7 +10247,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755876</v>
+        <v>125755845</v>
       </c>
       <c r="B100" t="n">
         <v>78972</v>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523457</v>
+        <v>523663</v>
       </c>
       <c r="R100" t="n">
-        <v>6846106</v>
+        <v>6846295</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755861</v>
+        <v>125755876</v>
       </c>
       <c r="B101" t="n">
         <v>78972</v>
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523389</v>
+        <v>523457</v>
       </c>
       <c r="R101" t="n">
-        <v>6846092</v>
+        <v>6846106</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755884</v>
+        <v>125755861</v>
       </c>
       <c r="B102" t="n">
         <v>78972</v>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523471</v>
+        <v>523389</v>
       </c>
       <c r="R102" t="n">
-        <v>6846134</v>
+        <v>6846092</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755820</v>
+        <v>125755887</v>
       </c>
       <c r="B104" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523410</v>
+        <v>523473</v>
       </c>
       <c r="R104" t="n">
-        <v>6846112</v>
+        <v>6846157</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10732,10 +10732,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755887</v>
+        <v>125755820</v>
       </c>
       <c r="B105" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,21 +10743,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523473</v>
+        <v>523410</v>
       </c>
       <c r="R105" t="n">
-        <v>6846157</v>
+        <v>6846112</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755896</v>
+        <v>125755818</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523465</v>
+        <v>523628</v>
       </c>
       <c r="R10" t="n">
-        <v>6846335</v>
+        <v>6846224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R11" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -6358,48 +6358,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125740221</v>
+        <v>125755828</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523538</v>
+        <v>523512</v>
       </c>
       <c r="R60" t="n">
-        <v>6846149</v>
+        <v>6846071</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6443,69 +6452,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755828</v>
+        <v>125740221</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523512</v>
+        <v>523538</v>
       </c>
       <c r="R61" t="n">
-        <v>6846071</v>
+        <v>6846149</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6549,12 +6549,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755807</v>
+        <v>125755815</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,27 +783,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523379</v>
+        <v>523605</v>
       </c>
       <c r="R3" t="n">
-        <v>6846064</v>
+        <v>6846199</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755815</v>
+        <v>125755807</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,27 +885,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523605</v>
+        <v>523379</v>
       </c>
       <c r="R4" t="n">
-        <v>6846199</v>
+        <v>6846064</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R10" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755896</v>
+        <v>125755818</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523465</v>
+        <v>523628</v>
       </c>
       <c r="R11" t="n">
-        <v>6846335</v>
+        <v>6846224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1946,45 +1946,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755850</v>
+        <v>125755829</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523417</v>
+        <v>523458</v>
       </c>
       <c r="R15" t="n">
-        <v>6846164</v>
+        <v>6846108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2043,7 +2052,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755892</v>
+        <v>125755850</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2078,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523495</v>
+        <v>523417</v>
       </c>
       <c r="R16" t="n">
-        <v>6846328</v>
+        <v>6846164</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,50 +2149,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755816</v>
+        <v>125755892</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523620</v>
+        <v>523495</v>
       </c>
       <c r="R17" t="n">
-        <v>6846303</v>
+        <v>6846328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,42 +2246,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755829</v>
+        <v>125755816</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523458</v>
+        <v>523620</v>
       </c>
       <c r="R18" t="n">
-        <v>6846108</v>
+        <v>6846303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755839</v>
+        <v>125755874</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523537</v>
+        <v>523446</v>
       </c>
       <c r="R22" t="n">
-        <v>6846261</v>
+        <v>6846093</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755836</v>
+        <v>125755839</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523502</v>
+        <v>523537</v>
       </c>
       <c r="R23" t="n">
-        <v>6846299</v>
+        <v>6846261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R24" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755873</v>
+        <v>125740933</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,37 +4905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523443</v>
+        <v>523405</v>
       </c>
       <c r="R45" t="n">
-        <v>6846083</v>
+        <v>6846104</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,44 +4979,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755833</v>
+        <v>125755873</v>
       </c>
       <c r="B46" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523511</v>
+        <v>523443</v>
       </c>
       <c r="R46" t="n">
-        <v>6846118</v>
+        <v>6846083</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755879</v>
+        <v>125755848</v>
       </c>
       <c r="B47" t="n">
         <v>78972</v>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523502</v>
+        <v>523515</v>
       </c>
       <c r="R47" t="n">
-        <v>6846082</v>
+        <v>6846181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5388,32 +5388,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755848</v>
+        <v>125755833</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523515</v>
+        <v>523511</v>
       </c>
       <c r="R50" t="n">
-        <v>6846181</v>
+        <v>6846118</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125740933</v>
+        <v>125755879</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5496,37 +5496,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523405</v>
+        <v>523502</v>
       </c>
       <c r="R51" t="n">
-        <v>6846104</v>
+        <v>6846082</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,12 +5570,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6164,10 +6164,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755806</v>
+        <v>125755875</v>
       </c>
       <c r="B58" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6175,21 +6175,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523381</v>
+        <v>523436</v>
       </c>
       <c r="R58" t="n">
-        <v>6846064</v>
+        <v>6846102</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6261,45 +6261,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R59" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6358,54 +6367,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B60" t="n">
-        <v>98339</v>
+        <v>79004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R60" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755846</v>
+        <v>125755796</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,21 +6572,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523604</v>
+        <v>523627</v>
       </c>
       <c r="R62" t="n">
-        <v>6846240</v>
+        <v>6846239</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755863</v>
+        <v>125755846</v>
       </c>
       <c r="B63" t="n">
         <v>78972</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523376</v>
+        <v>523604</v>
       </c>
       <c r="R63" t="n">
-        <v>6846074</v>
+        <v>6846240</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B64" t="n">
         <v>78972</v>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R64" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755880</v>
+        <v>125755854</v>
       </c>
       <c r="B65" t="n">
         <v>78972</v>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523488</v>
+        <v>523410</v>
       </c>
       <c r="R65" t="n">
-        <v>6846089</v>
+        <v>6846112</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755796</v>
+        <v>125755880</v>
       </c>
       <c r="B66" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523627</v>
+        <v>523488</v>
       </c>
       <c r="R66" t="n">
-        <v>6846239</v>
+        <v>6846089</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B72" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R72" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755891</v>
+        <v>125755826</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523501</v>
+        <v>523408</v>
       </c>
       <c r="R73" t="n">
-        <v>6846327</v>
+        <v>6846116</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7736,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R74" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755843</v>
+        <v>125755817</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7833,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523662</v>
+        <v>523587</v>
       </c>
       <c r="R75" t="n">
-        <v>6846272</v>
+        <v>6846194</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7919,48 +7919,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125740592</v>
+        <v>125755897</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523450</v>
+        <v>523669</v>
       </c>
       <c r="R76" t="n">
-        <v>6846113</v>
+        <v>6846274</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8004,44 +8004,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755897</v>
+        <v>125755852</v>
       </c>
       <c r="B77" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523669</v>
+        <v>523420</v>
       </c>
       <c r="R77" t="n">
-        <v>6846274</v>
+        <v>6846145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755862</v>
+        <v>125755883</v>
       </c>
       <c r="B78" t="n">
         <v>78972</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523377</v>
+        <v>523485</v>
       </c>
       <c r="R78" t="n">
-        <v>6846085</v>
+        <v>6846121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B79" t="n">
         <v>78972</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R79" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755883</v>
+        <v>125755855</v>
       </c>
       <c r="B80" t="n">
         <v>78972</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523485</v>
+        <v>523410</v>
       </c>
       <c r="R80" t="n">
-        <v>6846121</v>
+        <v>6846095</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755847</v>
+        <v>125755858</v>
       </c>
       <c r="B81" t="n">
         <v>78972</v>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523553</v>
+        <v>523393</v>
       </c>
       <c r="R81" t="n">
-        <v>6846192</v>
+        <v>6846095</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755841</v>
+        <v>125740592</v>
       </c>
       <c r="B82" t="n">
         <v>78972</v>
@@ -8532,17 +8532,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523605</v>
+        <v>523450</v>
       </c>
       <c r="R82" t="n">
-        <v>6846199</v>
+        <v>6846113</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8586,19 +8586,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755855</v>
+        <v>125755862</v>
       </c>
       <c r="B83" t="n">
         <v>78972</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523410</v>
+        <v>523377</v>
       </c>
       <c r="R83" t="n">
-        <v>6846095</v>
+        <v>6846085</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755858</v>
+        <v>125755841</v>
       </c>
       <c r="B84" t="n">
         <v>78972</v>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523393</v>
+        <v>523605</v>
       </c>
       <c r="R84" t="n">
-        <v>6846095</v>
+        <v>6846199</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755851</v>
+        <v>125755807</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523422</v>
+        <v>523379</v>
       </c>
       <c r="R2" t="n">
-        <v>6846155</v>
+        <v>6846064</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755815</v>
+        <v>125755824</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523605</v>
+        <v>523501</v>
       </c>
       <c r="R3" t="n">
-        <v>6846199</v>
+        <v>6846078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,53 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755807</v>
+        <v>125755851</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523379</v>
+        <v>523422</v>
       </c>
       <c r="R4" t="n">
-        <v>6846064</v>
+        <v>6846155</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755824</v>
+        <v>125742098</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523501</v>
+        <v>523403</v>
       </c>
       <c r="R5" t="n">
-        <v>6846078</v>
+        <v>6846072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,57 +1056,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125740330</v>
+        <v>125755815</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523527</v>
+        <v>523605</v>
       </c>
       <c r="R6" t="n">
-        <v>6846185</v>
+        <v>6846199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125741230</v>
+        <v>125740330</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523475</v>
+        <v>523527</v>
       </c>
       <c r="R7" t="n">
-        <v>6846068</v>
+        <v>6846185</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B8" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R8" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755799</v>
+        <v>125755896</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523708</v>
+        <v>523465</v>
       </c>
       <c r="R9" t="n">
-        <v>6846300</v>
+        <v>6846335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755896</v>
+        <v>125755799</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523465</v>
+        <v>523708</v>
       </c>
       <c r="R10" t="n">
-        <v>6846335</v>
+        <v>6846300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755818</v>
+        <v>125742564</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523628</v>
+        <v>523612</v>
       </c>
       <c r="R11" t="n">
-        <v>6846224</v>
+        <v>6846245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125742564</v>
+        <v>125755818</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523612</v>
+        <v>523628</v>
       </c>
       <c r="R12" t="n">
-        <v>6846245</v>
+        <v>6846224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,12 +1740,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
         <v>125740292</v>
       </c>
       <c r="B13" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>125741174</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,54 +1946,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755829</v>
+        <v>125755850</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523458</v>
+        <v>523417</v>
       </c>
       <c r="R15" t="n">
-        <v>6846108</v>
+        <v>6846164</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755850</v>
+        <v>125755892</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2087,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523417</v>
+        <v>523495</v>
       </c>
       <c r="R16" t="n">
-        <v>6846164</v>
+        <v>6846328</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,45 +2140,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755892</v>
+        <v>125755816</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523495</v>
+        <v>523620</v>
       </c>
       <c r="R17" t="n">
-        <v>6846328</v>
+        <v>6846303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,38 +2242,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755816</v>
+        <v>125755829</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523620</v>
+        <v>523458</v>
       </c>
       <c r="R18" t="n">
-        <v>6846303</v>
+        <v>6846108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
         <v>125755812</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125740874</v>
+        <v>125742673</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,17 +2481,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523432</v>
+        <v>523590</v>
       </c>
       <c r="R20" t="n">
-        <v>6846118</v>
+        <v>6846277</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2535,22 +2535,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125742673</v>
+        <v>125740874</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,17 +2578,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523590</v>
+        <v>523432</v>
       </c>
       <c r="R21" t="n">
-        <v>6846277</v>
+        <v>6846118</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2632,12 +2632,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2647,7 +2647,7 @@
         <v>125755874</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755839</v>
+        <v>125755836</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523537</v>
+        <v>523502</v>
       </c>
       <c r="R23" t="n">
-        <v>6846261</v>
+        <v>6846299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755836</v>
+        <v>125755839</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523502</v>
+        <v>523537</v>
       </c>
       <c r="R24" t="n">
-        <v>6846299</v>
+        <v>6846261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755802</v>
+        <v>125755842</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523478</v>
+        <v>523656</v>
       </c>
       <c r="R25" t="n">
-        <v>6846087</v>
+        <v>6846239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,32 +3032,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755842</v>
+        <v>125755909</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>91821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523656</v>
+        <v>523407</v>
       </c>
       <c r="R26" t="n">
-        <v>6846239</v>
+        <v>6846172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,32 +3129,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755909</v>
+        <v>125755864</v>
       </c>
       <c r="B27" t="n">
-        <v>91819</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523407</v>
+        <v>523381</v>
       </c>
       <c r="R27" t="n">
-        <v>6846172</v>
+        <v>6846064</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R28" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,7 +3326,7 @@
         <v>125742433</v>
       </c>
       <c r="B29" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>125741338</v>
       </c>
       <c r="B30" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755877</v>
+        <v>125740278</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523461</v>
+        <v>523522</v>
       </c>
       <c r="R31" t="n">
-        <v>6846105</v>
+        <v>6846208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755853</v>
+        <v>125755877</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523425</v>
+        <v>523461</v>
       </c>
       <c r="R32" t="n">
-        <v>6846130</v>
+        <v>6846105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755840</v>
+        <v>125755853</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523595</v>
+        <v>523425</v>
       </c>
       <c r="R33" t="n">
-        <v>6846194</v>
+        <v>6846130</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125742754</v>
+        <v>125755840</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523569</v>
+        <v>523595</v>
       </c>
       <c r="R34" t="n">
-        <v>6846303</v>
+        <v>6846194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,22 +3907,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125740278</v>
+        <v>125740942</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523522</v>
+        <v>523475</v>
       </c>
       <c r="R35" t="n">
-        <v>6846208</v>
+        <v>6846068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B36" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R36" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
         <v>125755857</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>125755890</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>125740148</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755881</v>
+        <v>125740970</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4435,14 +4435,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523499</v>
+        <v>523383</v>
       </c>
       <c r="R40" t="n">
-        <v>6846107</v>
+        <v>6846110</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755901</v>
+        <v>125742499</v>
       </c>
       <c r="B41" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,37 +4512,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523588</v>
+        <v>523622</v>
       </c>
       <c r="R41" t="n">
-        <v>6846217</v>
+        <v>6846233</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4572,11 +4572,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,12 +4586,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4606,7 +4601,7 @@
         <v>125755814</v>
       </c>
       <c r="B42" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125740970</v>
+        <v>125755881</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4731,14 +4726,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523383</v>
+        <v>523499</v>
       </c>
       <c r="R43" t="n">
-        <v>6846110</v>
+        <v>6846107</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4785,22 +4780,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,37 +4803,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R44" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4868,6 +4863,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4882,60 +4882,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125740933</v>
+        <v>125755831</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523405</v>
+        <v>523491</v>
       </c>
       <c r="R45" t="n">
-        <v>6846104</v>
+        <v>6846097</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4979,44 +4988,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755873</v>
+        <v>125755813</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5035,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523443</v>
+        <v>523458</v>
       </c>
       <c r="R46" t="n">
-        <v>6846083</v>
+        <v>6846106</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5097,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755848</v>
+        <v>125740933</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,37 +5108,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523515</v>
+        <v>523405</v>
       </c>
       <c r="R47" t="n">
-        <v>6846181</v>
+        <v>6846104</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5173,66 +5182,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755831</v>
+        <v>125755873</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523491</v>
+        <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846097</v>
+        <v>6846083</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5291,32 +5291,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755813</v>
+        <v>125755833</v>
       </c>
       <c r="B49" t="n">
-        <v>97217</v>
+        <v>91395</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523458</v>
+        <v>523511</v>
       </c>
       <c r="R49" t="n">
-        <v>6846106</v>
+        <v>6846118</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5388,32 +5388,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755833</v>
+        <v>125755848</v>
       </c>
       <c r="B50" t="n">
-        <v>91393</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523511</v>
+        <v>523515</v>
       </c>
       <c r="R50" t="n">
-        <v>6846118</v>
+        <v>6846181</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
         <v>125755879</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755798</v>
+        <v>125755823</v>
       </c>
       <c r="B52" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523586</v>
+        <v>523377</v>
       </c>
       <c r="R52" t="n">
-        <v>6846194</v>
+        <v>6846073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5682,7 +5682,7 @@
         <v>125755859</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>125755878</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755823</v>
+        <v>125755798</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523377</v>
+        <v>523586</v>
       </c>
       <c r="R55" t="n">
-        <v>6846073</v>
+        <v>6846194</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125740194</v>
+        <v>125742527</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523518</v>
+        <v>523403</v>
       </c>
       <c r="R56" t="n">
-        <v>6846232</v>
+        <v>6846072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125742527</v>
+        <v>125740194</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523403</v>
+        <v>523518</v>
       </c>
       <c r="R57" t="n">
-        <v>6846072</v>
+        <v>6846232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
         <v>125755875</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6261,54 +6261,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R59" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6367,45 +6358,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755806</v>
+        <v>125755828</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523381</v>
+        <v>523512</v>
       </c>
       <c r="R60" t="n">
-        <v>6846064</v>
+        <v>6846071</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6467,7 +6467,7 @@
         <v>125740221</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755796</v>
+        <v>125755846</v>
       </c>
       <c r="B62" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,21 +6572,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523627</v>
+        <v>523604</v>
       </c>
       <c r="R62" t="n">
-        <v>6846239</v>
+        <v>6846240</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6658,10 +6658,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755846</v>
+        <v>125755863</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523604</v>
+        <v>523376</v>
       </c>
       <c r="R63" t="n">
-        <v>6846240</v>
+        <v>6846074</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,10 +6755,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755863</v>
+        <v>125755854</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523376</v>
+        <v>523410</v>
       </c>
       <c r="R64" t="n">
-        <v>6846074</v>
+        <v>6846112</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755854</v>
+        <v>125755880</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523410</v>
+        <v>523488</v>
       </c>
       <c r="R65" t="n">
-        <v>6846112</v>
+        <v>6846089</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755880</v>
+        <v>125755796</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523488</v>
+        <v>523627</v>
       </c>
       <c r="R66" t="n">
-        <v>6846089</v>
+        <v>6846239</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7049,7 +7049,7 @@
         <v>125740764</v>
       </c>
       <c r="B67" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7143,10 +7143,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755805</v>
+        <v>125755882</v>
       </c>
       <c r="B68" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7154,21 +7154,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523478</v>
+        <v>523515</v>
       </c>
       <c r="R68" t="n">
-        <v>6846168</v>
+        <v>6846106</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755804</v>
+        <v>125740179</v>
       </c>
       <c r="B69" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523485</v>
+        <v>523507</v>
       </c>
       <c r="R69" t="n">
-        <v>6846156</v>
+        <v>6846247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7325,22 +7325,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755882</v>
+        <v>125755805</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7348,21 +7348,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523515</v>
+        <v>523478</v>
       </c>
       <c r="R70" t="n">
-        <v>6846106</v>
+        <v>6846168</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125740179</v>
+        <v>125755804</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523507</v>
+        <v>523485</v>
       </c>
       <c r="R71" t="n">
-        <v>6846247</v>
+        <v>6846156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7519,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755843</v>
+        <v>125755817</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523662</v>
+        <v>523587</v>
       </c>
       <c r="R72" t="n">
-        <v>6846272</v>
+        <v>6846194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7631,7 +7631,7 @@
         <v>125755826</v>
       </c>
       <c r="B73" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755891</v>
+        <v>125755843</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523501</v>
+        <v>523662</v>
       </c>
       <c r="R74" t="n">
-        <v>6846327</v>
+        <v>6846272</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7833,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R75" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7919,32 +7919,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755897</v>
+        <v>125755883</v>
       </c>
       <c r="B76" t="n">
-        <v>92522</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523669</v>
+        <v>523485</v>
       </c>
       <c r="R76" t="n">
-        <v>6846274</v>
+        <v>6846121</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8016,10 +8016,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R77" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755883</v>
+        <v>125755841</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523485</v>
+        <v>523605</v>
       </c>
       <c r="R78" t="n">
-        <v>6846121</v>
+        <v>6846199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,10 +8210,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755847</v>
+        <v>125755855</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523553</v>
+        <v>523410</v>
       </c>
       <c r="R79" t="n">
-        <v>6846192</v>
+        <v>6846095</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,32 +8307,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755855</v>
+        <v>125755897</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523410</v>
+        <v>523669</v>
       </c>
       <c r="R80" t="n">
-        <v>6846095</v>
+        <v>6846274</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,10 +8404,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755858</v>
+        <v>125755862</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523393</v>
+        <v>523377</v>
       </c>
       <c r="R81" t="n">
-        <v>6846095</v>
+        <v>6846085</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,10 +8501,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125740592</v>
+        <v>125755852</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8532,17 +8532,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523450</v>
+        <v>523420</v>
       </c>
       <c r="R82" t="n">
-        <v>6846113</v>
+        <v>6846145</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8586,22 +8586,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755862</v>
+        <v>125755858</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523377</v>
+        <v>523393</v>
       </c>
       <c r="R83" t="n">
-        <v>6846085</v>
+        <v>6846095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,10 +8695,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755841</v>
+        <v>125740592</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,17 +8726,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523605</v>
+        <v>523450</v>
       </c>
       <c r="R84" t="n">
-        <v>6846199</v>
+        <v>6846113</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8780,22 +8780,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755827</v>
+        <v>125755837</v>
       </c>
       <c r="B85" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8803,21 +8803,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523501</v>
+        <v>523530</v>
       </c>
       <c r="R85" t="n">
-        <v>6846078</v>
+        <v>6846281</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755837</v>
+        <v>125755827</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523530</v>
+        <v>523501</v>
       </c>
       <c r="R86" t="n">
-        <v>6846281</v>
+        <v>6846078</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8989,7 +8989,7 @@
         <v>125755898</v>
       </c>
       <c r="B87" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>125755888</v>
       </c>
       <c r="B88" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>125755886</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>125755889</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755905</v>
+        <v>125755825</v>
       </c>
       <c r="B91" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R91" t="n">
-        <v>6846102</v>
+        <v>6846224</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B92" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R92" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B93" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R93" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755825</v>
+        <v>125755905</v>
       </c>
       <c r="B94" t="n">
-        <v>78730</v>
+        <v>78640</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523628</v>
+        <v>523497</v>
       </c>
       <c r="R94" t="n">
-        <v>6846224</v>
+        <v>6846102</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755885</v>
+        <v>125755904</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523473</v>
+        <v>523504</v>
       </c>
       <c r="R95" t="n">
-        <v>6846151</v>
+        <v>6846179</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9859,10 +9859,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755884</v>
+        <v>125755849</v>
       </c>
       <c r="B96" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523471</v>
+        <v>523414</v>
       </c>
       <c r="R96" t="n">
-        <v>6846134</v>
+        <v>6846169</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9956,10 +9956,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755849</v>
+        <v>125755884</v>
       </c>
       <c r="B97" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523414</v>
+        <v>523471</v>
       </c>
       <c r="R97" t="n">
-        <v>6846169</v>
+        <v>6846134</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10056,7 +10056,7 @@
         <v>125755834</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>125755844</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>125755845</v>
       </c>
       <c r="B100" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>125755876</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>125755861</v>
       </c>
       <c r="B102" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10538,10 +10538,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B103" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10549,21 +10549,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R103" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10666,17 +10666,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R104" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10720,22 +10720,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755820</v>
+        <v>125755903</v>
       </c>
       <c r="B105" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,21 +10743,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523410</v>
+        <v>523586</v>
       </c>
       <c r="R105" t="n">
-        <v>6846112</v>
+        <v>6846193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10829,10 +10829,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,37 +10840,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R106" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10914,12 +10914,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1364,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755896</v>
+        <v>125740292</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>98258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523465</v>
+        <v>523521</v>
       </c>
       <c r="R9" t="n">
-        <v>6846335</v>
+        <v>6846131</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,22 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755799</v>
+        <v>125741174</v>
       </c>
       <c r="B10" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523708</v>
+        <v>523475</v>
       </c>
       <c r="R10" t="n">
-        <v>6846300</v>
+        <v>6846068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,19 +1546,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125742564</v>
+        <v>125755896</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523612</v>
+        <v>523465</v>
       </c>
       <c r="R11" t="n">
-        <v>6846245</v>
+        <v>6846335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755818</v>
+        <v>125755799</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523628</v>
+        <v>523708</v>
       </c>
       <c r="R12" t="n">
-        <v>6846224</v>
+        <v>6846300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,48 +1752,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125740292</v>
+        <v>125742564</v>
       </c>
       <c r="B13" t="n">
-        <v>98258</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523521</v>
+        <v>523612</v>
       </c>
       <c r="R13" t="n">
-        <v>6846131</v>
+        <v>6846245</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1837,19 +1837,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125741174</v>
+        <v>125755818</v>
       </c>
       <c r="B14" t="n">
         <v>78732</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523475</v>
+        <v>523628</v>
       </c>
       <c r="R14" t="n">
-        <v>6846068</v>
+        <v>6846224</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,12 +1934,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740278</v>
+        <v>125755877</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523522</v>
+        <v>523461</v>
       </c>
       <c r="R31" t="n">
-        <v>6846208</v>
+        <v>6846105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,19 +3616,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755877</v>
+        <v>125755853</v>
       </c>
       <c r="B32" t="n">
         <v>78973</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523461</v>
+        <v>523425</v>
       </c>
       <c r="R32" t="n">
-        <v>6846105</v>
+        <v>6846130</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755853</v>
+        <v>125755840</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523425</v>
+        <v>523595</v>
       </c>
       <c r="R33" t="n">
-        <v>6846130</v>
+        <v>6846194</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755840</v>
+        <v>125740942</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523595</v>
+        <v>523475</v>
       </c>
       <c r="R34" t="n">
-        <v>6846194</v>
+        <v>6846068</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,22 +3907,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B35" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R35" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,34 +4415,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R40" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,6 +4477,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4489,19 +4494,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125742499</v>
+        <v>125740970</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4536,13 +4541,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523622</v>
+        <v>523383</v>
       </c>
       <c r="R41" t="n">
-        <v>6846233</v>
+        <v>6846110</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4598,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755814</v>
+        <v>125742499</v>
       </c>
       <c r="B42" t="n">
-        <v>92716</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,37 +4614,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523456</v>
+        <v>523622</v>
       </c>
       <c r="R42" t="n">
-        <v>6846109</v>
+        <v>6846233</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4683,22 +4688,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755881</v>
+        <v>125755814</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>92716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,21 +4711,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4730,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523499</v>
+        <v>523456</v>
       </c>
       <c r="R43" t="n">
-        <v>6846107</v>
+        <v>6846109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4792,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755901</v>
+        <v>125755881</v>
       </c>
       <c r="B44" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4803,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4827,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523588</v>
+        <v>523499</v>
       </c>
       <c r="R44" t="n">
-        <v>6846217</v>
+        <v>6846107</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,11 +4868,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4894,54 +4894,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755831</v>
+        <v>125755873</v>
       </c>
       <c r="B45" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523491</v>
+        <v>523443</v>
       </c>
       <c r="R45" t="n">
-        <v>6846097</v>
+        <v>6846083</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5000,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755813</v>
+        <v>125755833</v>
       </c>
       <c r="B46" t="n">
-        <v>97219</v>
+        <v>91395</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>1503</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5035,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523458</v>
+        <v>523511</v>
       </c>
       <c r="R46" t="n">
-        <v>6846106</v>
+        <v>6846118</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5097,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125740933</v>
+        <v>125755848</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5108,37 +5099,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523405</v>
+        <v>523515</v>
       </c>
       <c r="R47" t="n">
-        <v>6846104</v>
+        <v>6846181</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5182,19 +5173,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755873</v>
+        <v>125755879</v>
       </c>
       <c r="B48" t="n">
         <v>78973</v>
@@ -5229,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523443</v>
+        <v>523502</v>
       </c>
       <c r="R48" t="n">
-        <v>6846083</v>
+        <v>6846082</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5291,10 +5282,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755833</v>
+        <v>125755831</v>
       </c>
       <c r="B49" t="n">
-        <v>91395</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5302,34 +5293,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523511</v>
+        <v>523491</v>
       </c>
       <c r="R49" t="n">
-        <v>6846118</v>
+        <v>6846097</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5388,32 +5388,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755848</v>
+        <v>125755813</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>97219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523515</v>
+        <v>523458</v>
       </c>
       <c r="R50" t="n">
-        <v>6846181</v>
+        <v>6846106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755879</v>
+        <v>125740933</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5496,37 +5496,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523502</v>
+        <v>523405</v>
       </c>
       <c r="R51" t="n">
-        <v>6846082</v>
+        <v>6846104</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,22 +5570,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755823</v>
+        <v>125755859</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523377</v>
+        <v>523396</v>
       </c>
       <c r="R52" t="n">
-        <v>6846073</v>
+        <v>6846092</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R53" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755878</v>
+        <v>125755798</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5787,21 +5787,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523484</v>
+        <v>523586</v>
       </c>
       <c r="R54" t="n">
-        <v>6846075</v>
+        <v>6846194</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755798</v>
+        <v>125742527</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523586</v>
+        <v>523403</v>
       </c>
       <c r="R55" t="n">
-        <v>6846194</v>
+        <v>6846072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,19 +5958,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125742527</v>
+        <v>125740194</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523403</v>
+        <v>523518</v>
       </c>
       <c r="R56" t="n">
-        <v>6846072</v>
+        <v>6846232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125740194</v>
+        <v>125755823</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523518</v>
+        <v>523377</v>
       </c>
       <c r="R57" t="n">
-        <v>6846232</v>
+        <v>6846073</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6152,12 +6152,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125740179</v>
+        <v>125755805</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523507</v>
+        <v>523478</v>
       </c>
       <c r="R69" t="n">
-        <v>6846247</v>
+        <v>6846168</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7325,19 +7325,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755805</v>
+        <v>125755804</v>
       </c>
       <c r="B70" t="n">
         <v>79591</v>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523478</v>
+        <v>523485</v>
       </c>
       <c r="R70" t="n">
-        <v>6846168</v>
+        <v>6846156</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755804</v>
+        <v>125740179</v>
       </c>
       <c r="B71" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523485</v>
+        <v>523507</v>
       </c>
       <c r="R71" t="n">
-        <v>6846156</v>
+        <v>6846247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7519,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755817</v>
+        <v>125755826</v>
       </c>
       <c r="B72" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523587</v>
+        <v>523408</v>
       </c>
       <c r="R72" t="n">
-        <v>6846194</v>
+        <v>6846116</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R73" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B74" t="n">
         <v>78973</v>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R74" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755891</v>
+        <v>125755817</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7833,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523501</v>
+        <v>523587</v>
       </c>
       <c r="R75" t="n">
-        <v>6846327</v>
+        <v>6846194</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755825</v>
+        <v>125755819</v>
       </c>
       <c r="B91" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9412,7 +9412,7 @@
         <v>523628</v>
       </c>
       <c r="R91" t="n">
-        <v>6846224</v>
+        <v>6846238</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B92" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R92" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9568,10 +9568,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755885</v>
+        <v>125755905</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R93" t="n">
-        <v>6846151</v>
+        <v>6846102</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,7 +9665,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755905</v>
+        <v>125755904</v>
       </c>
       <c r="B94" t="n">
         <v>78640</v>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523497</v>
+        <v>523504</v>
       </c>
       <c r="R94" t="n">
-        <v>6846102</v>
+        <v>6846179</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755904</v>
+        <v>125755825</v>
       </c>
       <c r="B95" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R95" t="n">
-        <v>6846179</v>
+        <v>6846224</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755807</v>
+        <v>125740330</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523379</v>
+        <v>523527</v>
       </c>
       <c r="R2" t="n">
-        <v>6846064</v>
+        <v>6846185</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755824</v>
+        <v>125741230</v>
       </c>
       <c r="B3" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523501</v>
+        <v>523475</v>
       </c>
       <c r="R3" t="n">
-        <v>6846078</v>
+        <v>6846068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755851</v>
+        <v>125742098</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523422</v>
+        <v>523403</v>
       </c>
       <c r="R4" t="n">
-        <v>6846155</v>
+        <v>6846072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125742098</v>
+        <v>125755851</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523403</v>
+        <v>523422</v>
       </c>
       <c r="R5" t="n">
-        <v>6846072</v>
+        <v>6846155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,62 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755815</v>
+        <v>125755824</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523605</v>
+        <v>523501</v>
       </c>
       <c r="R6" t="n">
-        <v>6846199</v>
+        <v>6846078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,55 +1153,60 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125740330</v>
+        <v>125755807</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523527</v>
+        <v>523379</v>
       </c>
       <c r="R7" t="n">
-        <v>6846185</v>
+        <v>6846064</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,57 +1250,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125741230</v>
+        <v>125755815</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523475</v>
+        <v>523605</v>
       </c>
       <c r="R8" t="n">
-        <v>6846068</v>
+        <v>6846199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,60 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125740292</v>
+        <v>125742564</v>
       </c>
       <c r="B9" t="n">
-        <v>98258</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523521</v>
+        <v>523612</v>
       </c>
       <c r="R9" t="n">
-        <v>6846131</v>
+        <v>6846245</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,19 +1449,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125741174</v>
+        <v>125755818</v>
       </c>
       <c r="B10" t="n">
         <v>78732</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523475</v>
+        <v>523628</v>
       </c>
       <c r="R10" t="n">
-        <v>6846068</v>
+        <v>6846224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,60 +1546,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755896</v>
+        <v>125740292</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>98260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523465</v>
+        <v>523521</v>
       </c>
       <c r="R11" t="n">
-        <v>6846335</v>
+        <v>6846131</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1643,22 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755799</v>
+        <v>125741174</v>
       </c>
       <c r="B12" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523708</v>
+        <v>523475</v>
       </c>
       <c r="R12" t="n">
-        <v>6846300</v>
+        <v>6846068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,19 +1740,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125742564</v>
+        <v>125755896</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523612</v>
+        <v>523465</v>
       </c>
       <c r="R13" t="n">
-        <v>6846245</v>
+        <v>6846335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,22 +1837,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755818</v>
+        <v>125755799</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523628</v>
+        <v>523708</v>
       </c>
       <c r="R14" t="n">
-        <v>6846224</v>
+        <v>6846300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,52 +1939,57 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755850</v>
+        <v>125755816</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523417</v>
+        <v>523620</v>
       </c>
       <c r="R15" t="n">
-        <v>6846164</v>
+        <v>6846303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,14 +2041,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755892</v>
+        <v>125755850</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523495</v>
+        <v>523417</v>
       </c>
       <c r="R16" t="n">
-        <v>6846328</v>
+        <v>6846164</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2140,50 +2145,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755816</v>
+        <v>125755892</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523620</v>
+        <v>523495</v>
       </c>
       <c r="R17" t="n">
-        <v>6846303</v>
+        <v>6846328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>125755829</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,17 +2341,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B19" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,42 +2359,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R19" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2438,12 +2433,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2547,10 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2558,37 +2553,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R21" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2632,19 +2632,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R22" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755836</v>
+        <v>125755874</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523502</v>
+        <v>523446</v>
       </c>
       <c r="R23" t="n">
-        <v>6846299</v>
+        <v>6846093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755842</v>
+        <v>125741338</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523656</v>
+        <v>523403</v>
       </c>
       <c r="R25" t="n">
-        <v>6846239</v>
+        <v>6846072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,12 +3020,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3035,7 +3035,7 @@
         <v>125755909</v>
       </c>
       <c r="B26" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,45 +3129,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755864</v>
+        <v>125742433</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523381</v>
+        <v>523403</v>
       </c>
       <c r="R27" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,22 +3228,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755802</v>
+        <v>125755842</v>
       </c>
       <c r="B28" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3251,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523478</v>
+        <v>523656</v>
       </c>
       <c r="R28" t="n">
-        <v>6846087</v>
+        <v>6846239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,59 +3337,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125742433</v>
+        <v>125755802</v>
       </c>
       <c r="B29" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523403</v>
+        <v>523478</v>
       </c>
       <c r="R29" t="n">
-        <v>6846072</v>
+        <v>6846087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,22 +3422,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125741338</v>
+        <v>125755864</v>
       </c>
       <c r="B30" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523403</v>
+        <v>523381</v>
       </c>
       <c r="R30" t="n">
-        <v>6846072</v>
+        <v>6846064</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3519,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755877</v>
+        <v>125742754</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523461</v>
+        <v>523569</v>
       </c>
       <c r="R31" t="n">
-        <v>6846105</v>
+        <v>6846303</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,19 +3616,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755853</v>
+        <v>125755877</v>
       </c>
       <c r="B32" t="n">
         <v>78973</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523425</v>
+        <v>523461</v>
       </c>
       <c r="R32" t="n">
-        <v>6846130</v>
+        <v>6846105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755840</v>
+        <v>125740278</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523595</v>
+        <v>523522</v>
       </c>
       <c r="R33" t="n">
-        <v>6846194</v>
+        <v>6846208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125740278</v>
+        <v>125755853</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523522</v>
+        <v>523425</v>
       </c>
       <c r="R35" t="n">
-        <v>6846208</v>
+        <v>6846130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,19 +4004,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125742754</v>
+        <v>125755840</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523569</v>
+        <v>523595</v>
       </c>
       <c r="R36" t="n">
-        <v>6846303</v>
+        <v>6846194</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,19 +4101,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755857</v>
+        <v>125740148</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523398</v>
+        <v>523497</v>
       </c>
       <c r="R37" t="n">
-        <v>6846095</v>
+        <v>6846271</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,12 +4198,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125740148</v>
+        <v>125755857</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523497</v>
+        <v>523398</v>
       </c>
       <c r="R39" t="n">
-        <v>6846271</v>
+        <v>6846095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755901</v>
+        <v>125740970</v>
       </c>
       <c r="B40" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,34 +4415,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523588</v>
+        <v>523383</v>
       </c>
       <c r="R40" t="n">
-        <v>6846217</v>
+        <v>6846110</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,11 +4477,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4494,19 +4489,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125740970</v>
+        <v>125742499</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4541,13 +4536,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523383</v>
+        <v>523622</v>
       </c>
       <c r="R41" t="n">
-        <v>6846110</v>
+        <v>6846233</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,37 +4609,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R42" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4688,12 +4688,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4703,7 +4703,7 @@
         <v>125755814</v>
       </c>
       <c r="B43" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755833</v>
+        <v>125755879</v>
       </c>
       <c r="B46" t="n">
-        <v>91395</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523511</v>
+        <v>523502</v>
       </c>
       <c r="R46" t="n">
-        <v>6846118</v>
+        <v>6846082</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755848</v>
+        <v>125740933</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,37 +5099,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523515</v>
+        <v>523405</v>
       </c>
       <c r="R47" t="n">
-        <v>6846181</v>
+        <v>6846104</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5173,44 +5173,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755879</v>
+        <v>125755833</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>91397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523502</v>
+        <v>523511</v>
       </c>
       <c r="R48" t="n">
-        <v>6846082</v>
+        <v>6846118</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5275,61 +5275,52 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755831</v>
+        <v>125755848</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523491</v>
+        <v>523515</v>
       </c>
       <c r="R49" t="n">
-        <v>6846097</v>
+        <v>6846181</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5388,45 +5379,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755813</v>
+        <v>125755831</v>
       </c>
       <c r="B50" t="n">
-        <v>97219</v>
+        <v>98343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523458</v>
+        <v>523491</v>
       </c>
       <c r="R50" t="n">
-        <v>6846106</v>
+        <v>6846097</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,55 +5478,55 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125740933</v>
+        <v>125755813</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>97221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523405</v>
+        <v>523458</v>
       </c>
       <c r="R51" t="n">
-        <v>6846104</v>
+        <v>6846106</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,19 +5570,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755859</v>
+        <v>125740194</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523396</v>
+        <v>523518</v>
       </c>
       <c r="R52" t="n">
-        <v>6846092</v>
+        <v>6846232</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755878</v>
+        <v>125742527</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523484</v>
+        <v>523403</v>
       </c>
       <c r="R53" t="n">
-        <v>6846075</v>
+        <v>6846072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,22 +5764,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755798</v>
+        <v>125755878</v>
       </c>
       <c r="B54" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5787,21 +5787,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523586</v>
+        <v>523484</v>
       </c>
       <c r="R54" t="n">
-        <v>6846194</v>
+        <v>6846075</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125742527</v>
+        <v>125755859</v>
       </c>
       <c r="B55" t="n">
         <v>78973</v>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523403</v>
+        <v>523396</v>
       </c>
       <c r="R55" t="n">
-        <v>6846072</v>
+        <v>6846092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,22 +5958,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125740194</v>
+        <v>125755798</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523518</v>
+        <v>523586</v>
       </c>
       <c r="R56" t="n">
-        <v>6846232</v>
+        <v>6846194</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6055,12 +6055,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6157,14 +6157,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755875</v>
+        <v>125740221</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6195,17 +6195,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523436</v>
+        <v>523538</v>
       </c>
       <c r="R58" t="n">
-        <v>6846102</v>
+        <v>6846149</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6249,12 +6249,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6351,61 +6351,52 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R60" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6464,48 +6455,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125740221</v>
+        <v>125755828</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523538</v>
+        <v>523512</v>
       </c>
       <c r="R61" t="n">
-        <v>6846149</v>
+        <v>6846071</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6549,22 +6549,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755846</v>
+        <v>125740764</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6572,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523604</v>
+        <v>523443</v>
       </c>
       <c r="R62" t="n">
-        <v>6846240</v>
+        <v>6846070</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,19 +6646,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755863</v>
+        <v>125755854</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523376</v>
+        <v>523410</v>
       </c>
       <c r="R63" t="n">
-        <v>6846074</v>
+        <v>6846112</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755854</v>
+        <v>125755880</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523410</v>
+        <v>523488</v>
       </c>
       <c r="R64" t="n">
-        <v>6846112</v>
+        <v>6846089</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755880</v>
+        <v>125755846</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523488</v>
+        <v>523604</v>
       </c>
       <c r="R65" t="n">
-        <v>6846089</v>
+        <v>6846240</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7039,17 +7039,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125740764</v>
+        <v>125755863</v>
       </c>
       <c r="B67" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,37 +7057,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523443</v>
+        <v>523376</v>
       </c>
       <c r="R67" t="n">
-        <v>6846070</v>
+        <v>6846074</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7131,19 +7131,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755882</v>
+        <v>125740179</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523515</v>
+        <v>523507</v>
       </c>
       <c r="R68" t="n">
-        <v>6846106</v>
+        <v>6846247</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7228,22 +7228,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755805</v>
+        <v>125755882</v>
       </c>
       <c r="B69" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523478</v>
+        <v>523515</v>
       </c>
       <c r="R69" t="n">
-        <v>6846168</v>
+        <v>6846106</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7427,17 +7427,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125740179</v>
+        <v>125755805</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523507</v>
+        <v>523478</v>
       </c>
       <c r="R71" t="n">
-        <v>6846247</v>
+        <v>6846168</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7519,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R72" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R73" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755891</v>
+        <v>125755826</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7736,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523501</v>
+        <v>523408</v>
       </c>
       <c r="R74" t="n">
-        <v>6846327</v>
+        <v>6846116</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7912,14 +7912,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755883</v>
+        <v>125755862</v>
       </c>
       <c r="B76" t="n">
         <v>78973</v>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523485</v>
+        <v>523377</v>
       </c>
       <c r="R76" t="n">
-        <v>6846121</v>
+        <v>6846085</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755847</v>
+        <v>125755852</v>
       </c>
       <c r="B77" t="n">
         <v>78973</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523553</v>
+        <v>523420</v>
       </c>
       <c r="R77" t="n">
-        <v>6846192</v>
+        <v>6846145</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755841</v>
+        <v>125755883</v>
       </c>
       <c r="B78" t="n">
         <v>78973</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523605</v>
+        <v>523485</v>
       </c>
       <c r="R78" t="n">
-        <v>6846199</v>
+        <v>6846121</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8307,32 +8307,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755897</v>
+        <v>125755858</v>
       </c>
       <c r="B80" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523669</v>
+        <v>523393</v>
       </c>
       <c r="R80" t="n">
-        <v>6846274</v>
+        <v>6846095</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,32 +8404,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755862</v>
+        <v>125755897</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523377</v>
+        <v>523669</v>
       </c>
       <c r="R81" t="n">
-        <v>6846085</v>
+        <v>6846274</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B82" t="n">
         <v>78973</v>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R82" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755858</v>
+        <v>125755841</v>
       </c>
       <c r="B83" t="n">
         <v>78973</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523393</v>
+        <v>523605</v>
       </c>
       <c r="R83" t="n">
-        <v>6846095</v>
+        <v>6846199</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -8979,39 +8979,39 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755898</v>
+        <v>125755888</v>
       </c>
       <c r="B87" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523635</v>
+        <v>523478</v>
       </c>
       <c r="R87" t="n">
-        <v>6846293</v>
+        <v>6846168</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755888</v>
+        <v>125755886</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523478</v>
+        <v>523485</v>
       </c>
       <c r="R88" t="n">
-        <v>6846168</v>
+        <v>6846156</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755886</v>
+        <v>125755889</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523485</v>
+        <v>523490</v>
       </c>
       <c r="R89" t="n">
-        <v>6846156</v>
+        <v>6846171</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9277,32 +9277,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755889</v>
+        <v>125755898</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523490</v>
+        <v>523635</v>
       </c>
       <c r="R90" t="n">
-        <v>6846171</v>
+        <v>6846293</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B91" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R91" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755885</v>
+        <v>125755825</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523473</v>
+        <v>523628</v>
       </c>
       <c r="R92" t="n">
-        <v>6846151</v>
+        <v>6846224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9561,17 +9561,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755905</v>
+        <v>125755819</v>
       </c>
       <c r="B93" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R93" t="n">
-        <v>6846102</v>
+        <v>6846238</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9658,14 +9658,14 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755904</v>
+        <v>125755905</v>
       </c>
       <c r="B94" t="n">
         <v>78640</v>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523504</v>
+        <v>523497</v>
       </c>
       <c r="R94" t="n">
-        <v>6846179</v>
+        <v>6846102</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755825</v>
+        <v>125755904</v>
       </c>
       <c r="B95" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R95" t="n">
-        <v>6846224</v>
+        <v>6846179</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9859,7 +9859,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755849</v>
+        <v>125755884</v>
       </c>
       <c r="B96" t="n">
         <v>78973</v>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523414</v>
+        <v>523471</v>
       </c>
       <c r="R96" t="n">
-        <v>6846169</v>
+        <v>6846134</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755884</v>
+        <v>125755849</v>
       </c>
       <c r="B97" t="n">
         <v>78973</v>
@@ -9991,10 +9991,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523471</v>
+        <v>523414</v>
       </c>
       <c r="R97" t="n">
-        <v>6846134</v>
+        <v>6846169</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B103" t="n">
         <v>78973</v>
@@ -10569,17 +10569,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R103" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10623,22 +10623,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125742574</v>
+        <v>125755903</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,37 +10646,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523592</v>
+        <v>523586</v>
       </c>
       <c r="R104" t="n">
-        <v>6846248</v>
+        <v>6846193</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10720,22 +10720,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B105" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10743,21 +10743,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10767,10 +10767,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R105" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -3531,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125742754</v>
+        <v>125740278</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523569</v>
+        <v>523522</v>
       </c>
       <c r="R31" t="n">
-        <v>6846303</v>
+        <v>6846208</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755877</v>
+        <v>125740942</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523461</v>
+        <v>523475</v>
       </c>
       <c r="R32" t="n">
-        <v>6846105</v>
+        <v>6846068</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3713,19 +3713,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125740278</v>
+        <v>125755853</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523522</v>
+        <v>523425</v>
       </c>
       <c r="R33" t="n">
-        <v>6846208</v>
+        <v>6846130</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,22 +3810,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125740942</v>
+        <v>125755840</v>
       </c>
       <c r="B34" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523475</v>
+        <v>523595</v>
       </c>
       <c r="R34" t="n">
-        <v>6846068</v>
+        <v>6846194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3907,19 +3907,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755853</v>
+        <v>125742754</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523425</v>
+        <v>523569</v>
       </c>
       <c r="R35" t="n">
-        <v>6846130</v>
+        <v>6846303</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,19 +4004,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755840</v>
+        <v>125755877</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523595</v>
+        <v>523461</v>
       </c>
       <c r="R36" t="n">
-        <v>6846194</v>
+        <v>6846105</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125740194</v>
+        <v>125755823</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523518</v>
+        <v>523377</v>
       </c>
       <c r="R52" t="n">
-        <v>6846232</v>
+        <v>6846073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5667,19 +5667,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125742527</v>
+        <v>125740194</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523403</v>
+        <v>523518</v>
       </c>
       <c r="R53" t="n">
-        <v>6846072</v>
+        <v>6846232</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755878</v>
+        <v>125742527</v>
       </c>
       <c r="B54" t="n">
         <v>78973</v>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523484</v>
+        <v>523403</v>
       </c>
       <c r="R54" t="n">
-        <v>6846075</v>
+        <v>6846072</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5861,19 +5861,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B55" t="n">
         <v>78973</v>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R55" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755798</v>
+        <v>125755859</v>
       </c>
       <c r="B56" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523586</v>
+        <v>523396</v>
       </c>
       <c r="R56" t="n">
-        <v>6846194</v>
+        <v>6846092</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755823</v>
+        <v>125755798</v>
       </c>
       <c r="B57" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6078,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523377</v>
+        <v>523586</v>
       </c>
       <c r="R57" t="n">
-        <v>6846073</v>
+        <v>6846194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,45 +6358,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R60" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6448,61 +6457,52 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R61" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125740179</v>
+        <v>125755882</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523507</v>
+        <v>523515</v>
       </c>
       <c r="R68" t="n">
-        <v>6846247</v>
+        <v>6846106</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7228,19 +7228,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755882</v>
+        <v>125740179</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523515</v>
+        <v>523507</v>
       </c>
       <c r="R69" t="n">
-        <v>6846106</v>
+        <v>6846247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8792,32 +8792,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755837</v>
+        <v>125755898</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523530</v>
+        <v>523635</v>
       </c>
       <c r="R85" t="n">
-        <v>6846281</v>
+        <v>6846293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8882,17 +8882,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755827</v>
+        <v>125755837</v>
       </c>
       <c r="B86" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8900,21 +8900,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523501</v>
+        <v>523530</v>
       </c>
       <c r="R86" t="n">
-        <v>6846078</v>
+        <v>6846281</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8986,10 +8986,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755888</v>
+        <v>125755827</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8997,21 +8997,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523478</v>
+        <v>523501</v>
       </c>
       <c r="R87" t="n">
-        <v>6846168</v>
+        <v>6846078</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9076,14 +9076,14 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755886</v>
+        <v>125755888</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9118,10 +9118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523485</v>
+        <v>523478</v>
       </c>
       <c r="R88" t="n">
-        <v>6846156</v>
+        <v>6846168</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755889</v>
+        <v>125755886</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523490</v>
+        <v>523485</v>
       </c>
       <c r="R89" t="n">
-        <v>6846171</v>
+        <v>6846156</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9277,32 +9277,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755898</v>
+        <v>125755889</v>
       </c>
       <c r="B90" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523635</v>
+        <v>523490</v>
       </c>
       <c r="R90" t="n">
-        <v>6846293</v>
+        <v>6846171</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10538,10 +10538,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125742574</v>
+        <v>125755903</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10549,37 +10549,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523592</v>
+        <v>523586</v>
       </c>
       <c r="R103" t="n">
-        <v>6846248</v>
+        <v>6846193</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10623,22 +10623,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B104" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R104" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10732,7 +10732,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10763,17 +10763,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R105" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10817,12 +10817,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125740330</v>
+        <v>125755815</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523527</v>
+        <v>523605</v>
       </c>
       <c r="R2" t="n">
-        <v>6846185</v>
+        <v>6846199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125741230</v>
+        <v>125740307</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523475</v>
+        <v>523527</v>
       </c>
       <c r="R3" t="n">
-        <v>6846068</v>
+        <v>6846185</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R4" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755851</v>
+        <v>125742098</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523422</v>
+        <v>523403</v>
       </c>
       <c r="R5" t="n">
-        <v>6846155</v>
+        <v>6846072</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755824</v>
+        <v>125755851</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523501</v>
+        <v>523422</v>
       </c>
       <c r="R6" t="n">
-        <v>6846078</v>
+        <v>6846155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1158,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1255,57 +1260,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755815</v>
+        <v>125755824</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523605</v>
+        <v>523501</v>
       </c>
       <c r="R8" t="n">
-        <v>6846199</v>
+        <v>6846078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>125740292</v>
       </c>
       <c r="B11" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2041,52 +2041,61 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755850</v>
+        <v>125755829</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523417</v>
+        <v>523458</v>
       </c>
       <c r="R16" t="n">
-        <v>6846164</v>
+        <v>6846108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2154,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755892</v>
+        <v>125755850</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2180,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523495</v>
+        <v>523417</v>
       </c>
       <c r="R17" t="n">
-        <v>6846328</v>
+        <v>6846164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,54 +2251,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755829</v>
+        <v>125755892</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523458</v>
+        <v>523495</v>
       </c>
       <c r="R18" t="n">
-        <v>6846108</v>
+        <v>6846328</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,17 +2341,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,37 +2359,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R19" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2433,19 +2438,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125742673</v>
+        <v>125740874</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2476,17 +2481,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523590</v>
+        <v>523432</v>
       </c>
       <c r="R20" t="n">
-        <v>6846277</v>
+        <v>6846118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2530,22 +2535,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755812</v>
+        <v>125742673</v>
       </c>
       <c r="B21" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,39 +2558,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523437</v>
+        <v>523590</v>
       </c>
       <c r="R21" t="n">
-        <v>6846102</v>
+        <v>6846277</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,19 +2632,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755836</v>
+        <v>125755839</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523502</v>
+        <v>523537</v>
       </c>
       <c r="R22" t="n">
-        <v>6846299</v>
+        <v>6846261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755874</v>
+        <v>125755836</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523446</v>
+        <v>523502</v>
       </c>
       <c r="R23" t="n">
-        <v>6846093</v>
+        <v>6846299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755839</v>
+        <v>125755874</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523537</v>
+        <v>523446</v>
       </c>
       <c r="R24" t="n">
-        <v>6846261</v>
+        <v>6846093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125741338</v>
+        <v>125755842</v>
       </c>
       <c r="B25" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523403</v>
+        <v>523656</v>
       </c>
       <c r="R25" t="n">
-        <v>6846072</v>
+        <v>6846239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,44 +3020,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755909</v>
+        <v>125755864</v>
       </c>
       <c r="B26" t="n">
-        <v>91823</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523407</v>
+        <v>523381</v>
       </c>
       <c r="R26" t="n">
-        <v>6846172</v>
+        <v>6846064</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,59 +3129,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125742433</v>
+        <v>125755909</v>
       </c>
       <c r="B27" t="n">
-        <v>56844</v>
+        <v>91825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1179</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523403</v>
+        <v>523407</v>
       </c>
       <c r="R27" t="n">
-        <v>6846072</v>
+        <v>6846172</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,22 +3214,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755842</v>
+        <v>125755802</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523656</v>
+        <v>523478</v>
       </c>
       <c r="R28" t="n">
-        <v>6846239</v>
+        <v>6846087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,45 +3323,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755802</v>
+        <v>125742433</v>
       </c>
       <c r="B29" t="n">
-        <v>79591</v>
+        <v>56844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523478</v>
+        <v>523403</v>
       </c>
       <c r="R29" t="n">
-        <v>6846087</v>
+        <v>6846072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,22 +3422,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755864</v>
+        <v>125741338</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523381</v>
+        <v>523403</v>
       </c>
       <c r="R30" t="n">
-        <v>6846064</v>
+        <v>6846072</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3519,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740278</v>
+        <v>125755840</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523522</v>
+        <v>523595</v>
       </c>
       <c r="R31" t="n">
-        <v>6846208</v>
+        <v>6846194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,22 +3616,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R32" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755853</v>
+        <v>125742754</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523425</v>
+        <v>523569</v>
       </c>
       <c r="R33" t="n">
-        <v>6846130</v>
+        <v>6846303</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,19 +3810,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755840</v>
+        <v>125755877</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523595</v>
+        <v>523461</v>
       </c>
       <c r="R34" t="n">
-        <v>6846194</v>
+        <v>6846105</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125742754</v>
+        <v>125755853</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523569</v>
+        <v>523425</v>
       </c>
       <c r="R35" t="n">
-        <v>6846303</v>
+        <v>6846130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4004,22 +4004,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755877</v>
+        <v>125740942</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523461</v>
+        <v>523475</v>
       </c>
       <c r="R36" t="n">
-        <v>6846105</v>
+        <v>6846068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,12 +4101,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755890</v>
+        <v>125755857</v>
       </c>
       <c r="B38" t="n">
         <v>78973</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523496</v>
+        <v>523398</v>
       </c>
       <c r="R38" t="n">
-        <v>6846308</v>
+        <v>6846095</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755857</v>
+        <v>125755890</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523398</v>
+        <v>523496</v>
       </c>
       <c r="R39" t="n">
-        <v>6846095</v>
+        <v>6846308</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125740970</v>
+        <v>125755881</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4435,14 +4435,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523383</v>
+        <v>523499</v>
       </c>
       <c r="R40" t="n">
-        <v>6846110</v>
+        <v>6846107</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,37 +4512,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R41" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4572,6 +4572,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4586,22 +4591,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755901</v>
+        <v>125755814</v>
       </c>
       <c r="B42" t="n">
-        <v>78640</v>
+        <v>92720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523588</v>
+        <v>523456</v>
       </c>
       <c r="R42" t="n">
-        <v>6846217</v>
+        <v>6846109</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,10 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755814</v>
+        <v>125740970</v>
       </c>
       <c r="B43" t="n">
-        <v>92718</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,34 +4711,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523456</v>
+        <v>523383</v>
       </c>
       <c r="R43" t="n">
-        <v>6846109</v>
+        <v>6846110</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4785,19 +4785,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4828,17 +4828,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R44" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4882,44 +4882,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755873</v>
+        <v>125755833</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523443</v>
+        <v>523511</v>
       </c>
       <c r="R45" t="n">
-        <v>6846083</v>
+        <v>6846118</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,7 +4991,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755879</v>
+        <v>125755848</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523502</v>
+        <v>523515</v>
       </c>
       <c r="R46" t="n">
-        <v>6846082</v>
+        <v>6846181</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125740933</v>
+        <v>125755879</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,37 +5099,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523405</v>
+        <v>523502</v>
       </c>
       <c r="R47" t="n">
-        <v>6846104</v>
+        <v>6846082</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5173,44 +5173,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755833</v>
+        <v>125755873</v>
       </c>
       <c r="B48" t="n">
-        <v>91397</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523511</v>
+        <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846118</v>
+        <v>6846083</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5275,39 +5275,39 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755848</v>
+        <v>125755813</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>97223</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523515</v>
+        <v>523458</v>
       </c>
       <c r="R49" t="n">
-        <v>6846181</v>
+        <v>6846106</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
         <v>125755831</v>
       </c>
       <c r="B50" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5478,55 +5478,55 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755813</v>
+        <v>125740933</v>
       </c>
       <c r="B51" t="n">
-        <v>97221</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523458</v>
+        <v>523405</v>
       </c>
       <c r="R51" t="n">
-        <v>6846106</v>
+        <v>6846104</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,22 +5570,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755823</v>
+        <v>125755859</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523377</v>
+        <v>523396</v>
       </c>
       <c r="R52" t="n">
-        <v>6846073</v>
+        <v>6846092</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5672,14 +5672,14 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125740194</v>
+        <v>125755878</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523518</v>
+        <v>523484</v>
       </c>
       <c r="R53" t="n">
-        <v>6846232</v>
+        <v>6846075</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5764,19 +5764,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125742527</v>
+        <v>125740194</v>
       </c>
       <c r="B54" t="n">
         <v>78973</v>
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523403</v>
+        <v>523518</v>
       </c>
       <c r="R54" t="n">
-        <v>6846072</v>
+        <v>6846232</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755878</v>
+        <v>125742527</v>
       </c>
       <c r="B55" t="n">
         <v>78973</v>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523484</v>
+        <v>523403</v>
       </c>
       <c r="R55" t="n">
-        <v>6846075</v>
+        <v>6846072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,22 +5958,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755859</v>
+        <v>125755823</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523396</v>
+        <v>523377</v>
       </c>
       <c r="R56" t="n">
-        <v>6846092</v>
+        <v>6846073</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6157,17 +6157,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125740221</v>
+        <v>125755806</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6175,37 +6175,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523538</v>
+        <v>523381</v>
       </c>
       <c r="R58" t="n">
-        <v>6846149</v>
+        <v>6846064</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6249,57 +6249,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755806</v>
+        <v>125755828</v>
       </c>
       <c r="B59" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523381</v>
+        <v>523512</v>
       </c>
       <c r="R59" t="n">
-        <v>6846064</v>
+        <v>6846071</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6351,64 +6360,55 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755828</v>
+        <v>125740221</v>
       </c>
       <c r="B60" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523512</v>
+        <v>523538</v>
       </c>
       <c r="R60" t="n">
-        <v>6846071</v>
+        <v>6846149</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6452,12 +6452,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R63" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6949,10 +6949,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755796</v>
+        <v>125755854</v>
       </c>
       <c r="B66" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6960,21 +6960,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523627</v>
+        <v>523410</v>
       </c>
       <c r="R66" t="n">
-        <v>6846239</v>
+        <v>6846112</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7039,17 +7039,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755863</v>
+        <v>125755796</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,21 +7057,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7081,10 +7081,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523376</v>
+        <v>523627</v>
       </c>
       <c r="R67" t="n">
-        <v>6846074</v>
+        <v>6846239</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,10 +7240,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125740179</v>
+        <v>125755805</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523507</v>
+        <v>523478</v>
       </c>
       <c r="R69" t="n">
-        <v>6846247</v>
+        <v>6846168</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7325,12 +7325,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7427,17 +7427,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755805</v>
+        <v>125740179</v>
       </c>
       <c r="B71" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7445,21 +7445,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523478</v>
+        <v>523507</v>
       </c>
       <c r="R71" t="n">
-        <v>6846168</v>
+        <v>6846247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,19 +7519,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R72" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755891</v>
+        <v>125755843</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523501</v>
+        <v>523662</v>
       </c>
       <c r="R73" t="n">
-        <v>6846327</v>
+        <v>6846272</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7912,39 +7912,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755862</v>
+        <v>125755897</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523377</v>
+        <v>523669</v>
       </c>
       <c r="R76" t="n">
-        <v>6846085</v>
+        <v>6846274</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8016,7 +8016,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755852</v>
+        <v>125755847</v>
       </c>
       <c r="B77" t="n">
         <v>78973</v>
@@ -8051,10 +8051,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523420</v>
+        <v>523553</v>
       </c>
       <c r="R77" t="n">
-        <v>6846145</v>
+        <v>6846192</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755883</v>
+        <v>125755841</v>
       </c>
       <c r="B78" t="n">
         <v>78973</v>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523485</v>
+        <v>523605</v>
       </c>
       <c r="R78" t="n">
-        <v>6846121</v>
+        <v>6846199</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755855</v>
+        <v>125755862</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523410</v>
+        <v>523377</v>
       </c>
       <c r="R79" t="n">
-        <v>6846095</v>
+        <v>6846085</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,7 +8307,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755858</v>
+        <v>125755852</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523393</v>
+        <v>523420</v>
       </c>
       <c r="R80" t="n">
-        <v>6846095</v>
+        <v>6846145</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,32 +8404,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755897</v>
+        <v>125755883</v>
       </c>
       <c r="B81" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523669</v>
+        <v>523485</v>
       </c>
       <c r="R81" t="n">
-        <v>6846274</v>
+        <v>6846121</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755847</v>
+        <v>125755858</v>
       </c>
       <c r="B82" t="n">
         <v>78973</v>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523553</v>
+        <v>523393</v>
       </c>
       <c r="R82" t="n">
-        <v>6846192</v>
+        <v>6846095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755841</v>
+        <v>125755855</v>
       </c>
       <c r="B83" t="n">
         <v>78973</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523605</v>
+        <v>523410</v>
       </c>
       <c r="R83" t="n">
-        <v>6846199</v>
+        <v>6846095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8795,7 +8795,7 @@
         <v>125755898</v>
       </c>
       <c r="B85" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755885</v>
+        <v>125755905</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R91" t="n">
-        <v>6846151</v>
+        <v>6846102</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755825</v>
+        <v>125755904</v>
       </c>
       <c r="B92" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9482,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R92" t="n">
-        <v>6846224</v>
+        <v>6846179</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9561,17 +9561,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755819</v>
+        <v>125755885</v>
       </c>
       <c r="B93" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9579,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9603,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R93" t="n">
-        <v>6846238</v>
+        <v>6846151</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9658,17 +9658,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755905</v>
+        <v>125755825</v>
       </c>
       <c r="B94" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R94" t="n">
-        <v>6846102</v>
+        <v>6846224</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B95" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9773,21 +9773,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R95" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10538,10 +10538,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B103" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10549,21 +10549,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R103" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755887</v>
+        <v>125755903</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10646,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523473</v>
+        <v>523586</v>
       </c>
       <c r="R104" t="n">
-        <v>6846157</v>
+        <v>6846193</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125740307</v>
+        <v>125755851</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523527</v>
+        <v>523422</v>
       </c>
       <c r="R3" t="n">
-        <v>6846185</v>
+        <v>6846155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,60 +862,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125741230</v>
+        <v>125755807</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523475</v>
+        <v>523379</v>
       </c>
       <c r="R4" t="n">
-        <v>6846068</v>
+        <v>6846064</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125742098</v>
+        <v>125755824</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523403</v>
+        <v>523501</v>
       </c>
       <c r="R5" t="n">
-        <v>6846072</v>
+        <v>6846078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755851</v>
+        <v>125755818</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523422</v>
+        <v>523628</v>
       </c>
       <c r="R6" t="n">
-        <v>6846155</v>
+        <v>6846224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755807</v>
+        <v>125740292</v>
       </c>
       <c r="B7" t="n">
-        <v>56844</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,42 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523379</v>
+        <v>523521</v>
       </c>
       <c r="R7" t="n">
-        <v>6846064</v>
+        <v>6846131</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755824</v>
+        <v>125755896</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523501</v>
+        <v>523465</v>
       </c>
       <c r="R8" t="n">
-        <v>6846078</v>
+        <v>6846335</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125742564</v>
+        <v>125755799</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523612</v>
+        <v>523708</v>
       </c>
       <c r="R9" t="n">
-        <v>6846245</v>
+        <v>6846300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,57 +1449,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755818</v>
+        <v>125755816</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523628</v>
+        <v>523620</v>
       </c>
       <c r="R10" t="n">
-        <v>6846224</v>
+        <v>6846303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,48 +1563,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125740292</v>
+        <v>125755829</v>
       </c>
       <c r="B11" t="n">
-        <v>98262</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523521</v>
+        <v>523458</v>
       </c>
       <c r="R11" t="n">
-        <v>6846131</v>
+        <v>6846108</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1643,22 +1657,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125741174</v>
+        <v>125755850</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1680,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523475</v>
+        <v>523417</v>
       </c>
       <c r="R12" t="n">
-        <v>6846068</v>
+        <v>6846164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,19 +1754,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755896</v>
+        <v>125755892</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1787,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523465</v>
+        <v>523495</v>
       </c>
       <c r="R13" t="n">
-        <v>6846335</v>
+        <v>6846328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755799</v>
+        <v>125740874</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,37 +1874,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523708</v>
+        <v>523432</v>
       </c>
       <c r="R14" t="n">
-        <v>6846300</v>
+        <v>6846118</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1934,50 +1948,50 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755816</v>
+        <v>125755812</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1986,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523620</v>
+        <v>523437</v>
       </c>
       <c r="R15" t="n">
-        <v>6846303</v>
+        <v>6846102</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,54 +2062,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755829</v>
+        <v>125755839</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523458</v>
+        <v>523537</v>
       </c>
       <c r="R16" t="n">
-        <v>6846108</v>
+        <v>6846261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,7 +2159,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755850</v>
+        <v>125755836</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2189,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523417</v>
+        <v>523502</v>
       </c>
       <c r="R17" t="n">
-        <v>6846164</v>
+        <v>6846299</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,7 +2256,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755892</v>
+        <v>125755874</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2286,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523495</v>
+        <v>523446</v>
       </c>
       <c r="R18" t="n">
-        <v>6846328</v>
+        <v>6846093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755812</v>
+        <v>125755842</v>
       </c>
       <c r="B19" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,39 +2364,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523437</v>
+        <v>523656</v>
       </c>
       <c r="R19" t="n">
-        <v>6846102</v>
+        <v>6846239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125740874</v>
+        <v>125755864</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2481,17 +2481,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523432</v>
+        <v>523381</v>
       </c>
       <c r="R20" t="n">
-        <v>6846118</v>
+        <v>6846064</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2535,44 +2535,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125742673</v>
+        <v>125755909</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>91825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523590</v>
+        <v>523407</v>
       </c>
       <c r="R21" t="n">
-        <v>6846277</v>
+        <v>6846172</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,22 +2632,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755839</v>
+        <v>125755802</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523537</v>
+        <v>523478</v>
       </c>
       <c r="R22" t="n">
-        <v>6846261</v>
+        <v>6846087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755836</v>
+        <v>125755877</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523502</v>
+        <v>523461</v>
       </c>
       <c r="R23" t="n">
-        <v>6846299</v>
+        <v>6846105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755874</v>
+        <v>125755853</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523446</v>
+        <v>523425</v>
       </c>
       <c r="R24" t="n">
-        <v>6846093</v>
+        <v>6846130</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755842</v>
+        <v>125755840</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523656</v>
+        <v>523595</v>
       </c>
       <c r="R25" t="n">
-        <v>6846239</v>
+        <v>6846194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755864</v>
+        <v>125755857</v>
       </c>
       <c r="B26" t="n">
         <v>78973</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523381</v>
+        <v>523398</v>
       </c>
       <c r="R26" t="n">
-        <v>6846064</v>
+        <v>6846095</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,32 +3129,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755909</v>
+        <v>125755890</v>
       </c>
       <c r="B27" t="n">
-        <v>91825</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523407</v>
+        <v>523496</v>
       </c>
       <c r="R27" t="n">
-        <v>6846172</v>
+        <v>6846308</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755802</v>
+        <v>125755881</v>
       </c>
       <c r="B28" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523478</v>
+        <v>523499</v>
       </c>
       <c r="R28" t="n">
-        <v>6846087</v>
+        <v>6846107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,59 +3323,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125742433</v>
+        <v>125755901</v>
       </c>
       <c r="B29" t="n">
-        <v>56844</v>
+        <v>78640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523403</v>
+        <v>523588</v>
       </c>
       <c r="R29" t="n">
-        <v>6846072</v>
+        <v>6846217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,6 +3396,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3422,22 +3413,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125741338</v>
+        <v>125755814</v>
       </c>
       <c r="B30" t="n">
-        <v>78732</v>
+        <v>92720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3445,21 +3436,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3469,10 +3460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523403</v>
+        <v>523456</v>
       </c>
       <c r="R30" t="n">
-        <v>6846072</v>
+        <v>6846109</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3519,19 +3510,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755840</v>
+        <v>125740970</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3562,14 +3553,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523595</v>
+        <v>523383</v>
       </c>
       <c r="R31" t="n">
-        <v>6846194</v>
+        <v>6846110</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,19 +3607,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125740278</v>
+        <v>125742499</v>
       </c>
       <c r="B32" t="n">
         <v>78973</v>
@@ -3659,17 +3650,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523522</v>
+        <v>523622</v>
       </c>
       <c r="R32" t="n">
-        <v>6846208</v>
+        <v>6846233</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3713,44 +3704,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125742754</v>
+        <v>125755833</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523569</v>
+        <v>523511</v>
       </c>
       <c r="R33" t="n">
-        <v>6846303</v>
+        <v>6846118</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3810,19 +3801,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755877</v>
+        <v>125755848</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3857,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523461</v>
+        <v>523515</v>
       </c>
       <c r="R34" t="n">
-        <v>6846105</v>
+        <v>6846181</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3919,7 +3910,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755853</v>
+        <v>125755879</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3954,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523425</v>
+        <v>523502</v>
       </c>
       <c r="R35" t="n">
-        <v>6846130</v>
+        <v>6846082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,10 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125740942</v>
+        <v>125755873</v>
       </c>
       <c r="B36" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523475</v>
+        <v>523443</v>
       </c>
       <c r="R36" t="n">
-        <v>6846068</v>
+        <v>6846083</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4101,44 +4092,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125740148</v>
+        <v>125755813</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>97223</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4139,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523497</v>
+        <v>523458</v>
       </c>
       <c r="R37" t="n">
-        <v>6846271</v>
+        <v>6846106</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,57 +4189,66 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755857</v>
+        <v>125755831</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523398</v>
+        <v>523491</v>
       </c>
       <c r="R38" t="n">
-        <v>6846095</v>
+        <v>6846097</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755890</v>
+        <v>125740933</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4318,37 +4318,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523496</v>
+        <v>523405</v>
       </c>
       <c r="R39" t="n">
-        <v>6846308</v>
+        <v>6846104</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4392,19 +4392,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755881</v>
+        <v>125755859</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523499</v>
+        <v>523396</v>
       </c>
       <c r="R40" t="n">
-        <v>6846107</v>
+        <v>6846092</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755901</v>
+        <v>125755878</v>
       </c>
       <c r="B41" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523588</v>
+        <v>523484</v>
       </c>
       <c r="R41" t="n">
-        <v>6846217</v>
+        <v>6846075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755814</v>
+        <v>125755823</v>
       </c>
       <c r="B42" t="n">
-        <v>92720</v>
+        <v>78732</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523456</v>
+        <v>523377</v>
       </c>
       <c r="R42" t="n">
-        <v>6846109</v>
+        <v>6846073</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125740970</v>
+        <v>125755798</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,34 +4706,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523383</v>
+        <v>523586</v>
       </c>
       <c r="R43" t="n">
-        <v>6846110</v>
+        <v>6846194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4785,19 +4780,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125742499</v>
+        <v>125755875</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4828,17 +4823,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523622</v>
+        <v>523436</v>
       </c>
       <c r="R44" t="n">
-        <v>6846233</v>
+        <v>6846102</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4882,44 +4877,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755833</v>
+        <v>125755806</v>
       </c>
       <c r="B45" t="n">
-        <v>91399</v>
+        <v>79005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4924,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523511</v>
+        <v>523381</v>
       </c>
       <c r="R45" t="n">
-        <v>6846118</v>
+        <v>6846064</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,45 +4986,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755848</v>
+        <v>125755828</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523515</v>
+        <v>523512</v>
       </c>
       <c r="R46" t="n">
-        <v>6846181</v>
+        <v>6846071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,7 +5092,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755879</v>
+        <v>125740221</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5119,17 +5123,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523502</v>
+        <v>523538</v>
       </c>
       <c r="R47" t="n">
-        <v>6846082</v>
+        <v>6846149</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5173,22 +5177,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755873</v>
+        <v>125740764</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,37 +5200,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846083</v>
+        <v>6846070</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5270,44 +5274,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755813</v>
+        <v>125755863</v>
       </c>
       <c r="B49" t="n">
-        <v>97223</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5317,10 +5321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523458</v>
+        <v>523376</v>
       </c>
       <c r="R49" t="n">
-        <v>6846106</v>
+        <v>6846074</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5379,54 +5383,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755831</v>
+        <v>125755880</v>
       </c>
       <c r="B50" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523491</v>
+        <v>523488</v>
       </c>
       <c r="R50" t="n">
-        <v>6846097</v>
+        <v>6846089</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5485,10 +5480,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125740933</v>
+        <v>125755846</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5496,37 +5491,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523405</v>
+        <v>523604</v>
       </c>
       <c r="R51" t="n">
-        <v>6846104</v>
+        <v>6846240</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5570,19 +5565,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755859</v>
+        <v>125755854</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5617,10 +5612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523396</v>
+        <v>523410</v>
       </c>
       <c r="R52" t="n">
-        <v>6846092</v>
+        <v>6846112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5679,10 +5674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755878</v>
+        <v>125755796</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5690,21 +5685,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5714,10 +5709,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523484</v>
+        <v>523627</v>
       </c>
       <c r="R53" t="n">
-        <v>6846075</v>
+        <v>6846239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5776,7 +5771,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125740194</v>
+        <v>125755882</v>
       </c>
       <c r="B54" t="n">
         <v>78973</v>
@@ -5811,10 +5806,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523518</v>
+        <v>523515</v>
       </c>
       <c r="R54" t="n">
-        <v>6846232</v>
+        <v>6846106</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5861,22 +5856,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125742527</v>
+        <v>125755805</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5884,21 +5879,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5908,10 +5903,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523403</v>
+        <v>523478</v>
       </c>
       <c r="R55" t="n">
-        <v>6846072</v>
+        <v>6846168</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5958,22 +5953,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755823</v>
+        <v>125755804</v>
       </c>
       <c r="B56" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,21 +5976,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6005,10 +6000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523377</v>
+        <v>523485</v>
       </c>
       <c r="R56" t="n">
-        <v>6846073</v>
+        <v>6846156</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6067,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755798</v>
+        <v>125755891</v>
       </c>
       <c r="B57" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6078,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6102,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523586</v>
+        <v>523501</v>
       </c>
       <c r="R57" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6164,10 +6159,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755806</v>
+        <v>125755843</v>
       </c>
       <c r="B58" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6175,21 +6170,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6199,10 +6194,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523381</v>
+        <v>523662</v>
       </c>
       <c r="R58" t="n">
-        <v>6846064</v>
+        <v>6846272</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6261,54 +6256,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755828</v>
+        <v>125755826</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>78731</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523512</v>
+        <v>523408</v>
       </c>
       <c r="R59" t="n">
-        <v>6846071</v>
+        <v>6846116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6367,10 +6353,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125740221</v>
+        <v>125755817</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6378,37 +6364,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523538</v>
+        <v>523587</v>
       </c>
       <c r="R60" t="n">
-        <v>6846149</v>
+        <v>6846194</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6452,19 +6438,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755875</v>
+        <v>125755862</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6499,10 +6485,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523436</v>
+        <v>523377</v>
       </c>
       <c r="R61" t="n">
-        <v>6846102</v>
+        <v>6846085</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6561,10 +6547,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125740764</v>
+        <v>125755858</v>
       </c>
       <c r="B62" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6572,37 +6558,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523443</v>
+        <v>523393</v>
       </c>
       <c r="R62" t="n">
-        <v>6846070</v>
+        <v>6846095</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6646,19 +6632,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755863</v>
+        <v>125755852</v>
       </c>
       <c r="B63" t="n">
         <v>78973</v>
@@ -6693,10 +6679,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523376</v>
+        <v>523420</v>
       </c>
       <c r="R63" t="n">
-        <v>6846074</v>
+        <v>6846145</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6755,7 +6741,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755880</v>
+        <v>125755883</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -6790,10 +6776,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523488</v>
+        <v>523485</v>
       </c>
       <c r="R64" t="n">
-        <v>6846089</v>
+        <v>6846121</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6852,7 +6838,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755846</v>
+        <v>125755855</v>
       </c>
       <c r="B65" t="n">
         <v>78973</v>
@@ -6887,10 +6873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523604</v>
+        <v>523410</v>
       </c>
       <c r="R65" t="n">
-        <v>6846240</v>
+        <v>6846095</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6949,32 +6935,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755854</v>
+        <v>125755897</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6984,10 +6970,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523410</v>
+        <v>523669</v>
       </c>
       <c r="R66" t="n">
-        <v>6846112</v>
+        <v>6846274</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7046,10 +7032,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755796</v>
+        <v>125755847</v>
       </c>
       <c r="B67" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7057,21 +7043,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7081,10 +7067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523627</v>
+        <v>523553</v>
       </c>
       <c r="R67" t="n">
-        <v>6846239</v>
+        <v>6846192</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7143,7 +7129,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755882</v>
+        <v>125740592</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7174,17 +7160,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523515</v>
+        <v>523450</v>
       </c>
       <c r="R68" t="n">
-        <v>6846106</v>
+        <v>6846113</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7228,22 +7214,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755805</v>
+        <v>125755841</v>
       </c>
       <c r="B69" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7251,21 +7237,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7275,10 +7261,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523478</v>
+        <v>523605</v>
       </c>
       <c r="R69" t="n">
-        <v>6846168</v>
+        <v>6846199</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7337,32 +7323,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755804</v>
+        <v>125755898</v>
       </c>
       <c r="B70" t="n">
-        <v>79591</v>
+        <v>92528</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7372,10 +7358,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523485</v>
+        <v>523635</v>
       </c>
       <c r="R70" t="n">
-        <v>6846156</v>
+        <v>6846293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7434,7 +7420,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125740179</v>
+        <v>125755837</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7469,10 +7455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523507</v>
+        <v>523530</v>
       </c>
       <c r="R71" t="n">
-        <v>6846247</v>
+        <v>6846281</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7519,22 +7505,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755891</v>
+        <v>125755827</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7542,21 +7528,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7569,7 +7555,7 @@
         <v>523501</v>
       </c>
       <c r="R72" t="n">
-        <v>6846327</v>
+        <v>6846078</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7628,7 +7614,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755843</v>
+        <v>125755888</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7663,10 +7649,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523662</v>
+        <v>523478</v>
       </c>
       <c r="R73" t="n">
-        <v>6846272</v>
+        <v>6846168</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7725,10 +7711,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755826</v>
+        <v>125755886</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7736,21 +7722,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7760,10 +7746,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523408</v>
+        <v>523485</v>
       </c>
       <c r="R74" t="n">
-        <v>6846116</v>
+        <v>6846156</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7822,10 +7808,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755817</v>
+        <v>125755889</v>
       </c>
       <c r="B75" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7833,21 +7819,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7857,10 +7843,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523587</v>
+        <v>523490</v>
       </c>
       <c r="R75" t="n">
-        <v>6846194</v>
+        <v>6846171</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7919,32 +7905,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755897</v>
+        <v>125755905</v>
       </c>
       <c r="B76" t="n">
-        <v>92528</v>
+        <v>78640</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7954,10 +7940,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523669</v>
+        <v>523497</v>
       </c>
       <c r="R76" t="n">
-        <v>6846274</v>
+        <v>6846102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8016,10 +8002,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755847</v>
+        <v>125755904</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8027,21 +8013,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8051,10 +8037,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523553</v>
+        <v>523504</v>
       </c>
       <c r="R77" t="n">
-        <v>6846192</v>
+        <v>6846179</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8113,7 +8099,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755841</v>
+        <v>125755885</v>
       </c>
       <c r="B78" t="n">
         <v>78973</v>
@@ -8148,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523605</v>
+        <v>523473</v>
       </c>
       <c r="R78" t="n">
-        <v>6846199</v>
+        <v>6846151</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8210,10 +8196,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755862</v>
+        <v>125755825</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8221,21 +8207,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8245,10 +8231,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523377</v>
+        <v>523628</v>
       </c>
       <c r="R79" t="n">
-        <v>6846085</v>
+        <v>6846224</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8307,10 +8293,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755852</v>
+        <v>125755819</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8318,21 +8304,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8342,10 +8328,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523420</v>
+        <v>523628</v>
       </c>
       <c r="R80" t="n">
-        <v>6846145</v>
+        <v>6846238</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8404,7 +8390,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755883</v>
+        <v>125755884</v>
       </c>
       <c r="B81" t="n">
         <v>78973</v>
@@ -8439,10 +8425,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523485</v>
+        <v>523471</v>
       </c>
       <c r="R81" t="n">
-        <v>6846121</v>
+        <v>6846134</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8501,7 +8487,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755858</v>
+        <v>125755849</v>
       </c>
       <c r="B82" t="n">
         <v>78973</v>
@@ -8536,10 +8522,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523393</v>
+        <v>523414</v>
       </c>
       <c r="R82" t="n">
-        <v>6846095</v>
+        <v>6846169</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8598,7 +8584,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755855</v>
+        <v>125755834</v>
       </c>
       <c r="B83" t="n">
         <v>78973</v>
@@ -8633,10 +8619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523410</v>
+        <v>523489</v>
       </c>
       <c r="R83" t="n">
-        <v>6846095</v>
+        <v>6846326</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8695,7 +8681,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125740592</v>
+        <v>125755844</v>
       </c>
       <c r="B84" t="n">
         <v>78973</v>
@@ -8726,17 +8712,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523450</v>
+        <v>523705</v>
       </c>
       <c r="R84" t="n">
-        <v>6846113</v>
+        <v>6846300</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8780,44 +8766,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755898</v>
+        <v>125755845</v>
       </c>
       <c r="B85" t="n">
-        <v>92528</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8827,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523635</v>
+        <v>523663</v>
       </c>
       <c r="R85" t="n">
-        <v>6846293</v>
+        <v>6846295</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8889,7 +8875,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755837</v>
+        <v>125755876</v>
       </c>
       <c r="B86" t="n">
         <v>78973</v>
@@ -8924,10 +8910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523530</v>
+        <v>523457</v>
       </c>
       <c r="R86" t="n">
-        <v>6846281</v>
+        <v>6846106</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8986,10 +8972,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755827</v>
+        <v>125755861</v>
       </c>
       <c r="B87" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8997,21 +8983,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9021,10 +9007,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523501</v>
+        <v>523389</v>
       </c>
       <c r="R87" t="n">
-        <v>6846078</v>
+        <v>6846092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9083,7 +9069,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755888</v>
+        <v>125755887</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9118,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523478</v>
+        <v>523473</v>
       </c>
       <c r="R88" t="n">
-        <v>6846168</v>
+        <v>6846157</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9180,10 +9166,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755886</v>
+        <v>125755903</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9191,21 +9177,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9215,10 +9201,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523485</v>
+        <v>523586</v>
       </c>
       <c r="R89" t="n">
-        <v>6846156</v>
+        <v>6846193</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9277,7 +9263,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755889</v>
+        <v>125742574</v>
       </c>
       <c r="B90" t="n">
         <v>78973</v>
@@ -9308,17 +9294,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523490</v>
+        <v>523592</v>
       </c>
       <c r="R90" t="n">
-        <v>6846171</v>
+        <v>6846248</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9362,22 +9348,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755905</v>
+        <v>125755820</v>
       </c>
       <c r="B91" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9385,21 +9371,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9409,10 +9395,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523497</v>
+        <v>523410</v>
       </c>
       <c r="R91" t="n">
-        <v>6846102</v>
+        <v>6846112</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,10 +9457,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755904</v>
+        <v>125740307</v>
       </c>
       <c r="B92" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9482,21 +9468,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9506,10 +9492,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523504</v>
+        <v>523527</v>
       </c>
       <c r="R92" t="n">
-        <v>6846179</v>
+        <v>6846185</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9556,22 +9542,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755885</v>
+        <v>125742098</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9565,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523473</v>
+        <v>523403</v>
       </c>
       <c r="R93" t="n">
-        <v>6846151</v>
+        <v>6846072</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9653,22 +9639,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755825</v>
+        <v>125741230</v>
       </c>
       <c r="B94" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9676,21 +9662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9700,10 +9686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523628</v>
+        <v>523475</v>
       </c>
       <c r="R94" t="n">
-        <v>6846224</v>
+        <v>6846068</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9750,19 +9736,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755819</v>
+        <v>125741174</v>
       </c>
       <c r="B95" t="n">
         <v>78732</v>
@@ -9797,10 +9783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523628</v>
+        <v>523475</v>
       </c>
       <c r="R95" t="n">
-        <v>6846238</v>
+        <v>6846068</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9847,19 +9833,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755884</v>
+        <v>125742564</v>
       </c>
       <c r="B96" t="n">
         <v>78973</v>
@@ -9894,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523471</v>
+        <v>523612</v>
       </c>
       <c r="R96" t="n">
-        <v>6846134</v>
+        <v>6846245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9944,19 +9930,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755849</v>
+        <v>125742673</v>
       </c>
       <c r="B97" t="n">
         <v>78973</v>
@@ -9991,10 +9977,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523414</v>
+        <v>523590</v>
       </c>
       <c r="R97" t="n">
-        <v>6846169</v>
+        <v>6846277</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10041,22 +10027,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755834</v>
+        <v>125741338</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10064,21 +10050,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10088,10 +10074,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523489</v>
+        <v>523403</v>
       </c>
       <c r="R98" t="n">
-        <v>6846326</v>
+        <v>6846072</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10138,57 +10124,73 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755844</v>
+        <v>125742433</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523705</v>
+        <v>523403</v>
       </c>
       <c r="R99" t="n">
-        <v>6846300</v>
+        <v>6846072</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10235,22 +10237,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755845</v>
+        <v>125740942</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10258,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10282,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523663</v>
+        <v>523475</v>
       </c>
       <c r="R100" t="n">
-        <v>6846295</v>
+        <v>6846068</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10332,19 +10334,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755876</v>
+        <v>125740278</v>
       </c>
       <c r="B101" t="n">
         <v>78973</v>
@@ -10379,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523457</v>
+        <v>523522</v>
       </c>
       <c r="R101" t="n">
-        <v>6846106</v>
+        <v>6846208</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10429,19 +10431,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755861</v>
+        <v>125742754</v>
       </c>
       <c r="B102" t="n">
         <v>78973</v>
@@ -10476,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523389</v>
+        <v>523569</v>
       </c>
       <c r="R102" t="n">
-        <v>6846092</v>
+        <v>6846303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10526,19 +10528,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755887</v>
+        <v>125740148</v>
       </c>
       <c r="B103" t="n">
         <v>78973</v>
@@ -10573,10 +10575,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R103" t="n">
-        <v>6846157</v>
+        <v>6846271</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10623,22 +10625,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755903</v>
+        <v>125742527</v>
       </c>
       <c r="B104" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10646,21 +10648,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10670,10 +10672,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523586</v>
+        <v>523403</v>
       </c>
       <c r="R104" t="n">
-        <v>6846193</v>
+        <v>6846072</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10720,19 +10722,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125742574</v>
+        <v>125740194</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10763,17 +10765,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523592</v>
+        <v>523518</v>
       </c>
       <c r="R105" t="n">
-        <v>6846248</v>
+        <v>6846232</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10817,22 +10819,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755820</v>
+        <v>125740179</v>
       </c>
       <c r="B106" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10840,21 +10842,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10864,10 +10866,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523410</v>
+        <v>523507</v>
       </c>
       <c r="R106" t="n">
-        <v>6846112</v>
+        <v>6846247</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10914,12 +10916,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125755851</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125755807</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125755824</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,48 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755818</v>
+        <v>125740292</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>98266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523628</v>
+        <v>523521</v>
       </c>
       <c r="R6" t="n">
-        <v>6846224</v>
+        <v>6846131</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,60 +1158,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125740292</v>
+        <v>125755799</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523521</v>
+        <v>523708</v>
       </c>
       <c r="R7" t="n">
-        <v>6846131</v>
+        <v>6846300</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
         <v>125755896</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755799</v>
+        <v>125755818</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523708</v>
+        <v>523628</v>
       </c>
       <c r="R9" t="n">
-        <v>6846300</v>
+        <v>6846224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>125755829</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>125755850</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>125755892</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,37 +1874,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R14" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1948,22 +1953,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B15" t="n">
-        <v>57649</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,42 +1976,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R15" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2050,22 +2050,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755839</v>
+        <v>125755874</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523537</v>
+        <v>523446</v>
       </c>
       <c r="R16" t="n">
-        <v>6846261</v>
+        <v>6846093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
         <v>125755836</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755874</v>
+        <v>125755839</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523446</v>
+        <v>523537</v>
       </c>
       <c r="R18" t="n">
-        <v>6846093</v>
+        <v>6846261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755842</v>
+        <v>125755909</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>91829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523656</v>
+        <v>523407</v>
       </c>
       <c r="R19" t="n">
-        <v>6846239</v>
+        <v>6846172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R20" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,32 +2547,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755909</v>
+        <v>125755842</v>
       </c>
       <c r="B21" t="n">
-        <v>91825</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523407</v>
+        <v>523656</v>
       </c>
       <c r="R21" t="n">
-        <v>6846172</v>
+        <v>6846239</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755802</v>
+        <v>125755864</v>
       </c>
       <c r="B22" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523478</v>
+        <v>523381</v>
       </c>
       <c r="R22" t="n">
-        <v>6846087</v>
+        <v>6846064</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755877</v>
+        <v>125755853</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523461</v>
+        <v>523425</v>
       </c>
       <c r="R23" t="n">
-        <v>6846105</v>
+        <v>6846130</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755853</v>
+        <v>125755877</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523425</v>
+        <v>523461</v>
       </c>
       <c r="R24" t="n">
-        <v>6846130</v>
+        <v>6846105</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>125755840</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>125755857</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>125755890</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755881</v>
+        <v>125755814</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>92724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,21 +3237,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523499</v>
+        <v>523456</v>
       </c>
       <c r="R28" t="n">
-        <v>6846107</v>
+        <v>6846109</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755901</v>
+        <v>125740970</v>
       </c>
       <c r="B29" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,34 +3334,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523588</v>
+        <v>523383</v>
       </c>
       <c r="R29" t="n">
-        <v>6846217</v>
+        <v>6846110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,11 +3396,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3413,22 +3408,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755814</v>
+        <v>125742499</v>
       </c>
       <c r="B30" t="n">
-        <v>92720</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3436,37 +3431,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523456</v>
+        <v>523622</v>
       </c>
       <c r="R30" t="n">
-        <v>6846109</v>
+        <v>6846233</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3510,22 +3505,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3533,34 +3528,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R31" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,6 +3590,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3607,22 +3607,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125742499</v>
+        <v>125755881</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523622</v>
+        <v>523499</v>
       </c>
       <c r="R32" t="n">
-        <v>6846233</v>
+        <v>6846107</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3704,60 +3704,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755833</v>
+        <v>125740933</v>
       </c>
       <c r="B33" t="n">
-        <v>91399</v>
+        <v>78736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523511</v>
+        <v>523405</v>
       </c>
       <c r="R33" t="n">
-        <v>6846118</v>
+        <v>6846104</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,44 +3801,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755848</v>
+        <v>125755833</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>91403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523515</v>
+        <v>523511</v>
       </c>
       <c r="R34" t="n">
-        <v>6846181</v>
+        <v>6846118</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
         <v>125755879</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125755873</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,32 +4104,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755813</v>
+        <v>125755848</v>
       </c>
       <c r="B37" t="n">
-        <v>97223</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523458</v>
+        <v>523515</v>
       </c>
       <c r="R37" t="n">
-        <v>6846106</v>
+        <v>6846181</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4204,7 +4204,7 @@
         <v>125755831</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,48 +4307,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125740933</v>
+        <v>125755813</v>
       </c>
       <c r="B39" t="n">
-        <v>78732</v>
+        <v>97227</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523405</v>
+        <v>523458</v>
       </c>
       <c r="R39" t="n">
-        <v>6846104</v>
+        <v>6846106</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4392,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755859</v>
+        <v>125755823</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523396</v>
+        <v>523377</v>
       </c>
       <c r="R40" t="n">
-        <v>6846092</v>
+        <v>6846073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4504,7 +4504,7 @@
         <v>125755878</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755823</v>
+        <v>125755798</v>
       </c>
       <c r="B42" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523377</v>
+        <v>523586</v>
       </c>
       <c r="R42" t="n">
-        <v>6846073</v>
+        <v>6846194</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755798</v>
+        <v>125755859</v>
       </c>
       <c r="B43" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523586</v>
+        <v>523396</v>
       </c>
       <c r="R43" t="n">
-        <v>6846194</v>
+        <v>6846092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755875</v>
+        <v>125755806</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79009</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523436</v>
+        <v>523381</v>
       </c>
       <c r="R44" t="n">
-        <v>6846102</v>
+        <v>6846064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4889,45 +4889,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755806</v>
+        <v>125755828</v>
       </c>
       <c r="B45" t="n">
-        <v>79005</v>
+        <v>98349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523381</v>
+        <v>523512</v>
       </c>
       <c r="R45" t="n">
-        <v>6846064</v>
+        <v>6846071</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4986,54 +4995,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B46" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R46" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5095,7 +5095,7 @@
         <v>125740221</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125740764</v>
+        <v>125755796</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5200,37 +5200,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523443</v>
+        <v>523627</v>
       </c>
       <c r="R48" t="n">
-        <v>6846070</v>
+        <v>6846239</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5274,22 +5274,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755863</v>
+        <v>125755854</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523376</v>
+        <v>523410</v>
       </c>
       <c r="R49" t="n">
-        <v>6846074</v>
+        <v>6846112</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755880</v>
+        <v>125740764</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5394,37 +5394,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523488</v>
+        <v>523443</v>
       </c>
       <c r="R50" t="n">
-        <v>6846089</v>
+        <v>6846070</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5468,12 +5468,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
         <v>125755846</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R52" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755796</v>
+        <v>125755880</v>
       </c>
       <c r="B53" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523627</v>
+        <v>523488</v>
       </c>
       <c r="R53" t="n">
-        <v>6846239</v>
+        <v>6846089</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755882</v>
+        <v>125755804</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523515</v>
+        <v>523485</v>
       </c>
       <c r="R54" t="n">
-        <v>6846106</v>
+        <v>6846156</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5871,7 +5871,7 @@
         <v>125755805</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5965,10 +5965,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755804</v>
+        <v>125755882</v>
       </c>
       <c r="B56" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5976,21 +5976,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523485</v>
+        <v>523515</v>
       </c>
       <c r="R56" t="n">
-        <v>6846156</v>
+        <v>6846106</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755891</v>
+        <v>125755826</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523501</v>
+        <v>523408</v>
       </c>
       <c r="R57" t="n">
-        <v>6846327</v>
+        <v>6846116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,7 +6162,7 @@
         <v>125755843</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755826</v>
+        <v>125755891</v>
       </c>
       <c r="B59" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523408</v>
+        <v>523501</v>
       </c>
       <c r="R59" t="n">
-        <v>6846116</v>
+        <v>6846327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
         <v>125755817</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755862</v>
+        <v>125740592</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6481,17 +6481,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523377</v>
+        <v>523450</v>
       </c>
       <c r="R61" t="n">
-        <v>6846085</v>
+        <v>6846113</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6535,22 +6535,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755858</v>
+        <v>125755883</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523393</v>
+        <v>523485</v>
       </c>
       <c r="R62" t="n">
-        <v>6846095</v>
+        <v>6846121</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6644,10 +6644,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755852</v>
+        <v>125755841</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523420</v>
+        <v>523605</v>
       </c>
       <c r="R63" t="n">
-        <v>6846145</v>
+        <v>6846199</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6741,10 +6741,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755883</v>
+        <v>125755855</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523485</v>
+        <v>523410</v>
       </c>
       <c r="R64" t="n">
-        <v>6846121</v>
+        <v>6846095</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6838,32 +6838,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755855</v>
+        <v>125755897</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523410</v>
+        <v>523669</v>
       </c>
       <c r="R65" t="n">
-        <v>6846095</v>
+        <v>6846274</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6935,32 +6935,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755897</v>
+        <v>125755862</v>
       </c>
       <c r="B66" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523669</v>
+        <v>523377</v>
       </c>
       <c r="R66" t="n">
-        <v>6846274</v>
+        <v>6846085</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755847</v>
+        <v>125755852</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523553</v>
+        <v>523420</v>
       </c>
       <c r="R67" t="n">
-        <v>6846192</v>
+        <v>6846145</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7129,10 +7129,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125740592</v>
+        <v>125755847</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7160,17 +7160,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523450</v>
+        <v>523553</v>
       </c>
       <c r="R68" t="n">
-        <v>6846113</v>
+        <v>6846192</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7214,22 +7214,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755841</v>
+        <v>125755858</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7261,10 +7261,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523605</v>
+        <v>523393</v>
       </c>
       <c r="R69" t="n">
-        <v>6846199</v>
+        <v>6846095</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7323,32 +7323,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755898</v>
+        <v>125755827</v>
       </c>
       <c r="B70" t="n">
-        <v>92528</v>
+        <v>78735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523635</v>
+        <v>523501</v>
       </c>
       <c r="R70" t="n">
-        <v>6846293</v>
+        <v>6846078</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755837</v>
+        <v>125755888</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523530</v>
+        <v>523478</v>
       </c>
       <c r="R71" t="n">
-        <v>6846281</v>
+        <v>6846168</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755827</v>
+        <v>125755837</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7528,21 +7528,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523501</v>
+        <v>523530</v>
       </c>
       <c r="R72" t="n">
-        <v>6846078</v>
+        <v>6846281</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7614,32 +7614,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755888</v>
+        <v>125755898</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523478</v>
+        <v>523635</v>
       </c>
       <c r="R73" t="n">
-        <v>6846168</v>
+        <v>6846293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7714,7 +7714,7 @@
         <v>125755886</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>125755889</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755905</v>
+        <v>125755825</v>
       </c>
       <c r="B76" t="n">
-        <v>78640</v>
+        <v>78735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7916,21 +7916,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523497</v>
+        <v>523628</v>
       </c>
       <c r="R76" t="n">
-        <v>6846102</v>
+        <v>6846224</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8002,10 +8002,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B77" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8013,21 +8013,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R77" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755885</v>
+        <v>125755905</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523473</v>
+        <v>523497</v>
       </c>
       <c r="R78" t="n">
-        <v>6846151</v>
+        <v>6846102</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755825</v>
+        <v>125755885</v>
       </c>
       <c r="B79" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8207,21 +8207,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523628</v>
+        <v>523473</v>
       </c>
       <c r="R79" t="n">
-        <v>6846224</v>
+        <v>6846151</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8293,10 +8293,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755819</v>
+        <v>125755904</v>
       </c>
       <c r="B80" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8304,21 +8304,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8328,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R80" t="n">
-        <v>6846238</v>
+        <v>6846179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8390,10 +8390,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755884</v>
+        <v>125755849</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8425,10 +8425,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523471</v>
+        <v>523414</v>
       </c>
       <c r="R81" t="n">
-        <v>6846134</v>
+        <v>6846169</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8487,10 +8487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755849</v>
+        <v>125755884</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523414</v>
+        <v>523471</v>
       </c>
       <c r="R82" t="n">
-        <v>6846169</v>
+        <v>6846134</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8584,10 +8584,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755834</v>
+        <v>125755844</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523489</v>
+        <v>523705</v>
       </c>
       <c r="R83" t="n">
-        <v>6846326</v>
+        <v>6846300</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8681,10 +8681,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755844</v>
+        <v>125755861</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523705</v>
+        <v>523389</v>
       </c>
       <c r="R84" t="n">
-        <v>6846300</v>
+        <v>6846092</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8778,10 +8778,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755845</v>
+        <v>125755834</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523663</v>
+        <v>523489</v>
       </c>
       <c r="R85" t="n">
-        <v>6846295</v>
+        <v>6846326</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8875,10 +8875,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755876</v>
+        <v>125755845</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523457</v>
+        <v>523663</v>
       </c>
       <c r="R86" t="n">
-        <v>6846106</v>
+        <v>6846295</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755861</v>
+        <v>125755876</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523389</v>
+        <v>523457</v>
       </c>
       <c r="R87" t="n">
-        <v>6846092</v>
+        <v>6846106</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9100,17 +9100,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R88" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9154,12 +9154,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
         <v>125755903</v>
       </c>
       <c r="B89" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125742574</v>
+        <v>125755887</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9294,17 +9294,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523592</v>
+        <v>523473</v>
       </c>
       <c r="R90" t="n">
-        <v>6846248</v>
+        <v>6846157</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9348,12 +9348,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9363,7 +9363,7 @@
         <v>125755820</v>
       </c>
       <c r="B91" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>125740307</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9554,10 +9554,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B93" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9565,21 +9565,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R93" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9651,10 +9651,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125741230</v>
+        <v>125742098</v>
       </c>
       <c r="B94" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9662,21 +9662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523475</v>
+        <v>523403</v>
       </c>
       <c r="R94" t="n">
-        <v>6846068</v>
+        <v>6846072</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9748,10 +9748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125741174</v>
+        <v>125742564</v>
       </c>
       <c r="B95" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9759,21 +9759,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523475</v>
+        <v>523612</v>
       </c>
       <c r="R95" t="n">
-        <v>6846068</v>
+        <v>6846245</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9845,10 +9845,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R96" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
         <v>125742673</v>
       </c>
       <c r="B97" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>125741338</v>
       </c>
       <c r="B98" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>125742433</v>
       </c>
       <c r="B99" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B100" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R100" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,10 +10346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125740278</v>
+        <v>125742754</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523522</v>
+        <v>523569</v>
       </c>
       <c r="R101" t="n">
-        <v>6846208</v>
+        <v>6846303</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125742754</v>
+        <v>125740942</v>
       </c>
       <c r="B102" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523569</v>
+        <v>523475</v>
       </c>
       <c r="R102" t="n">
-        <v>6846303</v>
+        <v>6846068</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10543,7 +10543,7 @@
         <v>125740148</v>
       </c>
       <c r="B103" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125742527</v>
+        <v>125740194</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10672,10 +10672,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523403</v>
+        <v>523518</v>
       </c>
       <c r="R104" t="n">
-        <v>6846072</v>
+        <v>6846232</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10734,10 +10734,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125740194</v>
+        <v>125742527</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523518</v>
+        <v>523403</v>
       </c>
       <c r="R105" t="n">
-        <v>6846232</v>
+        <v>6846072</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10834,7 +10834,7 @@
         <v>125740179</v>
       </c>
       <c r="B106" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1073,48 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125740292</v>
+        <v>125755799</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523521</v>
+        <v>523708</v>
       </c>
       <c r="R6" t="n">
-        <v>6846131</v>
+        <v>6846300</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755799</v>
+        <v>125755896</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523708</v>
+        <v>523465</v>
       </c>
       <c r="R7" t="n">
-        <v>6846300</v>
+        <v>6846335</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755896</v>
+        <v>125740292</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>98266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523465</v>
+        <v>523521</v>
       </c>
       <c r="R8" t="n">
-        <v>6846335</v>
+        <v>6846131</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,34 +3334,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R29" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,6 +3396,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3408,19 +3413,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125742499</v>
+        <v>125755881</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3451,17 +3456,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523622</v>
+        <v>523499</v>
       </c>
       <c r="R30" t="n">
-        <v>6846233</v>
+        <v>6846107</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3505,22 +3510,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755901</v>
+        <v>125740970</v>
       </c>
       <c r="B31" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3528,34 +3533,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523588</v>
+        <v>523383</v>
       </c>
       <c r="R31" t="n">
-        <v>6846217</v>
+        <v>6846110</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,11 +3595,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3607,19 +3607,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B32" t="n">
         <v>78977</v>
@@ -3650,17 +3650,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R32" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3704,12 +3704,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755878</v>
+        <v>125755859</v>
       </c>
       <c r="B41" t="n">
         <v>78977</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523484</v>
+        <v>523396</v>
       </c>
       <c r="R41" t="n">
-        <v>6846075</v>
+        <v>6846092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R43" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755796</v>
+        <v>125740764</v>
       </c>
       <c r="B48" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5200,37 +5200,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523627</v>
+        <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846239</v>
+        <v>6846070</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5274,22 +5274,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755854</v>
+        <v>125755796</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523410</v>
+        <v>523627</v>
       </c>
       <c r="R49" t="n">
-        <v>6846112</v>
+        <v>6846239</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125740764</v>
+        <v>125755854</v>
       </c>
       <c r="B50" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5394,37 +5394,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523443</v>
+        <v>523410</v>
       </c>
       <c r="R50" t="n">
-        <v>6846070</v>
+        <v>6846112</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5468,12 +5468,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755826</v>
+        <v>125755817</v>
       </c>
       <c r="B57" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523408</v>
+        <v>523587</v>
       </c>
       <c r="R57" t="n">
-        <v>6846116</v>
+        <v>6846194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755843</v>
+        <v>125755826</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6170,21 +6170,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523662</v>
+        <v>523408</v>
       </c>
       <c r="R58" t="n">
-        <v>6846272</v>
+        <v>6846116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755891</v>
+        <v>125755843</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523501</v>
+        <v>523662</v>
       </c>
       <c r="R59" t="n">
-        <v>6846327</v>
+        <v>6846272</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B60" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R60" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6547,32 +6547,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755883</v>
+        <v>125755897</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523485</v>
+        <v>523669</v>
       </c>
       <c r="R62" t="n">
-        <v>6846121</v>
+        <v>6846274</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755841</v>
+        <v>125755862</v>
       </c>
       <c r="B63" t="n">
         <v>78977</v>
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523605</v>
+        <v>523377</v>
       </c>
       <c r="R63" t="n">
-        <v>6846199</v>
+        <v>6846085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755855</v>
+        <v>125755852</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523410</v>
+        <v>523420</v>
       </c>
       <c r="R64" t="n">
-        <v>6846095</v>
+        <v>6846145</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6838,32 +6838,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755897</v>
+        <v>125755847</v>
       </c>
       <c r="B65" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523669</v>
+        <v>523553</v>
       </c>
       <c r="R65" t="n">
-        <v>6846274</v>
+        <v>6846192</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755862</v>
+        <v>125755858</v>
       </c>
       <c r="B66" t="n">
         <v>78977</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523377</v>
+        <v>523393</v>
       </c>
       <c r="R66" t="n">
-        <v>6846085</v>
+        <v>6846095</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755852</v>
+        <v>125755883</v>
       </c>
       <c r="B67" t="n">
         <v>78977</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523420</v>
+        <v>523485</v>
       </c>
       <c r="R67" t="n">
-        <v>6846145</v>
+        <v>6846121</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755847</v>
+        <v>125755841</v>
       </c>
       <c r="B68" t="n">
         <v>78977</v>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523553</v>
+        <v>523605</v>
       </c>
       <c r="R68" t="n">
-        <v>6846192</v>
+        <v>6846199</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755858</v>
+        <v>125755855</v>
       </c>
       <c r="B69" t="n">
         <v>78977</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523393</v>
+        <v>523410</v>
       </c>
       <c r="R69" t="n">
         <v>6846095</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9080,37 +9080,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R88" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9154,22 +9154,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755903</v>
+        <v>125742574</v>
       </c>
       <c r="B89" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9177,37 +9177,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523586</v>
+        <v>523592</v>
       </c>
       <c r="R89" t="n">
-        <v>6846193</v>
+        <v>6846248</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9251,22 +9251,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755887</v>
+        <v>125755903</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9274,21 +9274,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523473</v>
+        <v>523586</v>
       </c>
       <c r="R90" t="n">
-        <v>6846157</v>
+        <v>6846193</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755820</v>
+        <v>125755887</v>
       </c>
       <c r="B91" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9371,21 +9371,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9395,10 +9395,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523410</v>
+        <v>523473</v>
       </c>
       <c r="R91" t="n">
-        <v>6846112</v>
+        <v>6846157</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740278</v>
+        <v>125740942</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523522</v>
+        <v>523475</v>
       </c>
       <c r="R100" t="n">
-        <v>6846208</v>
+        <v>6846068</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125742754</v>
+        <v>125740278</v>
       </c>
       <c r="B101" t="n">
         <v>78977</v>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523569</v>
+        <v>523522</v>
       </c>
       <c r="R101" t="n">
-        <v>6846303</v>
+        <v>6846208</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B102" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R102" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755815</v>
+        <v>125755851</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523605</v>
+        <v>523422</v>
       </c>
       <c r="R2" t="n">
-        <v>6846199</v>
+        <v>6846155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,48 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755851</v>
+        <v>125755807</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523422</v>
+        <v>523379</v>
       </c>
       <c r="R3" t="n">
-        <v>6846155</v>
+        <v>6846064</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755807</v>
+        <v>125755815</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,27 +885,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523379</v>
+        <v>523605</v>
       </c>
       <c r="R4" t="n">
-        <v>6846064</v>
+        <v>6846199</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1073,48 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755799</v>
+        <v>125740292</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523708</v>
+        <v>523521</v>
       </c>
       <c r="R6" t="n">
-        <v>6846300</v>
+        <v>6846131</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,22 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755896</v>
+        <v>125755799</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523465</v>
+        <v>523708</v>
       </c>
       <c r="R7" t="n">
-        <v>6846335</v>
+        <v>6846300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125740292</v>
+        <v>125755818</v>
       </c>
       <c r="B8" t="n">
-        <v>98266</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523521</v>
+        <v>523628</v>
       </c>
       <c r="R8" t="n">
-        <v>6846131</v>
+        <v>6846224</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755818</v>
+        <v>125755896</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523628</v>
+        <v>523465</v>
       </c>
       <c r="R9" t="n">
-        <v>6846224</v>
+        <v>6846335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,57 +1454,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755816</v>
+        <v>125755850</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523620</v>
+        <v>523417</v>
       </c>
       <c r="R10" t="n">
-        <v>6846303</v>
+        <v>6846164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,54 +1558,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755829</v>
+        <v>125755892</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523458</v>
+        <v>523495</v>
       </c>
       <c r="R11" t="n">
-        <v>6846108</v>
+        <v>6846328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,45 +1655,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755850</v>
+        <v>125755816</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523417</v>
+        <v>523620</v>
       </c>
       <c r="R12" t="n">
-        <v>6846164</v>
+        <v>6846303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,45 +1757,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755892</v>
+        <v>125755829</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523495</v>
+        <v>523458</v>
       </c>
       <c r="R13" t="n">
-        <v>6846328</v>
+        <v>6846108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755812</v>
+        <v>125740874</v>
       </c>
       <c r="B14" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,42 +1874,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523437</v>
+        <v>523432</v>
       </c>
       <c r="R14" t="n">
-        <v>6846102</v>
+        <v>6846118</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1953,22 +1948,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125740874</v>
+        <v>125755812</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,37 +1971,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523432</v>
+        <v>523437</v>
       </c>
       <c r="R15" t="n">
-        <v>6846118</v>
+        <v>6846102</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2050,12 +2050,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2443,17 +2443,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755802</v>
+        <v>125755842</v>
       </c>
       <c r="B20" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523478</v>
+        <v>523656</v>
       </c>
       <c r="R20" t="n">
-        <v>6846087</v>
+        <v>6846239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755842</v>
+        <v>125755864</v>
       </c>
       <c r="B21" t="n">
         <v>78977</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523656</v>
+        <v>523381</v>
       </c>
       <c r="R21" t="n">
-        <v>6846239</v>
+        <v>6846064</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R22" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755853</v>
+        <v>125755877</v>
       </c>
       <c r="B23" t="n">
         <v>78977</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523425</v>
+        <v>523461</v>
       </c>
       <c r="R23" t="n">
-        <v>6846130</v>
+        <v>6846105</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755877</v>
+        <v>125755853</v>
       </c>
       <c r="B24" t="n">
         <v>78977</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523461</v>
+        <v>523425</v>
       </c>
       <c r="R24" t="n">
-        <v>6846105</v>
+        <v>6846130</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755901</v>
+        <v>125755881</v>
       </c>
       <c r="B29" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523588</v>
+        <v>523499</v>
       </c>
       <c r="R29" t="n">
-        <v>6846217</v>
+        <v>6846107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3394,11 +3394,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3425,7 +3420,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755881</v>
+        <v>125740970</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3456,14 +3451,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523499</v>
+        <v>523383</v>
       </c>
       <c r="R30" t="n">
-        <v>6846107</v>
+        <v>6846110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3510,19 +3505,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740970</v>
+        <v>125742499</v>
       </c>
       <c r="B31" t="n">
         <v>78977</v>
@@ -3557,13 +3552,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523383</v>
+        <v>523622</v>
       </c>
       <c r="R31" t="n">
-        <v>6846110</v>
+        <v>6846233</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3619,10 +3614,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125742499</v>
+        <v>125755901</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3630,37 +3625,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523622</v>
+        <v>523588</v>
       </c>
       <c r="R32" t="n">
-        <v>6846233</v>
+        <v>6846217</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3690,6 +3685,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3704,22 +3704,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125740933</v>
+        <v>125755873</v>
       </c>
       <c r="B33" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,37 +3727,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523405</v>
+        <v>523443</v>
       </c>
       <c r="R33" t="n">
-        <v>6846104</v>
+        <v>6846083</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,12 +3801,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755879</v>
+        <v>125755848</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523502</v>
+        <v>523515</v>
       </c>
       <c r="R35" t="n">
-        <v>6846082</v>
+        <v>6846181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755873</v>
+        <v>125755879</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523443</v>
+        <v>523502</v>
       </c>
       <c r="R36" t="n">
-        <v>6846083</v>
+        <v>6846082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4104,45 +4104,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755848</v>
+        <v>125755831</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523515</v>
+        <v>523491</v>
       </c>
       <c r="R37" t="n">
-        <v>6846181</v>
+        <v>6846097</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4201,54 +4210,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755831</v>
+        <v>125755813</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>97230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523491</v>
+        <v>523458</v>
       </c>
       <c r="R38" t="n">
-        <v>6846097</v>
+        <v>6846106</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,48 +4307,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755813</v>
+        <v>125740933</v>
       </c>
       <c r="B39" t="n">
-        <v>97227</v>
+        <v>78736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523458</v>
+        <v>523405</v>
       </c>
       <c r="R39" t="n">
-        <v>6846106</v>
+        <v>6846104</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4392,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755823</v>
+        <v>125755859</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523377</v>
+        <v>523396</v>
       </c>
       <c r="R40" t="n">
-        <v>6846073</v>
+        <v>6846092</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B41" t="n">
         <v>78977</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R41" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755878</v>
+        <v>125755823</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523484</v>
+        <v>523377</v>
       </c>
       <c r="R43" t="n">
-        <v>6846075</v>
+        <v>6846073</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755806</v>
+        <v>125740221</v>
       </c>
       <c r="B44" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4803,37 +4803,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523381</v>
+        <v>523538</v>
       </c>
       <c r="R44" t="n">
-        <v>6846064</v>
+        <v>6846149</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4877,66 +4877,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755828</v>
+        <v>125755806</v>
       </c>
       <c r="B45" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523512</v>
+        <v>523381</v>
       </c>
       <c r="R45" t="n">
-        <v>6846071</v>
+        <v>6846064</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4995,45 +4986,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R46" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125740221</v>
+        <v>125755875</v>
       </c>
       <c r="B47" t="n">
         <v>78977</v>
@@ -5123,17 +5123,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523538</v>
+        <v>523436</v>
       </c>
       <c r="R47" t="n">
-        <v>6846149</v>
+        <v>6846102</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5177,22 +5177,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125740764</v>
+        <v>125755846</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5200,37 +5200,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523443</v>
+        <v>523604</v>
       </c>
       <c r="R48" t="n">
-        <v>6846070</v>
+        <v>6846240</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5274,22 +5274,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755796</v>
+        <v>125755863</v>
       </c>
       <c r="B49" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523627</v>
+        <v>523376</v>
       </c>
       <c r="R49" t="n">
-        <v>6846239</v>
+        <v>6846074</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755846</v>
+        <v>125755880</v>
       </c>
       <c r="B51" t="n">
         <v>78977</v>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523604</v>
+        <v>523488</v>
       </c>
       <c r="R51" t="n">
-        <v>6846240</v>
+        <v>6846089</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755863</v>
+        <v>125755796</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5588,21 +5588,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523376</v>
+        <v>523627</v>
       </c>
       <c r="R52" t="n">
-        <v>6846074</v>
+        <v>6846239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755880</v>
+        <v>125740764</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5685,37 +5685,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523488</v>
+        <v>523443</v>
       </c>
       <c r="R53" t="n">
-        <v>6846089</v>
+        <v>6846070</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5759,22 +5759,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755804</v>
+        <v>125755882</v>
       </c>
       <c r="B54" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523485</v>
+        <v>523515</v>
       </c>
       <c r="R54" t="n">
-        <v>6846156</v>
+        <v>6846106</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5965,10 +5965,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755882</v>
+        <v>125755804</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5976,21 +5976,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523515</v>
+        <v>523485</v>
       </c>
       <c r="R56" t="n">
-        <v>6846106</v>
+        <v>6846156</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755817</v>
+        <v>125755826</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523587</v>
+        <v>523408</v>
       </c>
       <c r="R57" t="n">
-        <v>6846194</v>
+        <v>6846116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B58" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6170,21 +6170,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R58" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R59" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755891</v>
+        <v>125755817</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523501</v>
+        <v>523587</v>
       </c>
       <c r="R60" t="n">
-        <v>6846327</v>
+        <v>6846194</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755847</v>
+        <v>125755883</v>
       </c>
       <c r="B65" t="n">
         <v>78977</v>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523553</v>
+        <v>523485</v>
       </c>
       <c r="R65" t="n">
-        <v>6846192</v>
+        <v>6846121</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755858</v>
+        <v>125755847</v>
       </c>
       <c r="B66" t="n">
         <v>78977</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523393</v>
+        <v>523553</v>
       </c>
       <c r="R66" t="n">
-        <v>6846095</v>
+        <v>6846192</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755883</v>
+        <v>125755841</v>
       </c>
       <c r="B67" t="n">
         <v>78977</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523485</v>
+        <v>523605</v>
       </c>
       <c r="R67" t="n">
-        <v>6846121</v>
+        <v>6846199</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755841</v>
+        <v>125755855</v>
       </c>
       <c r="B68" t="n">
         <v>78977</v>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523605</v>
+        <v>523410</v>
       </c>
       <c r="R68" t="n">
-        <v>6846199</v>
+        <v>6846095</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755855</v>
+        <v>125755858</v>
       </c>
       <c r="B69" t="n">
         <v>78977</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523410</v>
+        <v>523393</v>
       </c>
       <c r="R69" t="n">
         <v>6846095</v>
@@ -7323,10 +7323,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755827</v>
+        <v>125755837</v>
       </c>
       <c r="B70" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7334,21 +7334,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523501</v>
+        <v>523530</v>
       </c>
       <c r="R70" t="n">
-        <v>6846078</v>
+        <v>6846281</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755888</v>
+        <v>125755827</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523478</v>
+        <v>523501</v>
       </c>
       <c r="R71" t="n">
-        <v>6846168</v>
+        <v>6846078</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7517,32 +7517,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755837</v>
+        <v>125755898</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523530</v>
+        <v>523635</v>
       </c>
       <c r="R72" t="n">
-        <v>6846281</v>
+        <v>6846293</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7607,39 +7607,39 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755898</v>
+        <v>125755888</v>
       </c>
       <c r="B73" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523635</v>
+        <v>523478</v>
       </c>
       <c r="R73" t="n">
-        <v>6846293</v>
+        <v>6846168</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755825</v>
+        <v>125755905</v>
       </c>
       <c r="B76" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7916,21 +7916,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523628</v>
+        <v>523497</v>
       </c>
       <c r="R76" t="n">
-        <v>6846224</v>
+        <v>6846102</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7995,17 +7995,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755819</v>
+        <v>125755904</v>
       </c>
       <c r="B77" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8013,21 +8013,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523628</v>
+        <v>523504</v>
       </c>
       <c r="R77" t="n">
-        <v>6846238</v>
+        <v>6846179</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8092,17 +8092,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755905</v>
+        <v>125755885</v>
       </c>
       <c r="B78" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523497</v>
+        <v>523473</v>
       </c>
       <c r="R78" t="n">
-        <v>6846102</v>
+        <v>6846151</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755885</v>
+        <v>125755825</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8207,21 +8207,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523473</v>
+        <v>523628</v>
       </c>
       <c r="R79" t="n">
-        <v>6846151</v>
+        <v>6846224</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8293,10 +8293,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755904</v>
+        <v>125755819</v>
       </c>
       <c r="B80" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8304,21 +8304,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8328,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523504</v>
+        <v>523628</v>
       </c>
       <c r="R80" t="n">
-        <v>6846179</v>
+        <v>6846238</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8584,7 +8584,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755844</v>
+        <v>125755834</v>
       </c>
       <c r="B83" t="n">
         <v>78977</v>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523705</v>
+        <v>523489</v>
       </c>
       <c r="R83" t="n">
-        <v>6846300</v>
+        <v>6846326</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755861</v>
+        <v>125755844</v>
       </c>
       <c r="B84" t="n">
         <v>78977</v>
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523389</v>
+        <v>523705</v>
       </c>
       <c r="R84" t="n">
-        <v>6846092</v>
+        <v>6846300</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8778,7 +8778,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755834</v>
+        <v>125755845</v>
       </c>
       <c r="B85" t="n">
         <v>78977</v>
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523489</v>
+        <v>523663</v>
       </c>
       <c r="R85" t="n">
-        <v>6846326</v>
+        <v>6846295</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8875,7 +8875,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755845</v>
+        <v>125755876</v>
       </c>
       <c r="B86" t="n">
         <v>78977</v>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523663</v>
+        <v>523457</v>
       </c>
       <c r="R86" t="n">
-        <v>6846295</v>
+        <v>6846106</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755876</v>
+        <v>125755861</v>
       </c>
       <c r="B87" t="n">
         <v>78977</v>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523457</v>
+        <v>523389</v>
       </c>
       <c r="R87" t="n">
-        <v>6846106</v>
+        <v>6846092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755820</v>
+        <v>125755903</v>
       </c>
       <c r="B88" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523410</v>
+        <v>523586</v>
       </c>
       <c r="R88" t="n">
-        <v>6846112</v>
+        <v>6846193</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,17 +9159,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125742574</v>
+        <v>125755820</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9177,37 +9177,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523592</v>
+        <v>523410</v>
       </c>
       <c r="R89" t="n">
-        <v>6846248</v>
+        <v>6846112</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9251,22 +9251,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755903</v>
+        <v>125755887</v>
       </c>
       <c r="B90" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9274,21 +9274,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523586</v>
+        <v>523473</v>
       </c>
       <c r="R90" t="n">
-        <v>6846193</v>
+        <v>6846157</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9360,7 +9360,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755887</v>
+        <v>125742574</v>
       </c>
       <c r="B91" t="n">
         <v>78977</v>
@@ -9391,17 +9391,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523473</v>
+        <v>523592</v>
       </c>
       <c r="R91" t="n">
-        <v>6846157</v>
+        <v>6846248</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9445,12 +9445,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9748,10 +9748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9759,21 +9759,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R95" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9845,10 +9845,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125741174</v>
+        <v>125742564</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523475</v>
+        <v>523612</v>
       </c>
       <c r="R96" t="n">
-        <v>6846068</v>
+        <v>6846245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10039,35 +10039,51 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125741338</v>
+        <v>125742433</v>
       </c>
       <c r="B98" t="n">
-        <v>78736</v>
+        <v>56848</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
@@ -10129,58 +10145,42 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125742433</v>
+        <v>125741338</v>
       </c>
       <c r="B99" t="n">
-        <v>56848</v>
+        <v>78736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
@@ -10242,17 +10242,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B100" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R100" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125740278</v>
+        <v>125742754</v>
       </c>
       <c r="B101" t="n">
         <v>78977</v>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523522</v>
+        <v>523569</v>
       </c>
       <c r="R101" t="n">
-        <v>6846208</v>
+        <v>6846303</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125742754</v>
+        <v>125740942</v>
       </c>
       <c r="B102" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523569</v>
+        <v>523475</v>
       </c>
       <c r="R102" t="n">
-        <v>6846303</v>
+        <v>6846068</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -1073,48 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125740292</v>
+        <v>125755896</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523521</v>
+        <v>523465</v>
       </c>
       <c r="R6" t="n">
-        <v>6846131</v>
+        <v>6846335</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755818</v>
+        <v>125740292</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523628</v>
+        <v>523521</v>
       </c>
       <c r="R8" t="n">
-        <v>6846224</v>
+        <v>6846131</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755896</v>
+        <v>125755818</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523465</v>
+        <v>523628</v>
       </c>
       <c r="R9" t="n">
-        <v>6846335</v>
+        <v>6846224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,52 +1454,57 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755850</v>
+        <v>125755816</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523417</v>
+        <v>523620</v>
       </c>
       <c r="R10" t="n">
-        <v>6846164</v>
+        <v>6846303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,45 +1563,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755892</v>
+        <v>125755829</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523495</v>
+        <v>523458</v>
       </c>
       <c r="R11" t="n">
-        <v>6846328</v>
+        <v>6846108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,50 +1669,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755816</v>
+        <v>125755850</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523620</v>
+        <v>523417</v>
       </c>
       <c r="R12" t="n">
-        <v>6846303</v>
+        <v>6846164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,54 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755829</v>
+        <v>125755892</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523458</v>
+        <v>523495</v>
       </c>
       <c r="R13" t="n">
-        <v>6846108</v>
+        <v>6846328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755814</v>
+        <v>125740970</v>
       </c>
       <c r="B28" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,34 +3237,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523456</v>
+        <v>523383</v>
       </c>
       <c r="R28" t="n">
-        <v>6846109</v>
+        <v>6846110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,19 +3311,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B29" t="n">
         <v>78977</v>
@@ -3354,17 +3354,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R29" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3408,22 +3408,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,34 +3431,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R30" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,6 +3493,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3505,22 +3510,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125742499</v>
+        <v>125755814</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3528,37 +3533,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523622</v>
+        <v>523456</v>
       </c>
       <c r="R31" t="n">
-        <v>6846233</v>
+        <v>6846109</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3602,22 +3607,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755901</v>
+        <v>125755881</v>
       </c>
       <c r="B32" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3625,21 +3630,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523588</v>
+        <v>523499</v>
       </c>
       <c r="R32" t="n">
-        <v>6846217</v>
+        <v>6846107</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3687,11 +3692,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3709,52 +3709,61 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755873</v>
+        <v>125755831</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523443</v>
+        <v>523491</v>
       </c>
       <c r="R33" t="n">
-        <v>6846083</v>
+        <v>6846097</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,48 +3822,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755833</v>
+        <v>125740933</v>
       </c>
       <c r="B34" t="n">
-        <v>91403</v>
+        <v>78736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523511</v>
+        <v>523405</v>
       </c>
       <c r="R34" t="n">
-        <v>6846118</v>
+        <v>6846104</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3898,19 +3907,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755848</v>
+        <v>125755873</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3945,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523515</v>
+        <v>523443</v>
       </c>
       <c r="R35" t="n">
-        <v>6846181</v>
+        <v>6846083</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4007,32 +4016,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755879</v>
+        <v>125755833</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>91403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523502</v>
+        <v>523511</v>
       </c>
       <c r="R36" t="n">
-        <v>6846082</v>
+        <v>6846118</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4104,54 +4113,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755831</v>
+        <v>125755848</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523491</v>
+        <v>523515</v>
       </c>
       <c r="R37" t="n">
-        <v>6846097</v>
+        <v>6846181</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755813</v>
+        <v>125755879</v>
       </c>
       <c r="B38" t="n">
-        <v>97230</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523458</v>
+        <v>523502</v>
       </c>
       <c r="R38" t="n">
-        <v>6846106</v>
+        <v>6846082</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,48 +4307,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125740933</v>
+        <v>125755813</v>
       </c>
       <c r="B39" t="n">
-        <v>78736</v>
+        <v>97230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523405</v>
+        <v>523458</v>
       </c>
       <c r="R39" t="n">
-        <v>6846104</v>
+        <v>6846106</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4392,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755859</v>
+        <v>125755823</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523396</v>
+        <v>523377</v>
       </c>
       <c r="R40" t="n">
-        <v>6846092</v>
+        <v>6846073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755878</v>
+        <v>125755859</v>
       </c>
       <c r="B41" t="n">
         <v>78977</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523484</v>
+        <v>523396</v>
       </c>
       <c r="R41" t="n">
-        <v>6846075</v>
+        <v>6846092</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755798</v>
+        <v>125755878</v>
       </c>
       <c r="B42" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523586</v>
+        <v>523484</v>
       </c>
       <c r="R42" t="n">
-        <v>6846194</v>
+        <v>6846075</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755823</v>
+        <v>125755798</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523377</v>
+        <v>523586</v>
       </c>
       <c r="R43" t="n">
-        <v>6846073</v>
+        <v>6846194</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755846</v>
+        <v>125740764</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5200,37 +5200,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523604</v>
+        <v>523443</v>
       </c>
       <c r="R48" t="n">
-        <v>6846240</v>
+        <v>6846070</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5274,19 +5274,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755863</v>
+        <v>125755846</v>
       </c>
       <c r="B49" t="n">
         <v>78977</v>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523376</v>
+        <v>523604</v>
       </c>
       <c r="R49" t="n">
-        <v>6846074</v>
+        <v>6846240</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B50" t="n">
         <v>78977</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R50" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755880</v>
+        <v>125755854</v>
       </c>
       <c r="B51" t="n">
         <v>78977</v>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523488</v>
+        <v>523410</v>
       </c>
       <c r="R51" t="n">
-        <v>6846089</v>
+        <v>6846112</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5577,10 +5577,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755796</v>
+        <v>125755880</v>
       </c>
       <c r="B52" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5588,21 +5588,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523627</v>
+        <v>523488</v>
       </c>
       <c r="R52" t="n">
-        <v>6846239</v>
+        <v>6846089</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125740764</v>
+        <v>125755796</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5685,37 +5685,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523443</v>
+        <v>523627</v>
       </c>
       <c r="R53" t="n">
-        <v>6846070</v>
+        <v>6846239</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5759,12 +5759,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755826</v>
+        <v>125755817</v>
       </c>
       <c r="B57" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523408</v>
+        <v>523587</v>
       </c>
       <c r="R57" t="n">
-        <v>6846116</v>
+        <v>6846194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755843</v>
+        <v>125755826</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6170,21 +6170,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523662</v>
+        <v>523408</v>
       </c>
       <c r="R58" t="n">
-        <v>6846272</v>
+        <v>6846116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755891</v>
+        <v>125755843</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523501</v>
+        <v>523662</v>
       </c>
       <c r="R59" t="n">
-        <v>6846327</v>
+        <v>6846272</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755817</v>
+        <v>125755891</v>
       </c>
       <c r="B60" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523587</v>
+        <v>523501</v>
       </c>
       <c r="R60" t="n">
-        <v>6846194</v>
+        <v>6846327</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6450,48 +6450,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125740592</v>
+        <v>125755897</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523450</v>
+        <v>523669</v>
       </c>
       <c r="R61" t="n">
-        <v>6846113</v>
+        <v>6846274</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6535,44 +6535,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755897</v>
+        <v>125755862</v>
       </c>
       <c r="B62" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523669</v>
+        <v>523377</v>
       </c>
       <c r="R62" t="n">
-        <v>6846274</v>
+        <v>6846085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6637,14 +6637,14 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755862</v>
+        <v>125755852</v>
       </c>
       <c r="B63" t="n">
         <v>78977</v>
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523377</v>
+        <v>523420</v>
       </c>
       <c r="R63" t="n">
-        <v>6846085</v>
+        <v>6846145</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755852</v>
+        <v>125755883</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523420</v>
+        <v>523485</v>
       </c>
       <c r="R64" t="n">
-        <v>6846145</v>
+        <v>6846121</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755883</v>
+        <v>125755847</v>
       </c>
       <c r="B65" t="n">
         <v>78977</v>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523485</v>
+        <v>523553</v>
       </c>
       <c r="R65" t="n">
-        <v>6846121</v>
+        <v>6846192</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755847</v>
+        <v>125755841</v>
       </c>
       <c r="B66" t="n">
         <v>78977</v>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523553</v>
+        <v>523605</v>
       </c>
       <c r="R66" t="n">
-        <v>6846192</v>
+        <v>6846199</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755841</v>
+        <v>125755855</v>
       </c>
       <c r="B67" t="n">
         <v>78977</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523605</v>
+        <v>523410</v>
       </c>
       <c r="R67" t="n">
-        <v>6846199</v>
+        <v>6846095</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755855</v>
+        <v>125755858</v>
       </c>
       <c r="B68" t="n">
         <v>78977</v>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523410</v>
+        <v>523393</v>
       </c>
       <c r="R68" t="n">
         <v>6846095</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755858</v>
+        <v>125740592</v>
       </c>
       <c r="B69" t="n">
         <v>78977</v>
@@ -7257,17 +7257,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523393</v>
+        <v>523450</v>
       </c>
       <c r="R69" t="n">
-        <v>6846095</v>
+        <v>6846113</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7311,12 +7311,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755851</v>
+        <v>125755807</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523422</v>
+        <v>523379</v>
       </c>
       <c r="R2" t="n">
-        <v>6846155</v>
+        <v>6846064</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,53 +777,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755807</v>
+        <v>125755824</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>78736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523379</v>
+        <v>523501</v>
       </c>
       <c r="R3" t="n">
-        <v>6846064</v>
+        <v>6846078</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,50 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755815</v>
+        <v>125755851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523605</v>
+        <v>523422</v>
       </c>
       <c r="R4" t="n">
-        <v>6846199</v>
+        <v>6846155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +971,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755824</v>
+        <v>125755815</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523501</v>
+        <v>523605</v>
       </c>
       <c r="R5" t="n">
-        <v>6846078</v>
+        <v>6846199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,48 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755896</v>
+        <v>125740292</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523465</v>
+        <v>523521</v>
       </c>
       <c r="R6" t="n">
-        <v>6846335</v>
+        <v>6846131</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125740292</v>
+        <v>125755896</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523521</v>
+        <v>523465</v>
       </c>
       <c r="R8" t="n">
-        <v>6846131</v>
+        <v>6846335</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1563,54 +1563,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755829</v>
+        <v>125755850</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523458</v>
+        <v>523417</v>
       </c>
       <c r="R11" t="n">
-        <v>6846108</v>
+        <v>6846164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755850</v>
+        <v>125755892</v>
       </c>
       <c r="B12" t="n">
         <v>78977</v>
@@ -1704,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523417</v>
+        <v>523495</v>
       </c>
       <c r="R12" t="n">
-        <v>6846164</v>
+        <v>6846328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,45 +1757,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755892</v>
+        <v>125755829</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523495</v>
+        <v>523458</v>
       </c>
       <c r="R13" t="n">
-        <v>6846328</v>
+        <v>6846108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755864</v>
+        <v>125755802</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2558,21 +2558,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523381</v>
+        <v>523478</v>
       </c>
       <c r="R21" t="n">
-        <v>6846064</v>
+        <v>6846087</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,10 +2644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755802</v>
+        <v>125755864</v>
       </c>
       <c r="B22" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,21 +2655,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523478</v>
+        <v>523381</v>
       </c>
       <c r="R22" t="n">
-        <v>6846087</v>
+        <v>6846064</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755877</v>
+        <v>125755853</v>
       </c>
       <c r="B23" t="n">
         <v>78977</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523461</v>
+        <v>523425</v>
       </c>
       <c r="R23" t="n">
-        <v>6846105</v>
+        <v>6846130</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755853</v>
+        <v>125755840</v>
       </c>
       <c r="B24" t="n">
         <v>78977</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523425</v>
+        <v>523595</v>
       </c>
       <c r="R24" t="n">
-        <v>6846130</v>
+        <v>6846194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755840</v>
+        <v>125755877</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523595</v>
+        <v>523461</v>
       </c>
       <c r="R25" t="n">
-        <v>6846194</v>
+        <v>6846105</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125740970</v>
+        <v>125755901</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,34 +3237,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523383</v>
+        <v>523588</v>
       </c>
       <c r="R28" t="n">
-        <v>6846110</v>
+        <v>6846217</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,6 +3299,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3311,22 +3316,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125742499</v>
+        <v>125755814</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>92724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,37 +3339,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523622</v>
+        <v>523456</v>
       </c>
       <c r="R29" t="n">
-        <v>6846233</v>
+        <v>6846109</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3408,22 +3413,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755901</v>
+        <v>125755881</v>
       </c>
       <c r="B30" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,21 +3436,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3455,10 +3460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523588</v>
+        <v>523499</v>
       </c>
       <c r="R30" t="n">
-        <v>6846217</v>
+        <v>6846107</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,11 +3498,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3515,17 +3515,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755814</v>
+        <v>125740970</v>
       </c>
       <c r="B31" t="n">
-        <v>92724</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3533,34 +3533,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523456</v>
+        <v>523383</v>
       </c>
       <c r="R31" t="n">
-        <v>6846109</v>
+        <v>6846110</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3607,19 +3607,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755881</v>
+        <v>125742499</v>
       </c>
       <c r="B32" t="n">
         <v>78977</v>
@@ -3650,17 +3650,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523499</v>
+        <v>523622</v>
       </c>
       <c r="R32" t="n">
-        <v>6846107</v>
+        <v>6846233</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3704,22 +3704,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755831</v>
+        <v>125755833</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>91403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,43 +3727,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523491</v>
+        <v>523511</v>
       </c>
       <c r="R33" t="n">
-        <v>6846097</v>
+        <v>6846118</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3822,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125740933</v>
+        <v>125755873</v>
       </c>
       <c r="B34" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,37 +3824,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523405</v>
+        <v>523443</v>
       </c>
       <c r="R34" t="n">
-        <v>6846104</v>
+        <v>6846083</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3907,19 +3898,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755873</v>
+        <v>125755848</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -3954,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523443</v>
+        <v>523515</v>
       </c>
       <c r="R35" t="n">
-        <v>6846083</v>
+        <v>6846181</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4016,32 +4007,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755833</v>
+        <v>125755879</v>
       </c>
       <c r="B36" t="n">
-        <v>91403</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523511</v>
+        <v>523502</v>
       </c>
       <c r="R36" t="n">
-        <v>6846118</v>
+        <v>6846082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4113,10 +4104,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755848</v>
+        <v>125740933</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,37 +4115,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523515</v>
+        <v>523405</v>
       </c>
       <c r="R37" t="n">
-        <v>6846181</v>
+        <v>6846104</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4198,44 +4189,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755879</v>
+        <v>125755813</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>97230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4236,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523502</v>
+        <v>523458</v>
       </c>
       <c r="R38" t="n">
-        <v>6846082</v>
+        <v>6846106</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4307,45 +4298,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755813</v>
+        <v>125755831</v>
       </c>
       <c r="B39" t="n">
-        <v>97230</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523458</v>
+        <v>523491</v>
       </c>
       <c r="R39" t="n">
-        <v>6846106</v>
+        <v>6846097</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755823</v>
+        <v>125755798</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523377</v>
+        <v>523586</v>
       </c>
       <c r="R40" t="n">
-        <v>6846073</v>
+        <v>6846194</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755859</v>
+        <v>125755878</v>
       </c>
       <c r="B41" t="n">
         <v>78977</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523396</v>
+        <v>523484</v>
       </c>
       <c r="R41" t="n">
-        <v>6846092</v>
+        <v>6846075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755878</v>
+        <v>125755823</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523484</v>
+        <v>523377</v>
       </c>
       <c r="R42" t="n">
-        <v>6846075</v>
+        <v>6846073</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755798</v>
+        <v>125755859</v>
       </c>
       <c r="B43" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523586</v>
+        <v>523396</v>
       </c>
       <c r="R43" t="n">
-        <v>6846194</v>
+        <v>6846092</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4986,54 +4986,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755828</v>
+        <v>125755875</v>
       </c>
       <c r="B46" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523512</v>
+        <v>523436</v>
       </c>
       <c r="R46" t="n">
-        <v>6846071</v>
+        <v>6846102</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5092,45 +5083,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755875</v>
+        <v>125755828</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523436</v>
+        <v>523512</v>
       </c>
       <c r="R47" t="n">
-        <v>6846102</v>
+        <v>6846071</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755863</v>
+        <v>125755796</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523376</v>
+        <v>523627</v>
       </c>
       <c r="R50" t="n">
-        <v>6846074</v>
+        <v>6846239</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755854</v>
+        <v>125755863</v>
       </c>
       <c r="B51" t="n">
         <v>78977</v>
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523410</v>
+        <v>523376</v>
       </c>
       <c r="R51" t="n">
-        <v>6846112</v>
+        <v>6846074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755880</v>
+        <v>125755854</v>
       </c>
       <c r="B52" t="n">
         <v>78977</v>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523488</v>
+        <v>523410</v>
       </c>
       <c r="R52" t="n">
-        <v>6846089</v>
+        <v>6846112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755796</v>
+        <v>125755880</v>
       </c>
       <c r="B53" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5685,21 +5685,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523627</v>
+        <v>523488</v>
       </c>
       <c r="R53" t="n">
-        <v>6846239</v>
+        <v>6846089</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755817</v>
+        <v>125755826</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523587</v>
+        <v>523408</v>
       </c>
       <c r="R57" t="n">
-        <v>6846194</v>
+        <v>6846116</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755826</v>
+        <v>125755843</v>
       </c>
       <c r="B58" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6170,21 +6170,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523408</v>
+        <v>523662</v>
       </c>
       <c r="R58" t="n">
-        <v>6846116</v>
+        <v>6846272</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755843</v>
+        <v>125755891</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523662</v>
+        <v>523501</v>
       </c>
       <c r="R59" t="n">
-        <v>6846272</v>
+        <v>6846327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755891</v>
+        <v>125755817</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523501</v>
+        <v>523587</v>
       </c>
       <c r="R60" t="n">
-        <v>6846327</v>
+        <v>6846194</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7323,32 +7323,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755837</v>
+        <v>125755898</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523530</v>
+        <v>523635</v>
       </c>
       <c r="R70" t="n">
-        <v>6846281</v>
+        <v>6846293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7420,10 +7420,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755827</v>
+        <v>125755837</v>
       </c>
       <c r="B71" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7431,21 +7431,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523501</v>
+        <v>523530</v>
       </c>
       <c r="R71" t="n">
-        <v>6846078</v>
+        <v>6846281</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7517,32 +7517,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755898</v>
+        <v>125755827</v>
       </c>
       <c r="B72" t="n">
-        <v>92532</v>
+        <v>78735</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523635</v>
+        <v>523501</v>
       </c>
       <c r="R72" t="n">
-        <v>6846293</v>
+        <v>6846078</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755903</v>
+        <v>125742574</v>
       </c>
       <c r="B88" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9080,37 +9080,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523586</v>
+        <v>523592</v>
       </c>
       <c r="R88" t="n">
-        <v>6846193</v>
+        <v>6846248</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9154,12 +9154,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755887</v>
+        <v>125755903</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9274,21 +9274,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9298,10 +9298,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523473</v>
+        <v>523586</v>
       </c>
       <c r="R90" t="n">
-        <v>6846157</v>
+        <v>6846193</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9360,7 +9360,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125742574</v>
+        <v>125755887</v>
       </c>
       <c r="B91" t="n">
         <v>78977</v>
@@ -9391,17 +9391,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523592</v>
+        <v>523473</v>
       </c>
       <c r="R91" t="n">
-        <v>6846248</v>
+        <v>6846157</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9445,12 +9445,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9554,10 +9554,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125741230</v>
+        <v>125742098</v>
       </c>
       <c r="B93" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9565,21 +9565,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523475</v>
+        <v>523403</v>
       </c>
       <c r="R93" t="n">
-        <v>6846068</v>
+        <v>6846072</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9651,10 +9651,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B94" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9662,21 +9662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R94" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10346,10 +10346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125742754</v>
+        <v>125740942</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10357,21 +10357,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523569</v>
+        <v>523475</v>
       </c>
       <c r="R101" t="n">
-        <v>6846303</v>
+        <v>6846068</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B102" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R102" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -9460,7 +9460,7 @@
         <v>125740307</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9554,10 +9554,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125742098</v>
+        <v>125741230</v>
       </c>
       <c r="B93" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9565,21 +9565,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523403</v>
+        <v>523475</v>
       </c>
       <c r="R93" t="n">
-        <v>6846072</v>
+        <v>6846068</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9651,10 +9651,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125741230</v>
+        <v>125742098</v>
       </c>
       <c r="B94" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9662,21 +9662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523475</v>
+        <v>523403</v>
       </c>
       <c r="R94" t="n">
-        <v>6846068</v>
+        <v>6846072</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9748,10 +9748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125741174</v>
+        <v>125742564</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9759,21 +9759,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523475</v>
+        <v>523612</v>
       </c>
       <c r="R95" t="n">
-        <v>6846068</v>
+        <v>6846245</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9845,10 +9845,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B96" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R96" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9945,7 +9945,7 @@
         <v>125742673</v>
       </c>
       <c r="B97" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>125742433</v>
       </c>
       <c r="B98" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>125741338</v>
       </c>
       <c r="B99" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>125740278</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B101" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10357,21 +10357,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R101" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125742754</v>
+        <v>125740942</v>
       </c>
       <c r="B102" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523569</v>
+        <v>523475</v>
       </c>
       <c r="R102" t="n">
-        <v>6846303</v>
+        <v>6846068</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10543,7 +10543,7 @@
         <v>125740148</v>
       </c>
       <c r="B103" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>125740194</v>
       </c>
       <c r="B104" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>125742527</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>125740179</v>
       </c>
       <c r="B106" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -9748,10 +9748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125742564</v>
+        <v>125741174</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9759,21 +9759,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523612</v>
+        <v>523475</v>
       </c>
       <c r="R95" t="n">
-        <v>6846245</v>
+        <v>6846068</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9845,10 +9845,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125741174</v>
+        <v>125742564</v>
       </c>
       <c r="B96" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523475</v>
+        <v>523612</v>
       </c>
       <c r="R96" t="n">
-        <v>6846068</v>
+        <v>6846245</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740278</v>
+        <v>125740942</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523522</v>
+        <v>523475</v>
       </c>
       <c r="R100" t="n">
-        <v>6846208</v>
+        <v>6846068</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125742754</v>
+        <v>125740278</v>
       </c>
       <c r="B101" t="n">
         <v>78980</v>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523569</v>
+        <v>523522</v>
       </c>
       <c r="R101" t="n">
-        <v>6846303</v>
+        <v>6846208</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B102" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R102" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -9457,7 +9457,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125740307</v>
+        <v>125741230</v>
       </c>
       <c r="B92" t="n">
         <v>78980</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523527</v>
+        <v>523475</v>
       </c>
       <c r="R92" t="n">
-        <v>6846185</v>
+        <v>6846068</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125741230</v>
+        <v>125740330</v>
       </c>
       <c r="B93" t="n">
         <v>78980</v>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523475</v>
+        <v>523527</v>
       </c>
       <c r="R93" t="n">
-        <v>6846068</v>
+        <v>6846185</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740942</v>
+        <v>125740278</v>
       </c>
       <c r="B100" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523475</v>
+        <v>523522</v>
       </c>
       <c r="R100" t="n">
-        <v>6846068</v>
+        <v>6846208</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125740278</v>
+        <v>125742754</v>
       </c>
       <c r="B101" t="n">
         <v>78980</v>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523522</v>
+        <v>523569</v>
       </c>
       <c r="R101" t="n">
-        <v>6846208</v>
+        <v>6846303</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125742754</v>
+        <v>125740942</v>
       </c>
       <c r="B102" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523569</v>
+        <v>523475</v>
       </c>
       <c r="R102" t="n">
-        <v>6846303</v>
+        <v>6846068</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -9457,7 +9457,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125741230</v>
+        <v>125740307</v>
       </c>
       <c r="B92" t="n">
         <v>78980</v>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523475</v>
+        <v>523527</v>
       </c>
       <c r="R92" t="n">
-        <v>6846068</v>
+        <v>6846185</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125740330</v>
+        <v>125741230</v>
       </c>
       <c r="B93" t="n">
         <v>78980</v>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523527</v>
+        <v>523475</v>
       </c>
       <c r="R93" t="n">
-        <v>6846185</v>
+        <v>6846068</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740278</v>
+        <v>125740942</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523522</v>
+        <v>523475</v>
       </c>
       <c r="R100" t="n">
-        <v>6846208</v>
+        <v>6846068</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125742754</v>
+        <v>125740278</v>
       </c>
       <c r="B101" t="n">
         <v>78980</v>
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523569</v>
+        <v>523522</v>
       </c>
       <c r="R101" t="n">
-        <v>6846303</v>
+        <v>6846208</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,10 +10443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125740942</v>
+        <v>125742754</v>
       </c>
       <c r="B102" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10454,21 +10454,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523475</v>
+        <v>523569</v>
       </c>
       <c r="R102" t="n">
-        <v>6846068</v>
+        <v>6846303</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10926,6 +10926,111 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125755906</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>523512</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6846116</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -10931,7 +10931,7 @@
         <v>125755906</v>
       </c>
       <c r="B107" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -10931,7 +10931,7 @@
         <v>125755906</v>
       </c>
       <c r="B107" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -11026,7 +11026,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -10931,7 +10931,7 @@
         <v>125755906</v>
       </c>
       <c r="B107" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -10931,7 +10931,7 @@
         <v>125755906</v>
       </c>
       <c r="B107" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755807</v>
+        <v>125755806</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523379</v>
+        <v>523381</v>
       </c>
       <c r="R2" t="n">
         <v>6846064</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755824</v>
+        <v>125755901</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523501</v>
+        <v>523588</v>
       </c>
       <c r="R3" t="n">
-        <v>6846078</v>
+        <v>6846217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På silverlåga utan hänsynssnitslar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755851</v>
+        <v>125755903</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523422</v>
+        <v>523586</v>
       </c>
       <c r="R4" t="n">
-        <v>6846155</v>
+        <v>6846193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,50 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755815</v>
+        <v>125755904</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523605</v>
+        <v>523504</v>
       </c>
       <c r="R5" t="n">
-        <v>6846199</v>
+        <v>6846179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,48 +1068,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125740292</v>
+        <v>125755905</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523521</v>
+        <v>523497</v>
       </c>
       <c r="R6" t="n">
-        <v>6846131</v>
+        <v>6846102</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,44 +1153,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755799</v>
+        <v>125755909</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>92522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523708</v>
+        <v>523407</v>
       </c>
       <c r="R7" t="n">
-        <v>6846300</v>
+        <v>6846172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755896</v>
+        <v>125755833</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523465</v>
+        <v>523511</v>
       </c>
       <c r="R8" t="n">
-        <v>6846335</v>
+        <v>6846118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755818</v>
+        <v>125755814</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523628</v>
+        <v>523456</v>
       </c>
       <c r="R9" t="n">
-        <v>6846224</v>
+        <v>6846109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,50 +1456,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755816</v>
+        <v>125755897</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523620</v>
+        <v>523669</v>
       </c>
       <c r="R10" t="n">
-        <v>6846303</v>
+        <v>6846274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755850</v>
+        <v>125755898</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523417</v>
+        <v>523635</v>
       </c>
       <c r="R11" t="n">
-        <v>6846164</v>
+        <v>6846293</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,14 +1650,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755892</v>
+        <v>125740028</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1691,17 +1681,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523495</v>
+        <v>523464</v>
       </c>
       <c r="R12" t="n">
-        <v>6846328</v>
+        <v>6846338</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1745,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755829</v>
+        <v>125740148</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,43 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523458</v>
+        <v>523497</v>
       </c>
       <c r="R13" t="n">
-        <v>6846108</v>
+        <v>6846271</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,26 +1832,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125740874</v>
+        <v>125740179</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1894,17 +1875,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523432</v>
+        <v>523507</v>
       </c>
       <c r="R14" t="n">
-        <v>6846118</v>
+        <v>6846247</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1948,62 +1929,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755812</v>
+        <v>125740194</v>
       </c>
       <c r="B15" t="n">
-        <v>57653</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523437</v>
+        <v>523518</v>
       </c>
       <c r="R15" t="n">
-        <v>6846102</v>
+        <v>6846232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2050,26 +2026,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755874</v>
+        <v>125740221</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2093,17 +2069,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523446</v>
+        <v>523538</v>
       </c>
       <c r="R16" t="n">
-        <v>6846093</v>
+        <v>6846149</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2147,26 +2123,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755836</v>
+        <v>125740278</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2194,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523502</v>
+        <v>523522</v>
       </c>
       <c r="R17" t="n">
-        <v>6846299</v>
+        <v>6846208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2244,26 +2220,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755839</v>
+        <v>125740307</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2291,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523537</v>
+        <v>523527</v>
       </c>
       <c r="R18" t="n">
-        <v>6846261</v>
+        <v>6846185</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755909</v>
+        <v>125740592</v>
       </c>
       <c r="B19" t="n">
-        <v>91829</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,37 +2340,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523407</v>
+        <v>523450</v>
       </c>
       <c r="R19" t="n">
-        <v>6846172</v>
+        <v>6846113</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2438,26 +2414,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755842</v>
+        <v>125740847</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2485,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523656</v>
+        <v>523475</v>
       </c>
       <c r="R20" t="n">
-        <v>6846239</v>
+        <v>6846068</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2535,60 +2511,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755802</v>
+        <v>125740874</v>
       </c>
       <c r="B21" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523478</v>
+        <v>523432</v>
       </c>
       <c r="R21" t="n">
-        <v>6846087</v>
+        <v>6846118</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2632,26 +2608,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755864</v>
+        <v>125740970</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2675,14 +2651,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523381</v>
+        <v>523383</v>
       </c>
       <c r="R22" t="n">
-        <v>6846064</v>
+        <v>6846110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,26 +2705,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755853</v>
+        <v>125741448</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2776,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523425</v>
+        <v>523403</v>
       </c>
       <c r="R23" t="n">
-        <v>6846130</v>
+        <v>6846072</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,26 +2802,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755840</v>
+        <v>125742499</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2869,17 +2845,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523595</v>
+        <v>523622</v>
       </c>
       <c r="R24" t="n">
-        <v>6846194</v>
+        <v>6846233</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2923,26 +2899,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755877</v>
+        <v>125742564</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2970,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523461</v>
+        <v>523612</v>
       </c>
       <c r="R25" t="n">
-        <v>6846105</v>
+        <v>6846245</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,26 +2996,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755857</v>
+        <v>125742574</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3063,17 +3039,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523398</v>
+        <v>523592</v>
       </c>
       <c r="R26" t="n">
-        <v>6846095</v>
+        <v>6846248</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3117,26 +3093,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755890</v>
+        <v>125742673</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3164,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523496</v>
+        <v>523590</v>
       </c>
       <c r="R27" t="n">
-        <v>6846308</v>
+        <v>6846277</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,44 +3190,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755901</v>
+        <v>125742725</v>
       </c>
       <c r="B28" t="n">
-        <v>78644</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3261,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523588</v>
+        <v>523569</v>
       </c>
       <c r="R28" t="n">
-        <v>6846217</v>
+        <v>6846303</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,11 +3275,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På silverlåga utan hänsynssnitslar</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3316,60 +3287,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755814</v>
+        <v>125742866</v>
       </c>
       <c r="B29" t="n">
-        <v>92724</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523456</v>
+        <v>523542</v>
       </c>
       <c r="R29" t="n">
-        <v>6846109</v>
+        <v>6846346</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3413,26 +3384,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755881</v>
+        <v>125755834</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3460,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523499</v>
+        <v>523489</v>
       </c>
       <c r="R30" t="n">
-        <v>6846107</v>
+        <v>6846326</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3522,14 +3493,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125740970</v>
+        <v>125755836</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3553,14 +3524,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523383</v>
+        <v>523502</v>
       </c>
       <c r="R31" t="n">
-        <v>6846110</v>
+        <v>6846299</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3607,26 +3578,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125742499</v>
+        <v>125755837</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3650,17 +3621,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523622</v>
+        <v>523530</v>
       </c>
       <c r="R32" t="n">
-        <v>6846233</v>
+        <v>6846281</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3704,22 +3675,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755833</v>
+        <v>125755839</v>
       </c>
       <c r="B33" t="n">
-        <v>91403</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3751,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523511</v>
+        <v>523537</v>
       </c>
       <c r="R33" t="n">
-        <v>6846118</v>
+        <v>6846261</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,14 +3784,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755873</v>
+        <v>125755840</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3848,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523443</v>
+        <v>523595</v>
       </c>
       <c r="R34" t="n">
-        <v>6846083</v>
+        <v>6846194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3910,14 +3881,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755848</v>
+        <v>125755841</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3945,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523515</v>
+        <v>523605</v>
       </c>
       <c r="R35" t="n">
-        <v>6846181</v>
+        <v>6846199</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4007,14 +3978,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755879</v>
+        <v>125755842</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4042,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523502</v>
+        <v>523656</v>
       </c>
       <c r="R36" t="n">
-        <v>6846082</v>
+        <v>6846239</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4104,48 +4075,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125740933</v>
+        <v>125755843</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523405</v>
+        <v>523662</v>
       </c>
       <c r="R37" t="n">
-        <v>6846104</v>
+        <v>6846272</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4189,44 +4160,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755813</v>
+        <v>125755844</v>
       </c>
       <c r="B38" t="n">
-        <v>97230</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4236,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523458</v>
+        <v>523705</v>
       </c>
       <c r="R38" t="n">
-        <v>6846106</v>
+        <v>6846300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4298,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755831</v>
+        <v>125755845</v>
       </c>
       <c r="B39" t="n">
-        <v>98352</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4309,43 +4280,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523491</v>
+        <v>523663</v>
       </c>
       <c r="R39" t="n">
-        <v>6846097</v>
+        <v>6846295</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755798</v>
+        <v>125755846</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523586</v>
+        <v>523604</v>
       </c>
       <c r="R40" t="n">
-        <v>6846194</v>
+        <v>6846240</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,14 +4463,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755878</v>
+        <v>125755847</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4536,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523484</v>
+        <v>523553</v>
       </c>
       <c r="R41" t="n">
-        <v>6846075</v>
+        <v>6846192</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4598,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755823</v>
+        <v>125755848</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523377</v>
+        <v>523515</v>
       </c>
       <c r="R42" t="n">
-        <v>6846073</v>
+        <v>6846181</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4695,14 +4657,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755859</v>
+        <v>125755849</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4730,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523396</v>
+        <v>523414</v>
       </c>
       <c r="R43" t="n">
-        <v>6846092</v>
+        <v>6846169</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4792,14 +4754,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125740221</v>
+        <v>125755850</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4823,17 +4785,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523538</v>
+        <v>523417</v>
       </c>
       <c r="R44" t="n">
-        <v>6846149</v>
+        <v>6846164</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4877,44 +4839,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755806</v>
+        <v>125755851</v>
       </c>
       <c r="B45" t="n">
-        <v>79009</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4924,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523381</v>
+        <v>523422</v>
       </c>
       <c r="R45" t="n">
-        <v>6846064</v>
+        <v>6846155</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4986,14 +4948,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755875</v>
+        <v>125755852</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5021,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523436</v>
+        <v>523420</v>
       </c>
       <c r="R46" t="n">
-        <v>6846102</v>
+        <v>6846145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5083,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755828</v>
+        <v>125755853</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5094,43 +5056,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523512</v>
+        <v>523425</v>
       </c>
       <c r="R47" t="n">
-        <v>6846071</v>
+        <v>6846130</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5189,48 +5142,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125740764</v>
+        <v>125755854</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523443</v>
+        <v>523410</v>
       </c>
       <c r="R48" t="n">
-        <v>6846070</v>
+        <v>6846112</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5274,26 +5227,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755846</v>
+        <v>125755855</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5321,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523604</v>
+        <v>523410</v>
       </c>
       <c r="R49" t="n">
-        <v>6846240</v>
+        <v>6846095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5383,32 +5336,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755796</v>
+        <v>125755857</v>
       </c>
       <c r="B50" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5418,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523627</v>
+        <v>523398</v>
       </c>
       <c r="R50" t="n">
-        <v>6846239</v>
+        <v>6846095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5480,14 +5433,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755863</v>
+        <v>125755858</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5515,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523376</v>
+        <v>523393</v>
       </c>
       <c r="R51" t="n">
-        <v>6846074</v>
+        <v>6846095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5577,14 +5530,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755854</v>
+        <v>125755859</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5612,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523410</v>
+        <v>523396</v>
       </c>
       <c r="R52" t="n">
-        <v>6846112</v>
+        <v>6846092</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5674,14 +5627,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755880</v>
+        <v>125755861</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5709,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523488</v>
+        <v>523389</v>
       </c>
       <c r="R53" t="n">
-        <v>6846089</v>
+        <v>6846092</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,14 +5724,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755882</v>
+        <v>125755862</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5806,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523515</v>
+        <v>523377</v>
       </c>
       <c r="R54" t="n">
-        <v>6846106</v>
+        <v>6846085</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5868,32 +5821,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755805</v>
+        <v>125755863</v>
       </c>
       <c r="B55" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5903,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523478</v>
+        <v>523376</v>
       </c>
       <c r="R55" t="n">
-        <v>6846168</v>
+        <v>6846074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5965,32 +5918,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755804</v>
+        <v>125755864</v>
       </c>
       <c r="B56" t="n">
-        <v>79595</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6000,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523485</v>
+        <v>523381</v>
       </c>
       <c r="R56" t="n">
-        <v>6846156</v>
+        <v>6846064</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6062,32 +6015,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755826</v>
+        <v>125755866</v>
       </c>
       <c r="B57" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6097,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523408</v>
+        <v>523377</v>
       </c>
       <c r="R57" t="n">
-        <v>6846116</v>
+        <v>6846049</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6159,14 +6112,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755843</v>
+        <v>125755867</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6194,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523662</v>
+        <v>523387</v>
       </c>
       <c r="R58" t="n">
-        <v>6846272</v>
+        <v>6846052</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6256,14 +6209,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755891</v>
+        <v>125755868</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6291,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523501</v>
+        <v>523368</v>
       </c>
       <c r="R59" t="n">
-        <v>6846327</v>
+        <v>6846059</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6353,32 +6306,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755817</v>
+        <v>125755870</v>
       </c>
       <c r="B60" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6388,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523587</v>
+        <v>523403</v>
       </c>
       <c r="R60" t="n">
-        <v>6846194</v>
+        <v>6846057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6450,32 +6403,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755897</v>
+        <v>125755871</v>
       </c>
       <c r="B61" t="n">
-        <v>92532</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6485,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523669</v>
+        <v>523411</v>
       </c>
       <c r="R61" t="n">
-        <v>6846274</v>
+        <v>6846060</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6547,14 +6500,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125755862</v>
+        <v>125755872</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6582,10 +6535,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523377</v>
+        <v>523424</v>
       </c>
       <c r="R62" t="n">
-        <v>6846085</v>
+        <v>6846058</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6644,14 +6597,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755852</v>
+        <v>125755873</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6679,10 +6632,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523420</v>
+        <v>523443</v>
       </c>
       <c r="R63" t="n">
-        <v>6846145</v>
+        <v>6846083</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6741,14 +6694,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755883</v>
+        <v>125755874</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6776,10 +6729,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523485</v>
+        <v>523446</v>
       </c>
       <c r="R64" t="n">
-        <v>6846121</v>
+        <v>6846093</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6838,14 +6791,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755847</v>
+        <v>125755875</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6873,10 +6826,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523553</v>
+        <v>523436</v>
       </c>
       <c r="R65" t="n">
-        <v>6846192</v>
+        <v>6846102</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6935,14 +6888,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755841</v>
+        <v>125755876</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6970,10 +6923,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523605</v>
+        <v>523457</v>
       </c>
       <c r="R66" t="n">
-        <v>6846199</v>
+        <v>6846106</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7032,14 +6985,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755855</v>
+        <v>125755877</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7067,10 +7020,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523410</v>
+        <v>523461</v>
       </c>
       <c r="R67" t="n">
-        <v>6846095</v>
+        <v>6846105</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7129,14 +7082,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755858</v>
+        <v>125755878</v>
       </c>
       <c r="B68" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7164,10 +7117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523393</v>
+        <v>523484</v>
       </c>
       <c r="R68" t="n">
-        <v>6846095</v>
+        <v>6846075</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7226,14 +7179,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125740592</v>
+        <v>125755879</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7257,17 +7210,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523450</v>
+        <v>523502</v>
       </c>
       <c r="R69" t="n">
-        <v>6846113</v>
+        <v>6846082</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7311,44 +7264,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755898</v>
+        <v>125755880</v>
       </c>
       <c r="B70" t="n">
-        <v>92532</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7358,10 +7311,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523635</v>
+        <v>523488</v>
       </c>
       <c r="R70" t="n">
-        <v>6846293</v>
+        <v>6846089</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7420,14 +7373,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755837</v>
+        <v>125755881</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7455,10 +7408,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523530</v>
+        <v>523499</v>
       </c>
       <c r="R71" t="n">
-        <v>6846281</v>
+        <v>6846107</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7517,32 +7470,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755827</v>
+        <v>125755882</v>
       </c>
       <c r="B72" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7552,10 +7505,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523501</v>
+        <v>523515</v>
       </c>
       <c r="R72" t="n">
-        <v>6846078</v>
+        <v>6846106</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7614,14 +7567,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755888</v>
+        <v>125755883</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7649,10 +7602,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523478</v>
+        <v>523485</v>
       </c>
       <c r="R73" t="n">
-        <v>6846168</v>
+        <v>6846121</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7711,14 +7664,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755886</v>
+        <v>125755884</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -7746,10 +7699,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523485</v>
+        <v>523471</v>
       </c>
       <c r="R74" t="n">
-        <v>6846156</v>
+        <v>6846134</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7808,14 +7761,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755889</v>
+        <v>125755885</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -7843,10 +7796,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523490</v>
+        <v>523473</v>
       </c>
       <c r="R75" t="n">
-        <v>6846171</v>
+        <v>6846151</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7905,32 +7858,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755905</v>
+        <v>125755886</v>
       </c>
       <c r="B76" t="n">
-        <v>78644</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7940,10 +7893,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523497</v>
+        <v>523485</v>
       </c>
       <c r="R76" t="n">
-        <v>6846102</v>
+        <v>6846156</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8002,32 +7955,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755904</v>
+        <v>125755887</v>
       </c>
       <c r="B77" t="n">
-        <v>78644</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8037,10 +7990,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523504</v>
+        <v>523473</v>
       </c>
       <c r="R77" t="n">
-        <v>6846179</v>
+        <v>6846157</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8099,14 +8052,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755885</v>
+        <v>125755888</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8134,10 +8087,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523473</v>
+        <v>523478</v>
       </c>
       <c r="R78" t="n">
-        <v>6846151</v>
+        <v>6846168</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,32 +8149,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755825</v>
+        <v>125755889</v>
       </c>
       <c r="B79" t="n">
-        <v>78735</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8231,10 +8184,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523628</v>
+        <v>523490</v>
       </c>
       <c r="R79" t="n">
-        <v>6846224</v>
+        <v>6846171</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8293,32 +8246,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755819</v>
+        <v>125755890</v>
       </c>
       <c r="B80" t="n">
-        <v>78736</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8281,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523628</v>
+        <v>523496</v>
       </c>
       <c r="R80" t="n">
-        <v>6846238</v>
+        <v>6846308</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8390,14 +8343,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755849</v>
+        <v>125755891</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -8425,10 +8378,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523414</v>
+        <v>523501</v>
       </c>
       <c r="R81" t="n">
-        <v>6846169</v>
+        <v>6846327</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8487,14 +8440,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755884</v>
+        <v>125755892</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -8522,10 +8475,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523471</v>
+        <v>523495</v>
       </c>
       <c r="R82" t="n">
-        <v>6846134</v>
+        <v>6846328</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8584,14 +8537,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755834</v>
+        <v>125755893</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -8619,10 +8572,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523489</v>
+        <v>523487</v>
       </c>
       <c r="R83" t="n">
-        <v>6846326</v>
+        <v>6846349</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8681,14 +8634,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755844</v>
+        <v>125755894</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -8716,10 +8669,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523705</v>
+        <v>523483</v>
       </c>
       <c r="R84" t="n">
-        <v>6846300</v>
+        <v>6846348</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8778,14 +8731,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755845</v>
+        <v>125755895</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -8813,10 +8766,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523663</v>
+        <v>523471</v>
       </c>
       <c r="R85" t="n">
-        <v>6846295</v>
+        <v>6846349</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8875,14 +8828,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755876</v>
+        <v>125755896</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -8910,10 +8863,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523457</v>
+        <v>523465</v>
       </c>
       <c r="R86" t="n">
-        <v>6846106</v>
+        <v>6846335</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8972,10 +8925,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755861</v>
+        <v>125755825</v>
       </c>
       <c r="B87" t="n">
-        <v>78977</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8983,21 +8936,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9007,10 +8960,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523389</v>
+        <v>523628</v>
       </c>
       <c r="R87" t="n">
-        <v>6846092</v>
+        <v>6846224</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9069,10 +9022,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125742574</v>
+        <v>125755826</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9080,37 +9033,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523592</v>
+        <v>523408</v>
       </c>
       <c r="R88" t="n">
-        <v>6846248</v>
+        <v>6846116</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9154,22 +9107,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755820</v>
+        <v>125755827</v>
       </c>
       <c r="B89" t="n">
-        <v>78736</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9177,21 +9130,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9201,10 +9154,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523410</v>
+        <v>523501</v>
       </c>
       <c r="R89" t="n">
-        <v>6846112</v>
+        <v>6846078</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9263,10 +9216,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755903</v>
+        <v>125740942</v>
       </c>
       <c r="B90" t="n">
-        <v>78644</v>
+        <v>79946</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9274,21 +9227,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9298,10 +9251,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523586</v>
+        <v>523475</v>
       </c>
       <c r="R90" t="n">
-        <v>6846193</v>
+        <v>6846068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9348,22 +9301,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755887</v>
+        <v>125741357</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>79946</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9371,21 +9324,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9395,10 +9348,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523473</v>
+        <v>523403</v>
       </c>
       <c r="R91" t="n">
-        <v>6846157</v>
+        <v>6846072</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9445,22 +9398,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125740307</v>
+        <v>125755796</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9468,21 +9421,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9492,10 +9445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523527</v>
+        <v>523627</v>
       </c>
       <c r="R92" t="n">
-        <v>6846185</v>
+        <v>6846239</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9542,22 +9495,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125741230</v>
+        <v>125755798</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9565,21 +9518,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9589,10 +9542,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523475</v>
+        <v>523586</v>
       </c>
       <c r="R93" t="n">
-        <v>6846068</v>
+        <v>6846194</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9639,22 +9592,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125742098</v>
+        <v>125755799</v>
       </c>
       <c r="B94" t="n">
-        <v>79598</v>
+        <v>79946</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9686,10 +9639,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523403</v>
+        <v>523708</v>
       </c>
       <c r="R94" t="n">
-        <v>6846072</v>
+        <v>6846300</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9736,22 +9689,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125741174</v>
+        <v>125755801</v>
       </c>
       <c r="B95" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9759,21 +9712,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9783,10 +9736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523475</v>
+        <v>523416</v>
       </c>
       <c r="R95" t="n">
-        <v>6846068</v>
+        <v>6846048</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9833,22 +9786,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125742564</v>
+        <v>125755802</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9856,21 +9809,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9880,10 +9833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523612</v>
+        <v>523478</v>
       </c>
       <c r="R96" t="n">
-        <v>6846245</v>
+        <v>6846087</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9930,22 +9883,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125742673</v>
+        <v>125755804</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9953,21 +9906,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9977,10 +9930,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523590</v>
+        <v>523485</v>
       </c>
       <c r="R97" t="n">
-        <v>6846277</v>
+        <v>6846156</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10027,73 +9980,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125742433</v>
+        <v>125755805</v>
       </c>
       <c r="B98" t="n">
-        <v>56849</v>
+        <v>79946</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523403</v>
+        <v>523478</v>
       </c>
       <c r="R98" t="n">
-        <v>6846072</v>
+        <v>6846168</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10140,57 +10077,62 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125741338</v>
+        <v>125755812</v>
       </c>
       <c r="B99" t="n">
-        <v>78739</v>
+        <v>57950</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523403</v>
+        <v>523437</v>
       </c>
       <c r="R99" t="n">
-        <v>6846072</v>
+        <v>6846102</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10237,57 +10179,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125740278</v>
+        <v>125755906</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523522</v>
+        <v>523512</v>
       </c>
       <c r="R100" t="n">
-        <v>6846208</v>
+        <v>6846116</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10334,57 +10284,73 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125742754</v>
+        <v>125742433</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>57141</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523569</v>
+        <v>523403</v>
       </c>
       <c r="R101" t="n">
-        <v>6846303</v>
+        <v>6846072</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10436,55 +10402,60 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125740942</v>
+        <v>125755807</v>
       </c>
       <c r="B102" t="n">
-        <v>79598</v>
+        <v>57141</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523475</v>
+        <v>523379</v>
       </c>
       <c r="R102" t="n">
-        <v>6846068</v>
+        <v>6846064</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10528,57 +10499,62 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125740148</v>
+        <v>125755815</v>
       </c>
       <c r="B103" t="n">
-        <v>78980</v>
+        <v>8455</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523497</v>
+        <v>523605</v>
       </c>
       <c r="R103" t="n">
-        <v>6846271</v>
+        <v>6846199</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10625,57 +10601,62 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125740194</v>
+        <v>125755816</v>
       </c>
       <c r="B104" t="n">
-        <v>78980</v>
+        <v>8455</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523518</v>
+        <v>523620</v>
       </c>
       <c r="R104" t="n">
-        <v>6846232</v>
+        <v>6846303</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10722,60 +10703,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125742527</v>
+        <v>125740292</v>
       </c>
       <c r="B105" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stora Mysingen, Hls</t>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523403</v>
+        <v>523521</v>
       </c>
       <c r="R105" t="n">
-        <v>6846072</v>
+        <v>6846131</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10819,57 +10800,66 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125740179</v>
+        <v>125755828</v>
       </c>
       <c r="B106" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523507</v>
+        <v>523512</v>
       </c>
       <c r="R106" t="n">
-        <v>6846247</v>
+        <v>6846071</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10916,65 +10906,66 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755906</v>
+        <v>125755829</v>
       </c>
       <c r="B107" t="n">
-        <v>57713</v>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Stora Mysingen, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523512</v>
+        <v>523458</v>
       </c>
       <c r="R107" t="n">
-        <v>6846116</v>
+        <v>6846108</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,6 +11021,1290 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>125755830</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>523514</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6846070</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125755831</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>523491</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6846097</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125755813</v>
+      </c>
+      <c r="B110" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>523458</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6846106</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>125740764</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>523443</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6846070</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>125740933</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>523405</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6846104</v>
+      </c>
+      <c r="S112" t="n">
+        <v>20</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125740938</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>523475</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6846068</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>125741338</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>523403</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6846072</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>125755817</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>523587</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6846194</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>125755818</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>523628</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6846224</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>125755819</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>523628</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6846238</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>125755820</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>523410</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6846112</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>125755823</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>523377</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6846073</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>125755824</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Stora Mysingen, Hls</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>523501</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6846078</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25595-2025 artfynd.xlsx
+++ b/artfynd/A 25595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755806</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755903</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755904</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755833</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755814</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755897</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755898</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740028</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740148</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740179</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740194</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740221</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740278</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740307</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740847</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740874</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740970</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125741448</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742499</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742564</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742574</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742673</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742725</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742866</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755834</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755836</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755837</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755839</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755840</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755841</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755842</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755843</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4266,6 +4451,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755844</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755845</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755846</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755847</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755848</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755849</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755850</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755851</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755852</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755853</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755854</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5333,6 +5573,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755855</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5430,6 +5675,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755857</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5527,6 +5777,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755858</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5624,6 +5879,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755859</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5721,6 +5981,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755861</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5818,6 +6083,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755862</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5915,6 +6185,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755863</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6012,6 +6287,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755864</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6109,6 +6389,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755866</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6206,6 +6491,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755867</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6303,6 +6593,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755868</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6400,6 +6695,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755870</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6497,6 +6797,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755871</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6594,6 +6899,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755872</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6691,6 +7001,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755873</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6788,6 +7103,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755874</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6885,6 +7205,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755875</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6982,6 +7307,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755876</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7079,6 +7409,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755877</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7176,6 +7511,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755878</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7273,6 +7613,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755879</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7370,6 +7715,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755880</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7467,6 +7817,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755881</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7564,6 +7919,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755882</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7661,6 +8021,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755883</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7758,6 +8123,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755884</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7855,6 +8225,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755885</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7952,6 +8327,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755886</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8049,6 +8429,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755887</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8146,6 +8531,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755888</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8243,6 +8633,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755889</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8340,6 +8735,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755890</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8437,6 +8837,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755891</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8534,6 +8939,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755892</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8631,6 +9041,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755893</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8728,6 +9143,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755894</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8825,6 +9245,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755895</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8922,6 +9347,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755896</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9019,6 +9449,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755825</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9116,6 +9551,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755826</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9213,6 +9653,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755827</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9310,6 +9755,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740942</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9407,6 +9857,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125741357</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9504,6 +9959,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755796</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9601,6 +10061,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755798</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9698,6 +10163,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755799</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9795,6 +10265,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755801</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9892,6 +10367,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755802</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9989,6 +10469,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755804</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10086,6 +10571,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755805</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10188,6 +10678,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755812</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10293,6 +10788,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755906</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10406,6 +10906,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125742433</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10508,6 +11013,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755807</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10610,6 +11120,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755815</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10712,6 +11227,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755816</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10809,6 +11329,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740292</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10915,6 +11440,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755828</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11021,6 +11551,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755829</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11132,6 +11667,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755830</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11238,6 +11778,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755831</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11335,6 +11880,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755813</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11432,6 +11982,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740764</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11529,6 +12084,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740933</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11626,6 +12186,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740938</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11723,6 +12288,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125741338</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11820,6 +12390,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755817</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11917,6 +12492,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755818</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12014,6 +12594,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755819</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12111,6 +12696,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755820</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12208,6 +12798,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755823</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12305,8 +12900,134 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125755824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>